--- a/output/licitacion_vitacura.xlsx
+++ b/output/licitacion_vitacura.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -212,6 +212,17 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -607,7 +618,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1170,9 +1181,9 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1300,6 +1311,13 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="27" fillId="15" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="27" fillId="15" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1309,11 +1327,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1324,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1332,10 +1351,10 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="13" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3134,7 +3153,9 @@
         </is>
       </c>
       <c r="D45" s="49" t="n"/>
-      <c r="E45" s="197" t="n"/>
+      <c r="E45" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F45" s="210">
         <f>+D45*E45</f>
         <v/>
@@ -3163,7 +3184,9 @@
         </is>
       </c>
       <c r="D46" s="49" t="n"/>
-      <c r="E46" s="197" t="n"/>
+      <c r="E46" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F46" s="210">
         <f>+D46*E46</f>
         <v/>
@@ -3192,7 +3215,9 @@
         </is>
       </c>
       <c r="D47" s="49" t="n"/>
-      <c r="E47" s="197" t="n"/>
+      <c r="E47" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F47" s="210">
         <f>+D47*E47</f>
         <v/>
@@ -3221,7 +3246,9 @@
         </is>
       </c>
       <c r="D48" s="49" t="n"/>
-      <c r="E48" s="197" t="n"/>
+      <c r="E48" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F48" s="210">
         <f>+D48*E48</f>
         <v/>
@@ -3283,7 +3310,9 @@
         </is>
       </c>
       <c r="D50" s="49" t="n"/>
-      <c r="E50" s="197" t="n"/>
+      <c r="E50" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F50" s="210">
         <f>+D50*E50</f>
         <v/>
@@ -3312,7 +3341,9 @@
         </is>
       </c>
       <c r="D51" s="49" t="n"/>
-      <c r="E51" s="197" t="n"/>
+      <c r="E51" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F51" s="210">
         <f>+D51*E51</f>
         <v/>
@@ -3341,7 +3372,9 @@
         </is>
       </c>
       <c r="D52" s="49" t="n"/>
-      <c r="E52" s="197" t="n"/>
+      <c r="E52" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F52" s="210">
         <f>+D52*E52</f>
         <v/>
@@ -3370,7 +3403,9 @@
         </is>
       </c>
       <c r="D53" s="49" t="n"/>
-      <c r="E53" s="197" t="n"/>
+      <c r="E53" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F53" s="210">
         <f>+D53*E53</f>
         <v/>
@@ -3399,9 +3434,11 @@
         </is>
       </c>
       <c r="D54" s="221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="197" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="E54" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F54" s="205">
         <f>D54*E54</f>
         <v/>
@@ -3628,7 +3665,9 @@
         </is>
       </c>
       <c r="D62" s="49" t="n"/>
-      <c r="E62" s="197" t="n"/>
+      <c r="E62" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F62" s="210">
         <f>+D62*E62</f>
         <v/>
@@ -3657,7 +3696,9 @@
         </is>
       </c>
       <c r="D63" s="49" t="n"/>
-      <c r="E63" s="197" t="n"/>
+      <c r="E63" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F63" s="210">
         <f>+D63*E63</f>
         <v/>
@@ -3686,7 +3727,9 @@
         </is>
       </c>
       <c r="D64" s="49" t="n"/>
-      <c r="E64" s="197" t="n"/>
+      <c r="E64" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F64" s="210">
         <f>+D64*E64</f>
         <v/>
@@ -3715,7 +3758,9 @@
         </is>
       </c>
       <c r="D65" s="49" t="n"/>
-      <c r="E65" s="197" t="n"/>
+      <c r="E65" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F65" s="210">
         <f>+D65*E65</f>
         <v/>
@@ -3777,7 +3822,9 @@
         </is>
       </c>
       <c r="D67" s="49" t="n"/>
-      <c r="E67" s="197" t="n"/>
+      <c r="E67" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F67" s="210">
         <f>+D67*E67</f>
         <v/>
@@ -3806,7 +3853,9 @@
         </is>
       </c>
       <c r="D68" s="49" t="n"/>
-      <c r="E68" s="197" t="n"/>
+      <c r="E68" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F68" s="210">
         <f>+D68*E68</f>
         <v/>
@@ -3835,7 +3884,9 @@
         </is>
       </c>
       <c r="D69" s="49" t="n"/>
-      <c r="E69" s="197" t="n"/>
+      <c r="E69" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F69" s="210">
         <f>+D69*E69</f>
         <v/>
@@ -3864,7 +3915,9 @@
         </is>
       </c>
       <c r="D70" s="49" t="n"/>
-      <c r="E70" s="197" t="n"/>
+      <c r="E70" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F70" s="210">
         <f>+D70*E70</f>
         <v/>
@@ -3893,7 +3946,9 @@
         </is>
       </c>
       <c r="D71" s="49" t="n"/>
-      <c r="E71" s="197" t="n"/>
+      <c r="E71" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F71" s="210">
         <f>+D71*E71</f>
         <v/>
@@ -4089,7 +4144,9 @@
         </is>
       </c>
       <c r="D78" s="49" t="n"/>
-      <c r="E78" s="197" t="n"/>
+      <c r="E78" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F78" s="210">
         <f>+D78*E78</f>
         <v/>
@@ -4118,7 +4175,9 @@
         </is>
       </c>
       <c r="D79" s="49" t="n"/>
-      <c r="E79" s="197" t="n"/>
+      <c r="E79" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F79" s="210">
         <f>+D79*E79</f>
         <v/>
@@ -4147,7 +4206,9 @@
         </is>
       </c>
       <c r="D80" s="49" t="n"/>
-      <c r="E80" s="197" t="n"/>
+      <c r="E80" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F80" s="210">
         <f>+D80*E80</f>
         <v/>
@@ -4176,7 +4237,9 @@
         </is>
       </c>
       <c r="D81" s="49" t="n"/>
-      <c r="E81" s="197" t="n"/>
+      <c r="E81" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F81" s="210">
         <f>+D81*E81</f>
         <v/>
@@ -4238,7 +4301,9 @@
         </is>
       </c>
       <c r="D83" s="49" t="n"/>
-      <c r="E83" s="197" t="n"/>
+      <c r="E83" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F83" s="210">
         <f>+D83*E83</f>
         <v/>
@@ -4267,7 +4332,9 @@
         </is>
       </c>
       <c r="D84" s="49" t="n"/>
-      <c r="E84" s="197" t="n"/>
+      <c r="E84" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F84" s="210">
         <f>+D84*E84</f>
         <v/>
@@ -4296,7 +4363,9 @@
         </is>
       </c>
       <c r="D85" s="49" t="n"/>
-      <c r="E85" s="197" t="n"/>
+      <c r="E85" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F85" s="210">
         <f>+D85*E85</f>
         <v/>
@@ -4325,7 +4394,9 @@
         </is>
       </c>
       <c r="D86" s="49" t="n"/>
-      <c r="E86" s="197" t="n"/>
+      <c r="E86" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F86" s="210">
         <f>+D86*E86</f>
         <v/>
@@ -4354,7 +4425,9 @@
         </is>
       </c>
       <c r="D87" s="49" t="n"/>
-      <c r="E87" s="197" t="n"/>
+      <c r="E87" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F87" s="210">
         <f>+D87*E87</f>
         <v/>
@@ -4550,7 +4623,9 @@
         </is>
       </c>
       <c r="D94" s="49" t="n"/>
-      <c r="E94" s="197" t="n"/>
+      <c r="E94" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F94" s="210">
         <f>+D94*E94</f>
         <v/>
@@ -4579,7 +4654,9 @@
         </is>
       </c>
       <c r="D95" s="49" t="n"/>
-      <c r="E95" s="197" t="n"/>
+      <c r="E95" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F95" s="210">
         <f>+D95*E95</f>
         <v/>
@@ -4608,7 +4685,9 @@
         </is>
       </c>
       <c r="D96" s="49" t="n"/>
-      <c r="E96" s="197" t="n"/>
+      <c r="E96" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F96" s="210">
         <f>+D96*E96</f>
         <v/>
@@ -4637,7 +4716,9 @@
         </is>
       </c>
       <c r="D97" s="49" t="n"/>
-      <c r="E97" s="197" t="n"/>
+      <c r="E97" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F97" s="210">
         <f>+D97*E97</f>
         <v/>
@@ -4699,7 +4780,9 @@
         </is>
       </c>
       <c r="D99" s="49" t="n"/>
-      <c r="E99" s="197" t="n"/>
+      <c r="E99" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F99" s="210">
         <f>+D99*E99</f>
         <v/>
@@ -4728,7 +4811,9 @@
         </is>
       </c>
       <c r="D100" s="49" t="n"/>
-      <c r="E100" s="197" t="n"/>
+      <c r="E100" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F100" s="210">
         <f>+D100*E100</f>
         <v/>
@@ -4757,7 +4842,9 @@
         </is>
       </c>
       <c r="D101" s="49" t="n"/>
-      <c r="E101" s="197" t="n"/>
+      <c r="E101" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F101" s="210">
         <f>+D101*E101</f>
         <v/>
@@ -4786,7 +4873,9 @@
         </is>
       </c>
       <c r="D102" s="49" t="n"/>
-      <c r="E102" s="197" t="n"/>
+      <c r="E102" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F102" s="210">
         <f>+D102*E102</f>
         <v/>
@@ -4815,7 +4904,9 @@
         </is>
       </c>
       <c r="D103" s="49" t="n"/>
-      <c r="E103" s="197" t="n"/>
+      <c r="E103" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F103" s="210">
         <f>+D103*E103</f>
         <v/>
@@ -5011,7 +5102,9 @@
         </is>
       </c>
       <c r="D110" s="49" t="n"/>
-      <c r="E110" s="197" t="n"/>
+      <c r="E110" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F110" s="210">
         <f>+D110*E110</f>
         <v/>
@@ -5040,7 +5133,9 @@
         </is>
       </c>
       <c r="D111" s="49" t="n"/>
-      <c r="E111" s="197" t="n"/>
+      <c r="E111" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F111" s="210">
         <f>+D111*E111</f>
         <v/>
@@ -5069,7 +5164,9 @@
         </is>
       </c>
       <c r="D112" s="49" t="n"/>
-      <c r="E112" s="197" t="n"/>
+      <c r="E112" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F112" s="210">
         <f>+D112*E112</f>
         <v/>
@@ -5098,7 +5195,9 @@
         </is>
       </c>
       <c r="D113" s="49" t="n"/>
-      <c r="E113" s="197" t="n"/>
+      <c r="E113" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F113" s="210">
         <f>+D113*E113</f>
         <v/>
@@ -5160,7 +5259,9 @@
         </is>
       </c>
       <c r="D115" s="49" t="n"/>
-      <c r="E115" s="197" t="n"/>
+      <c r="E115" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F115" s="210">
         <f>+D115*E115</f>
         <v/>
@@ -5189,7 +5290,9 @@
         </is>
       </c>
       <c r="D116" s="49" t="n"/>
-      <c r="E116" s="197" t="n"/>
+      <c r="E116" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F116" s="210">
         <f>+D116*E116</f>
         <v/>
@@ -5218,7 +5321,9 @@
         </is>
       </c>
       <c r="D117" s="49" t="n"/>
-      <c r="E117" s="197" t="n"/>
+      <c r="E117" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F117" s="210">
         <f>+D117*E117</f>
         <v/>
@@ -5247,7 +5352,9 @@
         </is>
       </c>
       <c r="D118" s="49" t="n"/>
-      <c r="E118" s="197" t="n"/>
+      <c r="E118" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F118" s="210">
         <f>+D118*E118</f>
         <v/>
@@ -5276,7 +5383,9 @@
         </is>
       </c>
       <c r="D119" s="49" t="n"/>
-      <c r="E119" s="197" t="n"/>
+      <c r="E119" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F119" s="210">
         <f>+D119*E119</f>
         <v/>
@@ -5472,7 +5581,9 @@
         </is>
       </c>
       <c r="D126" s="49" t="n"/>
-      <c r="E126" s="197" t="n"/>
+      <c r="E126" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F126" s="210">
         <f>+D126*E126</f>
         <v/>
@@ -5501,7 +5612,9 @@
         </is>
       </c>
       <c r="D127" s="49" t="n"/>
-      <c r="E127" s="197" t="n"/>
+      <c r="E127" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F127" s="210">
         <f>+D127*E127</f>
         <v/>
@@ -5530,7 +5643,9 @@
         </is>
       </c>
       <c r="D128" s="49" t="n"/>
-      <c r="E128" s="197" t="n"/>
+      <c r="E128" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F128" s="210">
         <f>+D128*E128</f>
         <v/>
@@ -5559,7 +5674,9 @@
         </is>
       </c>
       <c r="D129" s="49" t="n"/>
-      <c r="E129" s="197" t="n"/>
+      <c r="E129" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F129" s="210">
         <f>+D129*E129</f>
         <v/>
@@ -5621,7 +5738,9 @@
         </is>
       </c>
       <c r="D131" s="49" t="n"/>
-      <c r="E131" s="197" t="n"/>
+      <c r="E131" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F131" s="210">
         <f>+D131*E131</f>
         <v/>
@@ -5650,7 +5769,9 @@
         </is>
       </c>
       <c r="D132" s="49" t="n"/>
-      <c r="E132" s="197" t="n"/>
+      <c r="E132" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F132" s="210">
         <f>+D132*E132</f>
         <v/>
@@ -5679,7 +5800,9 @@
         </is>
       </c>
       <c r="D133" s="49" t="n"/>
-      <c r="E133" s="197" t="n"/>
+      <c r="E133" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F133" s="210">
         <f>+D133*E133</f>
         <v/>
@@ -5708,7 +5831,9 @@
         </is>
       </c>
       <c r="D134" s="49" t="n"/>
-      <c r="E134" s="197" t="n"/>
+      <c r="E134" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F134" s="210">
         <f>+D134*E134</f>
         <v/>
@@ -5737,7 +5862,9 @@
         </is>
       </c>
       <c r="D135" s="49" t="n"/>
-      <c r="E135" s="197" t="n"/>
+      <c r="E135" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F135" s="210">
         <f>+D135*E135</f>
         <v/>
@@ -5933,7 +6060,9 @@
         </is>
       </c>
       <c r="D142" s="49" t="n"/>
-      <c r="E142" s="197" t="n"/>
+      <c r="E142" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F142" s="210">
         <f>+D142*E142</f>
         <v/>
@@ -5962,7 +6091,9 @@
         </is>
       </c>
       <c r="D143" s="49" t="n"/>
-      <c r="E143" s="197" t="n"/>
+      <c r="E143" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F143" s="210">
         <f>+D143*E143</f>
         <v/>
@@ -5991,7 +6122,9 @@
         </is>
       </c>
       <c r="D144" s="49" t="n"/>
-      <c r="E144" s="197" t="n"/>
+      <c r="E144" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F144" s="210">
         <f>+D144*E144</f>
         <v/>
@@ -6020,7 +6153,9 @@
         </is>
       </c>
       <c r="D145" s="49" t="n"/>
-      <c r="E145" s="197" t="n"/>
+      <c r="E145" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F145" s="210">
         <f>+D145*E145</f>
         <v/>
@@ -6082,7 +6217,9 @@
         </is>
       </c>
       <c r="D147" s="49" t="n"/>
-      <c r="E147" s="197" t="n"/>
+      <c r="E147" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F147" s="210">
         <f>+D147*E147</f>
         <v/>
@@ -6111,7 +6248,9 @@
         </is>
       </c>
       <c r="D148" s="49" t="n"/>
-      <c r="E148" s="197" t="n"/>
+      <c r="E148" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F148" s="210">
         <f>+D148*E148</f>
         <v/>
@@ -6140,7 +6279,9 @@
         </is>
       </c>
       <c r="D149" s="49" t="n"/>
-      <c r="E149" s="197" t="n"/>
+      <c r="E149" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F149" s="210">
         <f>+D149*E149</f>
         <v/>
@@ -6169,7 +6310,9 @@
         </is>
       </c>
       <c r="D150" s="49" t="n"/>
-      <c r="E150" s="197" t="n"/>
+      <c r="E150" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F150" s="210">
         <f>+D150*E150</f>
         <v/>
@@ -6198,7 +6341,9 @@
         </is>
       </c>
       <c r="D151" s="49" t="n"/>
-      <c r="E151" s="197" t="n"/>
+      <c r="E151" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F151" s="210">
         <f>+D151*E151</f>
         <v/>
@@ -6394,7 +6539,9 @@
         </is>
       </c>
       <c r="D158" s="49" t="n"/>
-      <c r="E158" s="197" t="n"/>
+      <c r="E158" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F158" s="210">
         <f>+D158*E158</f>
         <v/>
@@ -6423,7 +6570,9 @@
         </is>
       </c>
       <c r="D159" s="49" t="n"/>
-      <c r="E159" s="197" t="n"/>
+      <c r="E159" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F159" s="210">
         <f>+D159*E159</f>
         <v/>
@@ -6452,7 +6601,9 @@
         </is>
       </c>
       <c r="D160" s="49" t="n"/>
-      <c r="E160" s="197" t="n"/>
+      <c r="E160" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F160" s="210">
         <f>+D160*E160</f>
         <v/>
@@ -6481,7 +6632,9 @@
         </is>
       </c>
       <c r="D161" s="49" t="n"/>
-      <c r="E161" s="197" t="n"/>
+      <c r="E161" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F161" s="210">
         <f>+D161*E161</f>
         <v/>
@@ -6543,7 +6696,9 @@
         </is>
       </c>
       <c r="D163" s="49" t="n"/>
-      <c r="E163" s="197" t="n"/>
+      <c r="E163" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F163" s="210">
         <f>+D163*E163</f>
         <v/>
@@ -6572,7 +6727,9 @@
         </is>
       </c>
       <c r="D164" s="49" t="n"/>
-      <c r="E164" s="197" t="n"/>
+      <c r="E164" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F164" s="210">
         <f>+D164*E164</f>
         <v/>
@@ -6601,7 +6758,9 @@
         </is>
       </c>
       <c r="D165" s="49" t="n"/>
-      <c r="E165" s="197" t="n"/>
+      <c r="E165" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F165" s="210">
         <f>+D165*E165</f>
         <v/>
@@ -6630,7 +6789,9 @@
         </is>
       </c>
       <c r="D166" s="49" t="n"/>
-      <c r="E166" s="197" t="n"/>
+      <c r="E166" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F166" s="210">
         <f>+D166*E166</f>
         <v/>
@@ -6659,7 +6820,9 @@
         </is>
       </c>
       <c r="D167" s="49" t="n"/>
-      <c r="E167" s="197" t="n"/>
+      <c r="E167" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F167" s="210">
         <f>+D167*E167</f>
         <v/>
@@ -6855,7 +7018,9 @@
         </is>
       </c>
       <c r="D174" s="49" t="n"/>
-      <c r="E174" s="197" t="n"/>
+      <c r="E174" s="222" t="n">
+        <v>72.7273</v>
+      </c>
       <c r="F174" s="210">
         <f>+D174*E174</f>
         <v/>
@@ -6884,7 +7049,9 @@
         </is>
       </c>
       <c r="D175" s="49" t="n"/>
-      <c r="E175" s="197" t="n"/>
+      <c r="E175" s="222" t="n">
+        <v>46.7532</v>
+      </c>
       <c r="F175" s="210">
         <f>+D175*E175</f>
         <v/>
@@ -6913,7 +7080,9 @@
         </is>
       </c>
       <c r="D176" s="49" t="n"/>
-      <c r="E176" s="197" t="n"/>
+      <c r="E176" s="222" t="n">
+        <v>38.961</v>
+      </c>
       <c r="F176" s="210">
         <f>+D176*E176</f>
         <v/>
@@ -6942,7 +7111,9 @@
         </is>
       </c>
       <c r="D177" s="49" t="n"/>
-      <c r="E177" s="197" t="n"/>
+      <c r="E177" s="222" t="n">
+        <v>90.9091</v>
+      </c>
       <c r="F177" s="210">
         <f>+D177*E177</f>
         <v/>
@@ -7004,7 +7175,9 @@
         </is>
       </c>
       <c r="D179" s="49" t="n"/>
-      <c r="E179" s="197" t="n"/>
+      <c r="E179" s="222" t="n">
+        <v>57.1429</v>
+      </c>
       <c r="F179" s="210">
         <f>+D179*E179</f>
         <v/>
@@ -7033,7 +7206,9 @@
         </is>
       </c>
       <c r="D180" s="49" t="n"/>
-      <c r="E180" s="197" t="n"/>
+      <c r="E180" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F180" s="210">
         <f>+D180*E180</f>
         <v/>
@@ -7062,7 +7237,9 @@
         </is>
       </c>
       <c r="D181" s="49" t="n"/>
-      <c r="E181" s="197" t="n"/>
+      <c r="E181" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F181" s="210">
         <f>+D181*E181</f>
         <v/>
@@ -7091,7 +7268,9 @@
         </is>
       </c>
       <c r="D182" s="49" t="n"/>
-      <c r="E182" s="197" t="n"/>
+      <c r="E182" s="222" t="n">
+        <v>1.1688</v>
+      </c>
       <c r="F182" s="210">
         <f>+D182*E182</f>
         <v/>
@@ -7120,9 +7299,11 @@
         </is>
       </c>
       <c r="D183" s="221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="197" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="E183" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F183" s="205">
         <f>D183*E183</f>
         <v/>
@@ -7375,7 +7556,9 @@
       <c r="D192" s="224" t="n">
         <v>39.54</v>
       </c>
-      <c r="E192" s="197" t="n"/>
+      <c r="E192" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F192" s="205">
         <f>D192*E192</f>
         <v/>
@@ -7406,7 +7589,9 @@
       <c r="D193" s="224" t="n">
         <v>19.77</v>
       </c>
-      <c r="E193" s="197" t="n"/>
+      <c r="E193" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F193" s="205">
         <f>D193*E193</f>
         <v/>
@@ -7438,7 +7623,9 @@
       <c r="D194" s="224" t="n">
         <v>24</v>
       </c>
-      <c r="E194" s="197" t="n"/>
+      <c r="E194" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F194" s="205">
         <f>D194*E194</f>
         <v/>
@@ -7500,9 +7687,11 @@
         </is>
       </c>
       <c r="D196" s="221" t="n">
-        <v>2334</v>
-      </c>
-      <c r="E196" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E196" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F196" s="205">
         <f>D196*E196</f>
         <v/>
@@ -7617,10 +7806,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D200" s="49" t="n"/>
-      <c r="E200" s="197" t="n"/>
-      <c r="F200" s="210">
-        <f>+D200*E200</f>
+      <c r="D200" s="221" t="n">
+        <v>7780</v>
+      </c>
+      <c r="E200" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F200" s="205">
+        <f>D200*E200</f>
         <v/>
       </c>
       <c r="G200" s="47" t="inlineStr">
@@ -7786,7 +7979,9 @@
       <c r="D206" s="224" t="n">
         <v>36.46</v>
       </c>
-      <c r="E206" s="197" t="n"/>
+      <c r="E206" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F206" s="205">
         <f>D206*E206</f>
         <v/>
@@ -7817,7 +8012,9 @@
       <c r="D207" s="224" t="n">
         <v>18.23</v>
       </c>
-      <c r="E207" s="197" t="n"/>
+      <c r="E207" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F207" s="205">
         <f>D207*E207</f>
         <v/>
@@ -7848,7 +8045,9 @@
       <c r="D208" s="224" t="n">
         <v>24</v>
       </c>
-      <c r="E208" s="197" t="n"/>
+      <c r="E208" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F208" s="205">
         <f>D208*E208</f>
         <v/>
@@ -7910,9 +8109,11 @@
         </is>
       </c>
       <c r="D210" s="221" t="n">
-        <v>1029.6</v>
-      </c>
-      <c r="E210" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E210" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F210" s="205">
         <f>D210*E210</f>
         <v/>
@@ -8027,10 +8228,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D214" s="49" t="n"/>
-      <c r="E214" s="197" t="n"/>
-      <c r="F214" s="210">
-        <f>+D214*E214</f>
+      <c r="D214" s="221" t="n">
+        <v>3432</v>
+      </c>
+      <c r="E214" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F214" s="205">
+        <f>D214*E214</f>
         <v/>
       </c>
       <c r="G214" s="47" t="inlineStr">
@@ -8196,7 +8401,9 @@
       <c r="D220" s="224" t="n">
         <v>21.98</v>
       </c>
-      <c r="E220" s="197" t="n"/>
+      <c r="E220" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F220" s="205">
         <f>D220*E220</f>
         <v/>
@@ -8227,7 +8434,9 @@
       <c r="D221" s="224" t="n">
         <v>10.99</v>
       </c>
-      <c r="E221" s="197" t="n"/>
+      <c r="E221" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F221" s="205">
         <f>D221*E221</f>
         <v/>
@@ -8258,7 +8467,9 @@
       <c r="D222" s="224" t="n">
         <v>24</v>
       </c>
-      <c r="E222" s="197" t="n"/>
+      <c r="E222" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F222" s="205">
         <f>D222*E222</f>
         <v/>
@@ -8320,9 +8531,11 @@
         </is>
       </c>
       <c r="D224" s="221" t="n">
-        <v>2370.6</v>
-      </c>
-      <c r="E224" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E224" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F224" s="205">
         <f>D224*E224</f>
         <v/>
@@ -8437,10 +8650,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D228" s="49" t="n"/>
-      <c r="E228" s="197" t="n"/>
-      <c r="F228" s="210">
-        <f>+D228*E228</f>
+      <c r="D228" s="221" t="n">
+        <v>7902</v>
+      </c>
+      <c r="E228" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F228" s="205">
+        <f>D228*E228</f>
         <v/>
       </c>
       <c r="G228" s="47" t="inlineStr">
@@ -8606,7 +8823,9 @@
       <c r="D234" s="224" t="n">
         <v>32.87</v>
       </c>
-      <c r="E234" s="197" t="n"/>
+      <c r="E234" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F234" s="205">
         <f>D234*E234</f>
         <v/>
@@ -8637,7 +8856,9 @@
       <c r="D235" s="224" t="n">
         <v>16.435</v>
       </c>
-      <c r="E235" s="197" t="n"/>
+      <c r="E235" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F235" s="205">
         <f>D235*E235</f>
         <v/>
@@ -8668,7 +8889,9 @@
       <c r="D236" s="224" t="n">
         <v>24</v>
       </c>
-      <c r="E236" s="197" t="n"/>
+      <c r="E236" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F236" s="205">
         <f>D236*E236</f>
         <v/>
@@ -8730,9 +8953,11 @@
         </is>
       </c>
       <c r="D238" s="221" t="n">
-        <v>1235.4</v>
-      </c>
-      <c r="E238" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E238" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F238" s="205">
         <f>D238*E238</f>
         <v/>
@@ -8847,10 +9072,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D242" s="49" t="n"/>
-      <c r="E242" s="197" t="n"/>
-      <c r="F242" s="210">
-        <f>+D242*E242</f>
+      <c r="D242" s="221" t="n">
+        <v>4118</v>
+      </c>
+      <c r="E242" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F242" s="205">
+        <f>D242*E242</f>
         <v/>
       </c>
       <c r="G242" s="47" t="inlineStr">
@@ -9016,7 +9245,9 @@
       <c r="D248" s="224" t="n">
         <v>26.95</v>
       </c>
-      <c r="E248" s="197" t="n"/>
+      <c r="E248" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F248" s="205">
         <f>D248*E248</f>
         <v/>
@@ -9047,7 +9278,9 @@
       <c r="D249" s="224" t="n">
         <v>13.475</v>
       </c>
-      <c r="E249" s="197" t="n"/>
+      <c r="E249" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F249" s="205">
         <f>D249*E249</f>
         <v/>
@@ -9078,7 +9311,9 @@
       <c r="D250" s="224" t="n">
         <v>24</v>
       </c>
-      <c r="E250" s="197" t="n"/>
+      <c r="E250" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F250" s="205">
         <f>D250*E250</f>
         <v/>
@@ -9140,9 +9375,11 @@
         </is>
       </c>
       <c r="D252" s="221" t="n">
-        <v>1786.8</v>
-      </c>
-      <c r="E252" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E252" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F252" s="205">
         <f>D252*E252</f>
         <v/>
@@ -9257,10 +9494,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D256" s="49" t="n"/>
-      <c r="E256" s="197" t="n"/>
-      <c r="F256" s="210">
-        <f>+D256*E256</f>
+      <c r="D256" s="221" t="n">
+        <v>5956</v>
+      </c>
+      <c r="E256" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F256" s="205">
+        <f>D256*E256</f>
         <v/>
       </c>
       <c r="G256" s="47" t="inlineStr">
@@ -9426,7 +9667,9 @@
       <c r="D262" s="204" t="n">
         <v>26.71</v>
       </c>
-      <c r="E262" s="197" t="n"/>
+      <c r="E262" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F262" s="205">
         <f>D262*E262</f>
         <v/>
@@ -9457,7 +9700,9 @@
       <c r="D263" s="204" t="n">
         <v>13.355</v>
       </c>
-      <c r="E263" s="197" t="n"/>
+      <c r="E263" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F263" s="205">
         <f>D263*E263</f>
         <v/>
@@ -9488,7 +9733,9 @@
       <c r="D264" s="204" t="n">
         <v>24</v>
       </c>
-      <c r="E264" s="197" t="n"/>
+      <c r="E264" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F264" s="205">
         <f>D264*E264</f>
         <v/>
@@ -9550,9 +9797,11 @@
         </is>
       </c>
       <c r="D266" s="221" t="n">
-        <v>1908</v>
-      </c>
-      <c r="E266" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E266" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F266" s="205">
         <f>D266*E266</f>
         <v/>
@@ -9667,10 +9916,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D270" s="49" t="n"/>
-      <c r="E270" s="197" t="n"/>
-      <c r="F270" s="210">
-        <f>+D270*E270</f>
+      <c r="D270" s="221" t="n">
+        <v>6360</v>
+      </c>
+      <c r="E270" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F270" s="205">
+        <f>D270*E270</f>
         <v/>
       </c>
       <c r="G270" s="47" t="inlineStr">
@@ -9836,7 +10089,9 @@
       <c r="D276" s="204" t="n">
         <v>26.76</v>
       </c>
-      <c r="E276" s="197" t="n"/>
+      <c r="E276" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F276" s="205">
         <f>D276*E276</f>
         <v/>
@@ -9867,7 +10122,9 @@
       <c r="D277" s="204" t="n">
         <v>13.38</v>
       </c>
-      <c r="E277" s="197" t="n"/>
+      <c r="E277" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F277" s="205">
         <f>D277*E277</f>
         <v/>
@@ -9898,7 +10155,9 @@
       <c r="D278" s="204" t="n">
         <v>24</v>
       </c>
-      <c r="E278" s="197" t="n"/>
+      <c r="E278" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F278" s="205">
         <f>D278*E278</f>
         <v/>
@@ -9960,9 +10219,11 @@
         </is>
       </c>
       <c r="D280" s="221" t="n">
-        <v>2206.2</v>
-      </c>
-      <c r="E280" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E280" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F280" s="205">
         <f>D280*E280</f>
         <v/>
@@ -10077,10 +10338,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D284" s="49" t="n"/>
-      <c r="E284" s="197" t="n"/>
-      <c r="F284" s="210">
-        <f>+D284*E284</f>
+      <c r="D284" s="221" t="n">
+        <v>7354</v>
+      </c>
+      <c r="E284" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F284" s="205">
+        <f>D284*E284</f>
         <v/>
       </c>
       <c r="G284" s="47" t="inlineStr">
@@ -10246,7 +10511,9 @@
       <c r="D290" s="204" t="n">
         <v>35.948</v>
       </c>
-      <c r="E290" s="197" t="n"/>
+      <c r="E290" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F290" s="205">
         <f>D290*E290</f>
         <v/>
@@ -10277,7 +10544,9 @@
       <c r="D291" s="204" t="n">
         <v>17.974</v>
       </c>
-      <c r="E291" s="197" t="n"/>
+      <c r="E291" s="222" t="n">
+        <v>5.4545</v>
+      </c>
       <c r="F291" s="205">
         <f>D291*E291</f>
         <v/>
@@ -10308,7 +10577,9 @@
       <c r="D292" s="204" t="n">
         <v>24</v>
       </c>
-      <c r="E292" s="197" t="n"/>
+      <c r="E292" s="222" t="n">
+        <v>4.6753</v>
+      </c>
       <c r="F292" s="205">
         <f>D292*E292</f>
         <v/>
@@ -10370,9 +10641,11 @@
         </is>
       </c>
       <c r="D294" s="221" t="n">
-        <v>1854.6</v>
-      </c>
-      <c r="E294" s="197" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E294" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F294" s="205">
         <f>D294*E294</f>
         <v/>
@@ -10487,10 +10760,14 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D298" s="49" t="n"/>
-      <c r="E298" s="197" t="n"/>
-      <c r="F298" s="210">
-        <f>+D298*E298</f>
+      <c r="D298" s="221" t="n">
+        <v>6182</v>
+      </c>
+      <c r="E298" s="222" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="F298" s="205">
+        <f>D298*E298</f>
         <v/>
       </c>
       <c r="G298" s="47" t="inlineStr">
@@ -10685,7 +10962,9 @@
       <c r="D304" s="204" t="n">
         <v>2000</v>
       </c>
-      <c r="E304" s="197" t="n"/>
+      <c r="E304" s="222" t="n">
+        <v>1.4286</v>
+      </c>
       <c r="F304" s="229">
         <f>D304*E304</f>
         <v/>
@@ -10854,7 +11133,9 @@
       <c r="D311" s="224" t="n">
         <v>317.61</v>
       </c>
-      <c r="E311" s="197" t="n"/>
+      <c r="E311" s="222" t="n">
+        <v>0.2208</v>
+      </c>
       <c r="F311" s="205">
         <f>D311*E311</f>
         <v/>
@@ -10890,7 +11171,9 @@
       <c r="D312" s="224" t="n">
         <v>66.6981</v>
       </c>
-      <c r="E312" s="197" t="n"/>
+      <c r="E312" s="222" t="n">
+        <v>0.4675</v>
+      </c>
       <c r="F312" s="205">
         <f>D312*E312</f>
         <v/>
@@ -10922,7 +11205,9 @@
       <c r="D313" s="224" t="n">
         <v>317.61</v>
       </c>
-      <c r="E313" s="197" t="n"/>
+      <c r="E313" s="222" t="n">
+        <v>0.9091</v>
+      </c>
       <c r="F313" s="205">
         <f>D313*E313</f>
         <v/>
@@ -10954,7 +11239,9 @@
       <c r="D314" s="224" t="n">
         <v>82.57859999999999</v>
       </c>
-      <c r="E314" s="197" t="n"/>
+      <c r="E314" s="222" t="n">
+        <v>0.3117</v>
+      </c>
       <c r="F314" s="205">
         <f>D314*E314</f>
         <v/>
@@ -10986,7 +11273,9 @@
       <c r="D315" s="224" t="n">
         <v>343.0188</v>
       </c>
-      <c r="E315" s="197" t="n"/>
+      <c r="E315" s="222" t="n">
+        <v>0.7272999999999999</v>
+      </c>
       <c r="F315" s="205">
         <f>D315*E315</f>
         <v/>
@@ -11018,7 +11307,9 @@
       <c r="D316" s="224" t="n">
         <v>317.61</v>
       </c>
-      <c r="E316" s="197" t="n"/>
+      <c r="E316" s="222" t="n">
+        <v>0.0649</v>
+      </c>
       <c r="F316" s="205">
         <f>D316*E316</f>
         <v/>
@@ -11050,7 +11341,9 @@
       <c r="D317" s="224" t="n">
         <v>317.61</v>
       </c>
-      <c r="E317" s="197" t="n"/>
+      <c r="E317" s="222" t="n">
+        <v>0.1169</v>
+      </c>
       <c r="F317" s="205">
         <f>D317*E317</f>
         <v/>
@@ -11082,7 +11375,9 @@
       <c r="D318" s="224" t="n">
         <v>317.61</v>
       </c>
-      <c r="E318" s="197" t="n"/>
+      <c r="E318" s="222" t="n">
+        <v>0.0312</v>
+      </c>
       <c r="F318" s="205">
         <f>D318*E318</f>
         <v/>
@@ -11114,7 +11409,9 @@
       <c r="D319" s="224" t="n">
         <v>276.3207</v>
       </c>
-      <c r="E319" s="197" t="n"/>
+      <c r="E319" s="222" t="n">
+        <v>0.5714</v>
+      </c>
       <c r="F319" s="205">
         <f>D319*E319</f>
         <v/>
@@ -11146,7 +11443,9 @@
       <c r="D320" s="224" t="n">
         <v>90.7457</v>
       </c>
-      <c r="E320" s="197" t="n"/>
+      <c r="E320" s="222" t="n">
+        <v>2.2078</v>
+      </c>
       <c r="F320" s="205">
         <f>D320*E320</f>
         <v/>
@@ -11178,7 +11477,9 @@
       <c r="D321" s="224" t="n">
         <v>60</v>
       </c>
-      <c r="E321" s="197" t="n"/>
+      <c r="E321" s="222" t="n">
+        <v>0.3117</v>
+      </c>
       <c r="F321" s="205">
         <f>D321*E321</f>
         <v/>
@@ -11210,7 +11511,9 @@
       <c r="D322" s="224" t="n">
         <v>40</v>
       </c>
-      <c r="E322" s="197" t="n"/>
+      <c r="E322" s="222" t="n">
+        <v>0.9091</v>
+      </c>
       <c r="F322" s="205">
         <f>D322*E322</f>
         <v/>
@@ -11241,7 +11544,9 @@
       <c r="D323" s="224" t="n">
         <v>20</v>
       </c>
-      <c r="E323" s="197" t="n"/>
+      <c r="E323" s="222" t="n">
+        <v>0.5714</v>
+      </c>
       <c r="F323" s="205">
         <f>D323*E323</f>
         <v/>
@@ -12300,7 +12605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H70"/>
+  <dimension ref="A2:I72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.5"/>
   <cols>
     <col width="6.265625" customWidth="1" style="9" min="1" max="1"/>
@@ -12438,9 +12743,15 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="126" t="n"/>
+      <c r="D10" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" s="237" t="n">
+        <v>100</v>
+      </c>
       <c r="G10" s="139">
         <f>+D10*E10*F10</f>
         <v/>
@@ -12448,6 +12759,11 @@
       <c r="H10" s="132" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
+        </is>
+      </c>
+      <c r="I10" s="238" t="inlineStr">
+        <is>
+          <t>REF: Servicio vigilancia 24h externalizado</t>
         </is>
       </c>
     </row>
@@ -12498,16 +12814,27 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="126" t="n"/>
+      <c r="D13" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="237" t="n">
+        <v>150</v>
+      </c>
       <c r="G13" s="139">
         <f>+D13*E13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="236" t="inlineStr">
+      <c r="H13" s="239" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
+        </is>
+      </c>
+      <c r="I13" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Administrador (~$5.8M CLP/mes)</t>
         </is>
       </c>
     </row>
@@ -12527,14 +12854,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="126" t="n"/>
+      <c r="D14" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" s="237" t="n">
+        <v>120</v>
+      </c>
       <c r="G14" s="139">
         <f>+D14*E14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="237" t="n"/>
+      <c r="H14" s="240" t="n"/>
+      <c r="I14" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Jefe de Terreno (~$4.6M CLP/mes)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -12552,14 +12890,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="126" t="n"/>
+      <c r="D15" s="236" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" s="237" t="n">
+        <v>90</v>
+      </c>
       <c r="G15" s="139">
         <f>+D15*E15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="237" t="n"/>
+      <c r="H15" s="240" t="n"/>
+      <c r="I15" s="238" t="inlineStr">
+        <is>
+          <t>REF: 2 Supervisores en turnos</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -12577,14 +12926,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="126" t="n"/>
+      <c r="D16" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="237" t="n">
+        <v>80</v>
+      </c>
       <c r="G16" s="139">
         <f>+D16*E16*F16</f>
         <v/>
       </c>
-      <c r="H16" s="237" t="n"/>
+      <c r="H16" s="240" t="n"/>
+      <c r="I16" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Encargado Prevencion Riesgos</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -12602,14 +12962,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="126" t="n"/>
+      <c r="D17" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" s="237" t="n">
+        <v>70</v>
+      </c>
       <c r="G17" s="139">
         <f>+D17*E17*F17</f>
         <v/>
       </c>
-      <c r="H17" s="237" t="n"/>
+      <c r="H17" s="240" t="n"/>
+      <c r="I17" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Encargado Medio Ambiente</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
@@ -12627,14 +12998,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="126" t="n"/>
+      <c r="D18" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" s="237" t="n">
+        <v>80</v>
+      </c>
       <c r="G18" s="139">
         <f>+D18*E18*F18</f>
         <v/>
       </c>
-      <c r="H18" s="237" t="n"/>
+      <c r="H18" s="240" t="n"/>
+      <c r="I18" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Topografo</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
@@ -12652,14 +13034,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="126" t="n"/>
+      <c r="D19" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" s="237" t="n">
+        <v>55</v>
+      </c>
       <c r="G19" s="139">
         <f>+D19*E19*F19</f>
         <v/>
       </c>
-      <c r="H19" s="237" t="n"/>
+      <c r="H19" s="240" t="n"/>
+      <c r="I19" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Trazador</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -12677,14 +13070,25 @@
           <t>mes</t>
         </is>
       </c>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="126" t="n"/>
+      <c r="D20" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" s="237" t="n">
+        <v>50</v>
+      </c>
       <c r="G20" s="139">
         <f>+D20*E20*F20</f>
         <v/>
       </c>
-      <c r="H20" s="237" t="n"/>
+      <c r="H20" s="240" t="n"/>
+      <c r="I20" s="238" t="inlineStr">
+        <is>
+          <t>REF: 1 Bodeguero</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
@@ -12702,7 +13106,7 @@
       <c r="E21" s="20" t="n"/>
       <c r="F21" s="22" t="n"/>
       <c r="G21" s="22" t="n"/>
-      <c r="H21" s="238" t="n"/>
+      <c r="H21" s="241" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="n"/>
@@ -12751,16 +13155,27 @@
           <t>und</t>
         </is>
       </c>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="126" t="n"/>
+      <c r="D24" s="236" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="237" t="n">
+        <v>35</v>
+      </c>
       <c r="G24" s="139">
         <f>+D24*E24*F24</f>
         <v/>
       </c>
-      <c r="H24" s="236" t="inlineStr">
+      <c r="H24" s="239" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
+        </is>
+      </c>
+      <c r="I24" s="238" t="inlineStr">
+        <is>
+          <t>REF: 3 Camionetas operativas</t>
         </is>
       </c>
     </row>
@@ -12780,14 +13195,25 @@
           <t>und</t>
         </is>
       </c>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="126" t="n"/>
+      <c r="D25" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" s="237" t="n">
+        <v>50</v>
+      </c>
       <c r="G25" s="139">
         <f>+D25*E25*F25</f>
         <v/>
       </c>
-      <c r="H25" s="237" t="n"/>
+      <c r="H25" s="240" t="n"/>
+      <c r="I25" s="238" t="inlineStr">
+        <is>
+          <t>REF: Fletes mensuales</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
@@ -12805,14 +13231,25 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="126" t="n"/>
+      <c r="D26" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="237" t="n">
+        <v>30</v>
+      </c>
       <c r="G26" s="139">
         <f>+D26*E26*F26</f>
         <v/>
       </c>
-      <c r="H26" s="237" t="n"/>
+      <c r="H26" s="240" t="n"/>
+      <c r="I26" s="238" t="inlineStr">
+        <is>
+          <t>REF: Arriendo andamios</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
@@ -12830,14 +13267,25 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="126" t="n"/>
+      <c r="D27" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" s="237" t="n">
+        <v>80</v>
+      </c>
       <c r="G27" s="139">
         <f>+D27*E27*F27</f>
         <v/>
       </c>
-      <c r="H27" s="238" t="n"/>
+      <c r="H27" s="241" t="n"/>
+      <c r="I27" s="238" t="inlineStr">
+        <is>
+          <t>REF: Equipos menores (grupos, compresor)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="35" t="n"/>
@@ -12886,16 +13334,27 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="126" t="n"/>
+      <c r="D30" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" s="237" t="n">
+        <v>50</v>
+      </c>
       <c r="G30" s="139">
         <f>+D30*E30*F30</f>
         <v/>
       </c>
-      <c r="H30" s="236" t="inlineStr">
+      <c r="H30" s="239" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
+        </is>
+      </c>
+      <c r="I30" s="238" t="inlineStr">
+        <is>
+          <t>REF: Disposicion residuos sólidos</t>
         </is>
       </c>
     </row>
@@ -12915,14 +13374,25 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="126" t="n"/>
+      <c r="D31" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="236" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" s="237" t="n">
+        <v>120</v>
+      </c>
       <c r="G31" s="139">
         <f>+D31*E31*F31</f>
         <v/>
       </c>
-      <c r="H31" s="238" t="n"/>
+      <c r="H31" s="241" t="n"/>
+      <c r="I31" s="238" t="inlineStr">
+        <is>
+          <t>REF: Disposicion excedentes excavación</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="n"/>
@@ -12970,7 +13440,7 @@
         <f>+D34*E34*F34</f>
         <v/>
       </c>
-      <c r="H34" s="239" t="inlineStr">
+      <c r="H34" s="242" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
         </is>
@@ -12991,7 +13461,7 @@
         <f>+D35*E35*F35</f>
         <v/>
       </c>
-      <c r="H35" s="237" t="n"/>
+      <c r="H35" s="240" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
@@ -13008,7 +13478,7 @@
         <f>+D36*E36*F36</f>
         <v/>
       </c>
-      <c r="H36" s="240" t="n"/>
+      <c r="H36" s="243" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="23" t="n"/>
@@ -13247,9 +13717,15 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D47" s="20" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="126" t="n"/>
+      <c r="D47" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="237" t="n">
+        <v>3200</v>
+      </c>
       <c r="G47" s="139">
         <f>+D47*E47*F47</f>
         <v/>
@@ -13259,6 +13735,11 @@
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
         </is>
       </c>
+      <c r="I47" s="238" t="inlineStr">
+        <is>
+          <t>REF: Aporte oficina central ~4.4% directo</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
@@ -13276,14 +13757,25 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D48" s="20" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="126" t="n"/>
+      <c r="D48" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="237" t="n">
+        <v>1800</v>
+      </c>
       <c r="G48" s="139">
         <f>+D48*E48*F48</f>
         <v/>
       </c>
       <c r="H48" s="207" t="n"/>
+      <c r="I48" s="238" t="inlineStr">
+        <is>
+          <t>REF: Gastos financieros ~2.5% directo</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
@@ -13301,14 +13793,25 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="126" t="n"/>
+      <c r="D49" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="237" t="n">
+        <v>1200</v>
+      </c>
       <c r="G49" s="139">
         <f>+D49*E49*F49</f>
         <v/>
       </c>
       <c r="H49" s="207" t="n"/>
+      <c r="I49" s="238" t="inlineStr">
+        <is>
+          <t>REF: Boletas garantia + seguros ~1.6% directo</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
@@ -13375,9 +13878,15 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="126" t="n"/>
+      <c r="D53" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="237" t="n">
+        <v>8000</v>
+      </c>
       <c r="G53" s="139">
         <f>+D53*E53*F53</f>
         <v/>
@@ -13385,6 +13894,11 @@
       <c r="H53" s="132" t="inlineStr">
         <is>
           <t>5% con el cumplimiento de Condiciones contractuales, 85% por avance proporcional y 10% con la recepción provisional de la obra</t>
+        </is>
+      </c>
+      <c r="I53" s="238" t="inlineStr">
+        <is>
+          <t>REF: Utilidad contratista ~11% directo</t>
         </is>
       </c>
     </row>
@@ -13545,11 +14059,19 @@
       <c r="B70" s="12" t="n"/>
       <c r="C70" s="156" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" s="244" t="inlineStr">
+        <is>
+          <t>⚠ Valores en salmón (cantidades, tiempos, precios) son REFERENCIALES para plazo 24 meses. Contratista debe ajustar a su estructura organizacional y plazo real.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="H30:H31"/>
     <mergeCell ref="H13:H21"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="H34:H36"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
@@ -13588,1718 +14110,1718 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="241" t="inlineStr">
+      <c r="A1" s="245" t="inlineStr">
         <is>
           <t>ANÁLISIS DE PRECIOS — TÚNEL LAT VITACURA-PROVIDENCIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>UF referencial: 38,500 CLP (mayo 2026) | Generado: 2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>⚠ SUPUESTO: cantidades sección 5 calculadas para 1 túnel Ø2.21m por tramo. Si la licitación requiere 2 túneles paralelos, multiplicar cantidades 5.x por 2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="244" t="inlineStr">
+      <c r="A5" s="248" t="inlineStr">
         <is>
           <t>1. CUBICACIÓN REALIZADA (cantidades pre-llenadas en hoja A)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B6" s="245" t="inlineStr">
+      <c r="B6" s="249" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="C6" s="245" t="inlineStr">
+      <c r="C6" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D6" s="245" t="inlineStr">
+      <c r="D6" s="249" t="inlineStr">
         <is>
           <t>Ítems licitación</t>
         </is>
       </c>
-      <c r="E6" s="245" t="inlineStr">
+      <c r="E6" s="249" t="inlineStr">
         <is>
           <t>UF est. medio</t>
         </is>
       </c>
-      <c r="F6" s="245" t="inlineStr">
+      <c r="F6" s="249" t="inlineStr">
         <is>
           <t>Fuente / Cómo se calculó</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="246" t="inlineStr">
+      <c r="A7" s="250" t="inlineStr">
         <is>
           <t>Excavación pique</t>
         </is>
       </c>
-      <c r="B7" s="246" t="n">
+      <c r="B7" s="250" t="n">
         <v>1770.35</v>
       </c>
-      <c r="C7" s="246" t="inlineStr">
+      <c r="C7" s="250" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="D7" s="246" t="inlineStr">
+      <c r="D7" s="250" t="inlineStr">
         <is>
           <t>4.1.1</t>
         </is>
       </c>
-      <c r="E7" s="246" t="inlineStr">
+      <c r="E7" s="250" t="inlineStr">
         <is>
           <t>4,868 UF</t>
         </is>
       </c>
-      <c r="F7" s="246" t="inlineStr">
+      <c r="F7" s="250" t="inlineStr">
         <is>
           <t>área(12.57m²) × profundidad(20m)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="246" t="inlineStr">
+      <c r="A8" s="250" t="inlineStr">
         <is>
           <t>Retiro excavación</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>1770.35</v>
       </c>
-      <c r="C8" s="246" t="inlineStr">
+      <c r="C8" s="250" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="D8" s="246" t="inlineStr">
+      <c r="D8" s="250" t="inlineStr">
         <is>
           <t>4.1.2</t>
         </is>
       </c>
-      <c r="E8" s="246" t="inlineStr">
+      <c r="E8" s="250" t="inlineStr">
         <is>
           <t>2,036 UF</t>
         </is>
       </c>
-      <c r="F8" s="246" t="inlineStr">
+      <c r="F8" s="250" t="inlineStr">
         <is>
           <t>igual excavación — flete botadero</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="246" t="inlineStr">
+      <c r="A9" s="250" t="inlineStr">
         <is>
           <t>Montaje liner pique</t>
         </is>
       </c>
-      <c r="B9" s="246" t="n">
+      <c r="B9" s="250" t="n">
         <v>140.88</v>
       </c>
-      <c r="C9" s="246" t="inlineStr">
+      <c r="C9" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D9" s="246" t="inlineStr">
+      <c r="D9" s="250" t="inlineStr">
         <is>
           <t>4.1.3</t>
         </is>
       </c>
-      <c r="E9" s="246" t="inlineStr">
+      <c r="E9" s="250" t="inlineStr">
         <is>
           <t>845 UF</t>
         </is>
       </c>
-      <c r="F9" s="246" t="inlineStr">
+      <c r="F9" s="250" t="inlineStr">
         <is>
           <t>profundidad pique (20m = 20 anillos)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="246" t="inlineStr">
+      <c r="A10" s="250" t="inlineStr">
         <is>
           <t>Montaje escalas+plataformas</t>
         </is>
       </c>
-      <c r="B10" s="246" t="n">
+      <c r="B10" s="250" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="246" t="inlineStr">
+      <c r="C10" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="D10" s="246" t="inlineStr">
+      <c r="D10" s="250" t="inlineStr">
         <is>
           <t>4.1.8</t>
         </is>
       </c>
-      <c r="E10" s="246" t="inlineStr">
+      <c r="E10" s="250" t="inlineStr">
         <is>
           <t>810 UF</t>
         </is>
       </c>
-      <c r="F10" s="246" t="inlineStr">
+      <c r="F10" s="250" t="inlineStr">
         <is>
           <t>1 gl por pique (STM aporta estructuras)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="246" t="inlineStr">
+      <c r="A11" s="250" t="inlineStr">
         <is>
           <t>Brocal definitivo</t>
         </is>
       </c>
-      <c r="B11" s="246" t="n">
+      <c r="B11" s="250" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="246" t="inlineStr">
+      <c r="C11" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="D11" s="246" t="inlineStr">
+      <c r="D11" s="250" t="inlineStr">
         <is>
           <t>4.1.15</t>
         </is>
       </c>
-      <c r="E11" s="246" t="inlineStr">
+      <c r="E11" s="250" t="inlineStr">
         <is>
           <t>1,035 UF</t>
         </is>
       </c>
-      <c r="F11" s="246" t="inlineStr">
+      <c r="F11" s="250" t="inlineStr">
         <is>
           <t>1 gl por pique</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="246" t="inlineStr">
+      <c r="A12" s="250" t="inlineStr">
         <is>
           <t>Excavación túnel</t>
         </is>
       </c>
-      <c r="B12" s="246" t="n">
+      <c r="B12" s="250" t="n">
         <v>9414.219999999999</v>
       </c>
-      <c r="C12" s="246" t="inlineStr">
+      <c r="C12" s="250" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="D12" s="246" t="inlineStr">
+      <c r="D12" s="250" t="inlineStr">
         <is>
           <t>5.1-5.8</t>
         </is>
       </c>
-      <c r="E12" s="246" t="inlineStr">
+      <c r="E12" s="250" t="inlineStr">
         <is>
           <t>47,071 UF</t>
         </is>
       </c>
-      <c r="F12" s="246" t="inlineStr">
+      <c r="F12" s="250" t="inlineStr">
         <is>
           <t>área(3.84m²) × longitud / 8 tramos</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="246" t="inlineStr">
+      <c r="A13" s="250" t="inlineStr">
         <is>
           <t>Montaje liner túnel Ø2.21m</t>
         </is>
       </c>
-      <c r="B13" s="246" t="n">
+      <c r="B13" s="250" t="n">
         <v>2454.2</v>
       </c>
-      <c r="C13" s="246" t="inlineStr">
+      <c r="C13" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D13" s="246" t="inlineStr">
+      <c r="D13" s="250" t="inlineStr">
         <is>
           <t>5.1-5.8</t>
         </is>
       </c>
-      <c r="E13" s="246" t="inlineStr">
+      <c r="E13" s="250" t="inlineStr">
         <is>
           <t>11,657 UF</t>
         </is>
       </c>
-      <c r="F13" s="246" t="inlineStr">
+      <c r="F13" s="250" t="inlineStr">
         <is>
           <t>longitud tunel / 8 tramos</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="246" t="inlineStr">
+      <c r="A14" s="250" t="inlineStr">
         <is>
           <t>Radier túnel H30</t>
         </is>
       </c>
-      <c r="B14" s="246" t="n">
+      <c r="B14" s="250" t="n">
         <v>813.5700000000001</v>
       </c>
-      <c r="C14" s="246" t="inlineStr">
+      <c r="C14" s="250" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="D14" s="246" t="inlineStr">
+      <c r="D14" s="250" t="inlineStr">
         <is>
           <t>5.1-5.8</t>
         </is>
       </c>
-      <c r="E14" s="246" t="inlineStr">
+      <c r="E14" s="250" t="inlineStr">
         <is>
           <t>6,915 UF</t>
         </is>
       </c>
-      <c r="F14" s="246" t="inlineStr">
+      <c r="F14" s="250" t="inlineStr">
         <is>
           <t>área × espesor(0.15m)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="244" t="inlineStr">
+      <c r="A16" s="248" t="inlineStr">
         <is>
           <t>2. NO CUBICADO — Requiere estudio específico o suma alzada del contratista</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="245" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>Ítem licitación</t>
         </is>
       </c>
-      <c r="B17" s="245" t="inlineStr">
+      <c r="B17" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C17" s="245" t="inlineStr">
+      <c r="C17" s="249" t="inlineStr">
         <is>
           <t>Razón / Recomendación</t>
         </is>
       </c>
-      <c r="D17" s="247" t="n"/>
-      <c r="E17" s="247" t="n"/>
-      <c r="F17" s="248" t="n"/>
+      <c r="D17" s="251" t="n"/>
+      <c r="E17" s="251" t="n"/>
+      <c r="F17" s="252" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>4.x.10  Shotcrete</t>
         </is>
       </c>
-      <c r="B18" s="249" t="inlineStr">
+      <c r="B18" s="253" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C18" s="250" t="inlineStr">
+      <c r="C18" s="254" t="inlineStr">
         <is>
           <t>Depende de clasificación RMR del terreno (geotecnia)</t>
         </is>
       </c>
-      <c r="D18" s="247" t="n"/>
-      <c r="E18" s="247" t="n"/>
-      <c r="F18" s="248" t="n"/>
+      <c r="D18" s="251" t="n"/>
+      <c r="E18" s="251" t="n"/>
+      <c r="F18" s="252" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="249" t="inlineStr">
+      <c r="A19" s="253" t="inlineStr">
         <is>
           <t>4.x.11  Malla</t>
         </is>
       </c>
-      <c r="B19" s="249" t="inlineStr">
+      <c r="B19" s="253" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C19" s="250" t="inlineStr">
+      <c r="C19" s="254" t="inlineStr">
         <is>
           <t>Diseño geotécnico — varía según tipo de suelo</t>
         </is>
       </c>
-      <c r="D19" s="247" t="n"/>
-      <c r="E19" s="247" t="n"/>
-      <c r="F19" s="248" t="n"/>
+      <c r="D19" s="251" t="n"/>
+      <c r="E19" s="251" t="n"/>
+      <c r="F19" s="252" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="249" t="inlineStr">
+      <c r="A20" s="253" t="inlineStr">
         <is>
           <t>4.x.12  Pernos de convergencia</t>
         </is>
       </c>
-      <c r="B20" s="249" t="inlineStr">
+      <c r="B20" s="253" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
-      <c r="C20" s="250" t="inlineStr">
+      <c r="C20" s="254" t="inlineStr">
         <is>
           <t>Análisis convergencia-confinamiento requerido</t>
         </is>
       </c>
-      <c r="D20" s="247" t="n"/>
-      <c r="E20" s="247" t="n"/>
-      <c r="F20" s="248" t="n"/>
+      <c r="D20" s="251" t="n"/>
+      <c r="E20" s="251" t="n"/>
+      <c r="F20" s="252" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="249" t="inlineStr">
+      <c r="A21" s="253" t="inlineStr">
         <is>
           <t>4.x.4   Refuerzo Losa Anillo Fondo</t>
         </is>
       </c>
-      <c r="B21" s="249" t="inlineStr">
+      <c r="B21" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C21" s="250" t="inlineStr">
+      <c r="C21" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D21" s="247" t="n"/>
-      <c r="E21" s="247" t="n"/>
-      <c r="F21" s="248" t="n"/>
+      <c r="D21" s="251" t="n"/>
+      <c r="E21" s="251" t="n"/>
+      <c r="F21" s="252" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="249" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>4.x.5   Construcción Dren</t>
         </is>
       </c>
-      <c r="B22" s="249" t="inlineStr">
+      <c r="B22" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C22" s="250" t="inlineStr">
+      <c r="C22" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D22" s="247" t="n"/>
-      <c r="E22" s="247" t="n"/>
-      <c r="F22" s="248" t="n"/>
+      <c r="D22" s="251" t="n"/>
+      <c r="E22" s="251" t="n"/>
+      <c r="F22" s="252" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="249" t="inlineStr">
+      <c r="A23" s="253" t="inlineStr">
         <is>
           <t>4.x.6   Terminaciones</t>
         </is>
       </c>
-      <c r="B23" s="249" t="inlineStr">
+      <c r="B23" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C23" s="250" t="inlineStr">
+      <c r="C23" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D23" s="247" t="n"/>
-      <c r="E23" s="247" t="n"/>
-      <c r="F23" s="248" t="n"/>
+      <c r="D23" s="251" t="n"/>
+      <c r="E23" s="251" t="n"/>
+      <c r="F23" s="252" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="249" t="inlineStr">
+      <c r="A24" s="253" t="inlineStr">
         <is>
           <t>4.x.7   Cobertura pique</t>
         </is>
       </c>
-      <c r="B24" s="249" t="inlineStr">
+      <c r="B24" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C24" s="250" t="inlineStr">
+      <c r="C24" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D24" s="247" t="n"/>
-      <c r="E24" s="247" t="n"/>
-      <c r="F24" s="248" t="n"/>
+      <c r="D24" s="251" t="n"/>
+      <c r="E24" s="251" t="n"/>
+      <c r="F24" s="252" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="249" t="inlineStr">
+      <c r="A25" s="253" t="inlineStr">
         <is>
           <t>4.x.9   Refuerzo apertura</t>
         </is>
       </c>
-      <c r="B25" s="249" t="inlineStr">
+      <c r="B25" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C25" s="250" t="inlineStr">
+      <c r="C25" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D25" s="247" t="n"/>
-      <c r="E25" s="247" t="n"/>
-      <c r="F25" s="248" t="n"/>
+      <c r="D25" s="251" t="n"/>
+      <c r="E25" s="251" t="n"/>
+      <c r="F25" s="252" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="249" t="inlineStr">
+      <c r="A26" s="253" t="inlineStr">
         <is>
           <t>4.x.14  Brocal temporal</t>
         </is>
       </c>
-      <c r="B26" s="249" t="inlineStr">
+      <c r="B26" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C26" s="250" t="inlineStr">
+      <c r="C26" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — cotización directa contratista</t>
         </is>
       </c>
-      <c r="D26" s="247" t="n"/>
-      <c r="E26" s="247" t="n"/>
-      <c r="F26" s="248" t="n"/>
+      <c r="D26" s="251" t="n"/>
+      <c r="E26" s="251" t="n"/>
+      <c r="F26" s="252" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="249" t="inlineStr">
+      <c r="A27" s="253" t="inlineStr">
         <is>
           <t>Sec. 2  Liner pique Ø4m + liner túnel Ø2.21m</t>
         </is>
       </c>
-      <c r="B27" s="249" t="inlineStr">
+      <c r="B27" s="253" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="250" t="inlineStr">
+      <c r="C27" s="254" t="inlineStr">
         <is>
           <t>Aporte STM: mandante suministra el material liner, contratista instala (ítems 4.x.3, 5.x.3)</t>
         </is>
       </c>
-      <c r="D27" s="247" t="n"/>
-      <c r="E27" s="247" t="n"/>
-      <c r="F27" s="248" t="n"/>
+      <c r="D27" s="251" t="n"/>
+      <c r="E27" s="251" t="n"/>
+      <c r="F27" s="252" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="249" t="inlineStr">
+      <c r="A28" s="253" t="inlineStr">
         <is>
           <t>Sec. 2  Escalas y plataformas (estructura)</t>
         </is>
       </c>
-      <c r="B28" s="249" t="inlineStr">
+      <c r="B28" s="253" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C28" s="250" t="inlineStr">
+      <c r="C28" s="254" t="inlineStr">
         <is>
           <t>Aporte STM: mandante suministra estructura, contratista monta (ítem 4.x.8)</t>
         </is>
       </c>
-      <c r="D28" s="247" t="n"/>
-      <c r="E28" s="247" t="n"/>
-      <c r="F28" s="248" t="n"/>
+      <c r="D28" s="251" t="n"/>
+      <c r="E28" s="251" t="n"/>
+      <c r="F28" s="252" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="249" t="inlineStr">
+      <c r="A29" s="253" t="inlineStr">
         <is>
           <t>Sec. 2  Extractor Soler-Palau TGT/6-1409 (37kW)</t>
         </is>
       </c>
-      <c r="B29" s="249" t="inlineStr">
+      <c r="B29" s="253" t="inlineStr">
         <is>
           <t>2 un</t>
         </is>
       </c>
-      <c r="C29" s="250" t="inlineStr">
+      <c r="C29" s="254" t="inlineStr">
         <is>
           <t>Aporte STM: 2 extractores Ø1410mm en bocas P1 y P9. 132.000 m³/h, 200 Pa. Contratista instala. Fuente: STM38110 §3.1 + §3.14</t>
         </is>
       </c>
-      <c r="D29" s="247" t="n"/>
-      <c r="E29" s="247" t="n"/>
-      <c r="F29" s="248" t="n"/>
+      <c r="D29" s="251" t="n"/>
+      <c r="E29" s="251" t="n"/>
+      <c r="F29" s="252" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="249" t="inlineStr">
+      <c r="A30" s="253" t="inlineStr">
         <is>
           <t>Sec. 2  Jet Fan S&amp;P TJHT2/4-315-CN (0.8kW)</t>
         </is>
       </c>
-      <c r="B30" s="249" t="inlineStr">
+      <c r="B30" s="253" t="inlineStr">
         <is>
           <t>23 un</t>
         </is>
       </c>
-      <c r="C30" s="250" t="inlineStr">
+      <c r="C30" s="254" t="inlineStr">
         <is>
           <t>Aporte STM: 23 ventiladores en tunel, 24N, 4.500 m³/h, Ø0.425m. Fan1 DM+70m a Fan23 DM+2380m, cada 105m. Fuente: STM38109 §4.5 Tabla 4.2 REV.E 28-01-2026</t>
         </is>
       </c>
-      <c r="D30" s="247" t="n"/>
-      <c r="E30" s="247" t="n"/>
-      <c r="F30" s="248" t="n"/>
+      <c r="D30" s="251" t="n"/>
+      <c r="E30" s="251" t="n"/>
+      <c r="F30" s="252" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="249" t="inlineStr">
+      <c r="A31" s="253" t="inlineStr">
         <is>
           <t>Sec. 1  Actividades Previas y Coordinación</t>
         </is>
       </c>
-      <c r="B31" s="249" t="inlineStr">
+      <c r="B31" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C31" s="250" t="inlineStr">
+      <c r="C31" s="254" t="inlineStr">
         <is>
           <t>Suma alzada — depende de empresa</t>
         </is>
       </c>
-      <c r="D31" s="247" t="n"/>
-      <c r="E31" s="247" t="n"/>
-      <c r="F31" s="248" t="n"/>
+      <c r="D31" s="251" t="n"/>
+      <c r="E31" s="251" t="n"/>
+      <c r="F31" s="252" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="249" t="inlineStr">
+      <c r="A32" s="253" t="inlineStr">
         <is>
           <t>Sec. 3  Instalación de Faenas</t>
         </is>
       </c>
-      <c r="B32" s="249" t="inlineStr">
+      <c r="B32" s="253" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C32" s="250" t="inlineStr">
+      <c r="C32" s="254" t="inlineStr">
         <is>
           <t>Suma alzada. IF SS Vitacura (STM-IF-20251009): 3 etapas (Túnel Liner / TL+OOEE / OOCC+OOEE). Contenido típico: contenedores oficinas/baños/bodega, compresor, winche, minicargador, acopio liner.</t>
         </is>
       </c>
-      <c r="D32" s="247" t="n"/>
-      <c r="E32" s="247" t="n"/>
-      <c r="F32" s="248" t="n"/>
+      <c r="D32" s="251" t="n"/>
+      <c r="E32" s="251" t="n"/>
+      <c r="F32" s="252" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="244" t="inlineStr">
+      <c r="A34" s="248" t="inlineStr">
         <is>
           <t>3. PRECIOS DE REFERENCIA MERCADO CHILE 2026 (estimados — solicitar cotización formal)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="245" t="inlineStr">
+      <c r="A35" s="249" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B35" s="245" t="inlineStr">
+      <c r="B35" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C35" s="245" t="inlineStr">
+      <c r="C35" s="249" t="inlineStr">
         <is>
           <t>UF mín/un</t>
         </is>
       </c>
-      <c r="D35" s="245" t="inlineStr">
+      <c r="D35" s="249" t="inlineStr">
         <is>
           <t>UF máx/un</t>
         </is>
       </c>
-      <c r="E35" s="245" t="inlineStr">
+      <c r="E35" s="249" t="inlineStr">
         <is>
           <t>CLP mín/un (aprox)</t>
         </is>
       </c>
-      <c r="F35" s="245" t="inlineStr">
+      <c r="F35" s="249" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="251" t="inlineStr">
+      <c r="A36" s="255" t="inlineStr">
         <is>
           <t>Excavación pique Ø4m</t>
         </is>
       </c>
-      <c r="B36" s="251" t="inlineStr">
+      <c r="B36" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C36" s="251" t="inlineStr">
+      <c r="C36" s="255" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="D36" s="251" t="inlineStr">
+      <c r="D36" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="E36" s="251" t="inlineStr">
+      <c r="E36" s="255" t="inlineStr">
         <is>
           <t>$77,000 – $134,750</t>
         </is>
       </c>
-      <c r="F36" s="251" t="inlineStr">
+      <c r="F36" s="255" t="inlineStr">
         <is>
           <t>ONDAC 2026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="251" t="inlineStr">
+      <c r="A37" s="255" t="inlineStr">
         <is>
           <t>Retiro excavación pique</t>
         </is>
       </c>
-      <c r="B37" s="251" t="inlineStr">
+      <c r="B37" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C37" s="251" t="inlineStr">
+      <c r="C37" s="255" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="D37" s="251" t="inlineStr">
+      <c r="D37" s="255" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="E37" s="251" t="inlineStr">
+      <c r="E37" s="255" t="inlineStr">
         <is>
           <t>$30,800 – $57,750</t>
         </is>
       </c>
-      <c r="F37" s="251" t="inlineStr">
+      <c r="F37" s="255" t="inlineStr">
         <is>
           <t>Mercado Santiago</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="251" t="inlineStr">
+      <c r="A38" s="255" t="inlineStr">
         <is>
           <t>Montaje liner pique Ø4m (solo inst.)</t>
         </is>
       </c>
-      <c r="B38" s="251" t="inlineStr">
+      <c r="B38" s="255" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="C38" s="251" t="inlineStr">
+      <c r="C38" s="255" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D38" s="251" t="inlineStr">
+      <c r="D38" s="255" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="E38" s="251" t="inlineStr">
+      <c r="E38" s="255" t="inlineStr">
         <is>
           <t>$154,000 – $308,000</t>
         </is>
       </c>
-      <c r="F38" s="251" t="inlineStr">
+      <c r="F38" s="255" t="inlineStr">
         <is>
           <t>Est. mercado</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="251" t="inlineStr">
+      <c r="A39" s="255" t="inlineStr">
         <is>
           <t>Shotcrete en pique</t>
         </is>
       </c>
-      <c r="B39" s="251" t="inlineStr">
+      <c r="B39" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C39" s="251" t="inlineStr">
+      <c r="C39" s="255" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="D39" s="251" t="inlineStr">
+      <c r="D39" s="255" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="E39" s="251" t="inlineStr">
+      <c r="E39" s="255" t="inlineStr">
         <is>
           <t>$173,250 – $269,500</t>
         </is>
       </c>
-      <c r="F39" s="251" t="inlineStr">
+      <c r="F39" s="255" t="inlineStr">
         <is>
           <t>ONDAC 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="251" t="inlineStr">
+      <c r="A40" s="255" t="inlineStr">
         <is>
           <t>Malla electrosoldada</t>
         </is>
       </c>
-      <c r="B40" s="251" t="inlineStr">
+      <c r="B40" s="255" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C40" s="251" t="inlineStr">
+      <c r="C40" s="255" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="D40" s="251" t="inlineStr">
+      <c r="D40" s="255" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="E40" s="251" t="inlineStr">
+      <c r="E40" s="255" t="inlineStr">
         <is>
           <t>$1,155 – $1,925</t>
         </is>
       </c>
-      <c r="F40" s="251" t="inlineStr">
+      <c r="F40" s="255" t="inlineStr">
         <is>
           <t>ONDAC 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="251" t="inlineStr">
+      <c r="A41" s="255" t="inlineStr">
         <is>
           <t>Montaje escalas+plataformas</t>
         </is>
       </c>
-      <c r="B41" s="251" t="inlineStr">
+      <c r="B41" s="255" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C41" s="251" t="inlineStr">
+      <c r="C41" s="255" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="D41" s="251" t="inlineStr">
+      <c r="D41" s="255" t="inlineStr">
         <is>
           <t>120.00</t>
         </is>
       </c>
-      <c r="E41" s="251" t="inlineStr">
+      <c r="E41" s="255" t="inlineStr">
         <is>
           <t>$2,310,000 – $4,620,000</t>
         </is>
       </c>
-      <c r="F41" s="251" t="inlineStr">
+      <c r="F41" s="255" t="inlineStr">
         <is>
           <t>Est. mercado/pique</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="251" t="inlineStr">
+      <c r="A42" s="255" t="inlineStr">
         <is>
           <t>Brocal definitivo</t>
         </is>
       </c>
-      <c r="B42" s="251" t="inlineStr">
+      <c r="B42" s="255" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="C42" s="251" t="inlineStr">
+      <c r="C42" s="255" t="inlineStr">
         <is>
           <t>80.00</t>
         </is>
       </c>
-      <c r="D42" s="251" t="inlineStr">
+      <c r="D42" s="255" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="E42" s="251" t="inlineStr">
+      <c r="E42" s="255" t="inlineStr">
         <is>
           <t>$3,080,000 – $5,775,000</t>
         </is>
       </c>
-      <c r="F42" s="251" t="inlineStr">
+      <c r="F42" s="255" t="inlineStr">
         <is>
           <t>Est. mercado</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="251" t="inlineStr">
+      <c r="A43" s="255" t="inlineStr">
         <is>
           <t>Excavación túnel Ø2.21m</t>
         </is>
       </c>
-      <c r="B43" s="251" t="inlineStr">
+      <c r="B43" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C43" s="251" t="inlineStr">
+      <c r="C43" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D43" s="251" t="inlineStr">
+      <c r="D43" s="255" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="E43" s="251" t="inlineStr">
+      <c r="E43" s="255" t="inlineStr">
         <is>
           <t>$134,750 – $231,000</t>
         </is>
       </c>
-      <c r="F43" s="251" t="inlineStr">
+      <c r="F43" s="255" t="inlineStr">
         <is>
           <t>ONDAC 2026 tunel urbano</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="251" t="inlineStr">
+      <c r="A44" s="255" t="inlineStr">
         <is>
           <t>Montaje liner túnel Ø2.21m</t>
         </is>
       </c>
-      <c r="B44" s="251" t="inlineStr">
+      <c r="B44" s="255" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="C44" s="251" t="inlineStr">
+      <c r="C44" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D44" s="251" t="inlineStr">
+      <c r="D44" s="255" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="E44" s="251" t="inlineStr">
+      <c r="E44" s="255" t="inlineStr">
         <is>
           <t>$134,750 – $231,000</t>
         </is>
       </c>
-      <c r="F44" s="251" t="inlineStr">
+      <c r="F44" s="255" t="inlineStr">
         <is>
           <t>Est. instalación</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="251" t="inlineStr">
+      <c r="A45" s="255" t="inlineStr">
         <is>
           <t>Radier túnel H30</t>
         </is>
       </c>
-      <c r="B45" s="251" t="inlineStr">
+      <c r="B45" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="C45" s="251" t="inlineStr">
+      <c r="C45" s="255" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="D45" s="251" t="inlineStr">
+      <c r="D45" s="255" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="E45" s="251" t="inlineStr">
+      <c r="E45" s="255" t="inlineStr">
         <is>
           <t>$269,500 – $385,000</t>
         </is>
       </c>
-      <c r="F45" s="251" t="inlineStr">
+      <c r="F45" s="255" t="inlineStr">
         <is>
           <t>ONDAC 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="251" t="inlineStr">
+      <c r="A46" s="255" t="inlineStr">
         <is>
           <t>Extractor Soler-Palau TGT/6-1409 (37kW) — 2 un</t>
         </is>
       </c>
-      <c r="B46" s="251" t="inlineStr">
+      <c r="B46" s="255" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="C46" s="251" t="inlineStr">
+      <c r="C46" s="255" t="inlineStr">
         <is>
           <t>800.00</t>
         </is>
       </c>
-      <c r="D46" s="251" t="inlineStr">
+      <c r="D46" s="255" t="inlineStr">
         <is>
           <t>1200.00</t>
         </is>
       </c>
-      <c r="E46" s="251" t="inlineStr">
+      <c r="E46" s="255" t="inlineStr">
         <is>
           <t>$30,800,000 – $46,200,000</t>
         </is>
       </c>
-      <c r="F46" s="251" t="inlineStr">
+      <c r="F46" s="255" t="inlineStr">
         <is>
           <t>STM38110 §3.14 — suministro STM, instalación contratista</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="251" t="inlineStr">
+      <c r="A47" s="255" t="inlineStr">
         <is>
           <t>Jet Fan S&amp;P TJHT/2/4-315-C (1.1kW) — N un</t>
         </is>
       </c>
-      <c r="B47" s="251" t="inlineStr">
+      <c r="B47" s="255" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="C47" s="251" t="inlineStr">
+      <c r="C47" s="255" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="D47" s="251" t="inlineStr">
+      <c r="D47" s="255" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="E47" s="251" t="inlineStr">
+      <c r="E47" s="255" t="inlineStr">
         <is>
           <t>$770,000 – $1,540,000</t>
         </is>
       </c>
-      <c r="F47" s="251" t="inlineStr">
+      <c r="F47" s="255" t="inlineStr">
         <is>
           <t>STM38110 §2.12 — suministro STM, cant. pendiente STM38109</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="244" t="inlineStr">
+      <c r="A49" s="248" t="inlineStr">
         <is>
           <t>4. ANÁLISIS DE SENSATEZ — PROYECTO COMPLETO (9 piques + 8 tramos)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="245" t="inlineStr">
+      <c r="A50" s="249" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B50" s="245" t="inlineStr">
+      <c r="B50" s="249" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="C50" s="245" t="inlineStr">
+      <c r="C50" s="249" t="inlineStr">
         <is>
           <t>UF/un Mín</t>
         </is>
       </c>
-      <c r="D50" s="245" t="inlineStr">
+      <c r="D50" s="249" t="inlineStr">
         <is>
           <t>UF/un Máx</t>
         </is>
       </c>
-      <c r="E50" s="245" t="inlineStr">
+      <c r="E50" s="249" t="inlineStr">
         <is>
           <t>Subtotal Mín (UF)</t>
         </is>
       </c>
-      <c r="F50" s="245" t="inlineStr">
+      <c r="F50" s="249" t="inlineStr">
         <is>
           <t>Subtotal Máx (UF)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="251" t="inlineStr">
+      <c r="A51" s="255" t="inlineStr">
         <is>
           <t>Excavación piques</t>
         </is>
       </c>
-      <c r="B51" s="251" t="n">
+      <c r="B51" s="255" t="n">
         <v>1770.3</v>
       </c>
-      <c r="C51" s="251" t="inlineStr">
+      <c r="C51" s="255" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="D51" s="251" t="inlineStr">
+      <c r="D51" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="E51" s="251" t="inlineStr">
+      <c r="E51" s="255" t="inlineStr">
         <is>
           <t>3,540.7</t>
         </is>
       </c>
-      <c r="F51" s="251" t="inlineStr">
+      <c r="F51" s="255" t="inlineStr">
         <is>
           <t>6,196.2</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="251" t="inlineStr">
+      <c r="A52" s="255" t="inlineStr">
         <is>
           <t>Retiro excav. piques</t>
         </is>
       </c>
-      <c r="B52" s="251" t="n">
+      <c r="B52" s="255" t="n">
         <v>1770.3</v>
       </c>
-      <c r="C52" s="251" t="inlineStr">
+      <c r="C52" s="255" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="D52" s="251" t="inlineStr">
+      <c r="D52" s="255" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="E52" s="251" t="inlineStr">
+      <c r="E52" s="255" t="inlineStr">
         <is>
           <t>1,416.3</t>
         </is>
       </c>
-      <c r="F52" s="251" t="inlineStr">
+      <c r="F52" s="255" t="inlineStr">
         <is>
           <t>2,655.5</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="251" t="inlineStr">
+      <c r="A53" s="255" t="inlineStr">
         <is>
           <t>Montaje liner piques</t>
         </is>
       </c>
-      <c r="B53" s="251" t="n">
+      <c r="B53" s="255" t="n">
         <v>140.9</v>
       </c>
-      <c r="C53" s="251" t="inlineStr">
+      <c r="C53" s="255" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D53" s="251" t="inlineStr">
+      <c r="D53" s="255" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="E53" s="251" t="inlineStr">
+      <c r="E53" s="255" t="inlineStr">
         <is>
           <t>563.6</t>
         </is>
       </c>
-      <c r="F53" s="251" t="inlineStr">
+      <c r="F53" s="255" t="inlineStr">
         <is>
           <t>1,127.2</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="251" t="inlineStr">
+      <c r="A54" s="255" t="inlineStr">
         <is>
           <t>Montaje escalas+plataformas</t>
         </is>
       </c>
-      <c r="B54" s="251" t="n">
+      <c r="B54" s="255" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="251" t="inlineStr">
+      <c r="C54" s="255" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="D54" s="251" t="inlineStr">
+      <c r="D54" s="255" t="inlineStr">
         <is>
           <t>120.00</t>
         </is>
       </c>
-      <c r="E54" s="251" t="inlineStr">
+      <c r="E54" s="255" t="inlineStr">
         <is>
           <t>540.0</t>
         </is>
       </c>
-      <c r="F54" s="251" t="inlineStr">
+      <c r="F54" s="255" t="inlineStr">
         <is>
           <t>1,080.0</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="251" t="inlineStr">
+      <c r="A55" s="255" t="inlineStr">
         <is>
           <t>Brocal definitivo</t>
         </is>
       </c>
-      <c r="B55" s="251" t="n">
+      <c r="B55" s="255" t="n">
         <v>9</v>
       </c>
-      <c r="C55" s="251" t="inlineStr">
+      <c r="C55" s="255" t="inlineStr">
         <is>
           <t>80.00</t>
         </is>
       </c>
-      <c r="D55" s="251" t="inlineStr">
+      <c r="D55" s="255" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="E55" s="251" t="inlineStr">
+      <c r="E55" s="255" t="inlineStr">
         <is>
           <t>720.0</t>
         </is>
       </c>
-      <c r="F55" s="251" t="inlineStr">
+      <c r="F55" s="255" t="inlineStr">
         <is>
           <t>1,350.0</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="251" t="inlineStr">
+      <c r="A56" s="255" t="inlineStr">
         <is>
           <t>Excavación túnel</t>
         </is>
       </c>
-      <c r="B56" s="251" t="n">
+      <c r="B56" s="255" t="n">
         <v>9414.200000000001</v>
       </c>
-      <c r="C56" s="251" t="inlineStr">
+      <c r="C56" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D56" s="251" t="inlineStr">
+      <c r="D56" s="255" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="E56" s="251" t="inlineStr">
+      <c r="E56" s="255" t="inlineStr">
         <is>
           <t>32,949.8</t>
         </is>
       </c>
-      <c r="F56" s="251" t="inlineStr">
+      <c r="F56" s="255" t="inlineStr">
         <is>
           <t>56,485.3</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="251" t="inlineStr">
+      <c r="A57" s="255" t="inlineStr">
         <is>
           <t>Montaje liner túnel</t>
         </is>
       </c>
-      <c r="B57" s="251" t="n">
+      <c r="B57" s="255" t="n">
         <v>2454.2</v>
       </c>
-      <c r="C57" s="251" t="inlineStr">
+      <c r="C57" s="255" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D57" s="251" t="inlineStr">
+      <c r="D57" s="255" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="E57" s="251" t="inlineStr">
+      <c r="E57" s="255" t="inlineStr">
         <is>
           <t>8,589.7</t>
         </is>
       </c>
-      <c r="F57" s="251" t="inlineStr">
+      <c r="F57" s="255" t="inlineStr">
         <is>
           <t>14,725.2</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="251" t="inlineStr">
+      <c r="A58" s="255" t="inlineStr">
         <is>
           <t>Radier H30</t>
         </is>
       </c>
-      <c r="B58" s="251" t="n">
+      <c r="B58" s="255" t="n">
         <v>813.6</v>
       </c>
-      <c r="C58" s="251" t="inlineStr">
+      <c r="C58" s="255" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="D58" s="251" t="inlineStr">
+      <c r="D58" s="255" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="E58" s="251" t="inlineStr">
+      <c r="E58" s="255" t="inlineStr">
         <is>
           <t>5,695.1</t>
         </is>
       </c>
-      <c r="F58" s="251" t="inlineStr">
+      <c r="F58" s="255" t="inlineStr">
         <is>
           <t>8,135.8</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="252" t="inlineStr">
+      <c r="A59" s="256" t="inlineStr">
         <is>
           <t>TOTAL ÍTEMS CUBICADOS</t>
         </is>
       </c>
-      <c r="B59" s="252" t="inlineStr"/>
-      <c r="C59" s="252" t="inlineStr"/>
-      <c r="D59" s="252" t="inlineStr"/>
-      <c r="E59" s="252" t="inlineStr">
+      <c r="B59" s="256" t="inlineStr"/>
+      <c r="C59" s="256" t="inlineStr"/>
+      <c r="D59" s="256" t="inlineStr"/>
+      <c r="E59" s="256" t="inlineStr">
         <is>
           <t>54,015 UF  (~$2079M CLP)</t>
         </is>
       </c>
-      <c r="F59" s="252" t="inlineStr">
+      <c r="F59" s="256" t="inlineStr">
         <is>
           <t>91,755 UF  (~$3532M CLP)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="243" t="inlineStr">
+      <c r="A60" s="247" t="inlineStr">
         <is>
           <t>⚠ NOTA: El rango anterior NO incluye shotcrete, malla, pernos, terminaciones, instalación de faenas ni actividades previas (Sec. 1, 3) — típicamente +30-50% adicional.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="244" t="inlineStr">
+      <c r="A62" s="248" t="inlineStr">
         <is>
           <t>5. CANTIDADES PRE-EXISTENTES EN TEMPLATE (de la licitación original)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="245" t="inlineStr">
+      <c r="A63" s="249" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B63" s="245" t="inlineStr">
+      <c r="B63" s="249" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C63" s="245" t="inlineStr">
+      <c r="C63" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D63" s="245" t="inlineStr">
+      <c r="D63" s="249" t="inlineStr">
         <is>
           <t>Cantidad original</t>
         </is>
       </c>
-      <c r="E63" s="245" t="inlineStr"/>
-      <c r="F63" s="245" t="inlineStr">
+      <c r="E63" s="249" t="inlineStr"/>
+      <c r="F63" s="249" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="253" t="inlineStr">
+      <c r="A64" s="257" t="inlineStr">
         <is>
           <t>5.1.4</t>
         </is>
       </c>
-      <c r="B64" s="253" t="inlineStr">
+      <c r="B64" s="257" t="inlineStr">
         <is>
           <t>Pernos frente fibra vidrio 4m (eventual)</t>
         </is>
       </c>
-      <c r="C64" s="253" t="inlineStr">
+      <c r="C64" s="257" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
-      <c r="D64" s="253" t="n">
+      <c r="D64" s="257" t="n">
         <v>39.54</v>
       </c>
-      <c r="F64" s="253" t="inlineStr">
+      <c r="F64" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="253" t="inlineStr">
+      <c r="A65" s="257" t="inlineStr">
         <is>
           <t>5.1.5</t>
         </is>
       </c>
-      <c r="B65" s="253" t="inlineStr">
+      <c r="B65" s="257" t="inlineStr">
         <is>
           <t>Shotcrete frente (eventual)</t>
         </is>
       </c>
-      <c r="C65" s="253" t="inlineStr">
+      <c r="C65" s="257" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="D65" s="253" t="n">
+      <c r="D65" s="257" t="n">
         <v>19.77</v>
       </c>
-      <c r="F65" s="253" t="inlineStr">
+      <c r="F65" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="253" t="inlineStr">
+      <c r="A66" s="257" t="inlineStr">
         <is>
           <t>5.1.6</t>
         </is>
       </c>
-      <c r="B66" s="253" t="inlineStr">
+      <c r="B66" s="257" t="inlineStr">
         <is>
           <t>Paraguas micropilotes (eventual)</t>
         </is>
       </c>
-      <c r="C66" s="253" t="inlineStr">
+      <c r="C66" s="257" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
-      <c r="D66" s="253" t="n">
+      <c r="D66" s="257" t="n">
         <v>24</v>
       </c>
-      <c r="F66" s="253" t="inlineStr">
+      <c r="F66" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="253" t="inlineStr">
+      <c r="A67" s="257" t="inlineStr">
         <is>
           <t>5.2.4–5.8.4</t>
         </is>
       </c>
-      <c r="B67" s="253" t="inlineStr">
+      <c r="B67" s="257" t="inlineStr">
         <is>
           <t>Pernos frente (tramos 2-8)</t>
         </is>
       </c>
-      <c r="C67" s="253" t="inlineStr">
+      <c r="C67" s="257" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
-      <c r="D67" s="253" t="inlineStr">
+      <c r="D67" s="257" t="inlineStr">
         <is>
           <t>36-36 por tramo</t>
         </is>
       </c>
-      <c r="F67" s="253" t="inlineStr">
+      <c r="F67" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="253" t="inlineStr">
+      <c r="A68" s="257" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B68" s="253" t="inlineStr">
+      <c r="B68" s="257" t="inlineStr">
         <is>
           <t>Base binder asfalto</t>
         </is>
       </c>
-      <c r="C68" s="253" t="inlineStr">
+      <c r="C68" s="257" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D68" s="253" t="n">
+      <c r="D68" s="257" t="n">
         <v>317.61</v>
       </c>
-      <c r="F68" s="253" t="inlineStr">
+      <c r="F68" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="253" t="inlineStr">
+      <c r="A69" s="257" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B69" s="253" t="inlineStr">
+      <c r="B69" s="257" t="inlineStr">
         <is>
           <t>Base chancada CBR80</t>
         </is>
       </c>
-      <c r="C69" s="253" t="inlineStr">
+      <c r="C69" s="257" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="D69" s="253" t="n">
+      <c r="D69" s="257" t="n">
         <v>66.7</v>
       </c>
-      <c r="F69" s="253" t="inlineStr">
+      <c r="F69" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="253" t="inlineStr">
+      <c r="A70" s="257" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B70" s="253" t="inlineStr">
+      <c r="B70" s="257" t="inlineStr">
         <is>
           <t>Calzada con tratamiento asfaltico</t>
         </is>
       </c>
-      <c r="C70" s="253" t="inlineStr">
+      <c r="C70" s="257" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D70" s="253" t="n">
+      <c r="D70" s="257" t="n">
         <v>317.61</v>
       </c>
-      <c r="F70" s="253" t="inlineStr">
+      <c r="F70" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="253" t="inlineStr">
+      <c r="A71" s="257" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B71" s="253" t="inlineStr">
+      <c r="B71" s="257" t="inlineStr">
         <is>
           <t>Excavación dura y transporte botadero</t>
         </is>
       </c>
-      <c r="C71" s="253" t="inlineStr">
+      <c r="C71" s="257" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="D71" s="253" t="n">
+      <c r="D71" s="257" t="n">
         <v>343.02</v>
       </c>
-      <c r="F71" s="253" t="inlineStr">
+      <c r="F71" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="253" t="inlineStr">
+      <c r="A72" s="257" t="inlineStr">
         <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="B72" s="253" t="inlineStr">
+      <c r="B72" s="257" t="inlineStr">
         <is>
           <t>Entibación excavaciones</t>
         </is>
       </c>
-      <c r="C72" s="253" t="inlineStr">
+      <c r="C72" s="257" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D72" s="253" t="n">
+      <c r="D72" s="257" t="n">
         <v>90.75</v>
       </c>
-      <c r="F72" s="253" t="inlineStr">
+      <c r="F72" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="253" t="inlineStr">
+      <c r="A73" s="257" t="inlineStr">
         <is>
           <t>7.11</t>
         </is>
       </c>
-      <c r="B73" s="253" t="inlineStr">
+      <c r="B73" s="257" t="inlineStr">
         <is>
           <t>Reposición áreas verdes</t>
         </is>
       </c>
-      <c r="C73" s="253" t="inlineStr">
+      <c r="C73" s="257" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D73" s="253" t="n">
+      <c r="D73" s="257" t="n">
         <v>60</v>
       </c>
-      <c r="F73" s="253" t="inlineStr">
+      <c r="F73" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="253" t="inlineStr">
+      <c r="A74" s="257" t="inlineStr">
         <is>
           <t>7.12</t>
         </is>
       </c>
-      <c r="B74" s="253" t="inlineStr">
+      <c r="B74" s="257" t="inlineStr">
         <is>
           <t>Reposición soleras</t>
         </is>
       </c>
-      <c r="C74" s="253" t="inlineStr">
+      <c r="C74" s="257" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D74" s="253" t="n">
+      <c r="D74" s="257" t="n">
         <v>40</v>
       </c>
-      <c r="F74" s="253" t="inlineStr">
+      <c r="F74" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="253" t="inlineStr">
+      <c r="A75" s="257" t="inlineStr">
         <is>
           <t>7.13</t>
         </is>
       </c>
-      <c r="B75" s="253" t="inlineStr">
+      <c r="B75" s="257" t="inlineStr">
         <is>
           <t>Demolición y reposición veredas</t>
         </is>
       </c>
-      <c r="C75" s="253" t="inlineStr">
+      <c r="C75" s="257" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D75" s="253" t="n">
+      <c r="D75" s="257" t="n">
         <v>20</v>
       </c>
-      <c r="F75" s="253" t="inlineStr">
+      <c r="F75" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="253" t="inlineStr">
+      <c r="A76" s="257" t="inlineStr">
         <is>
           <t>13.2</t>
         </is>
       </c>
-      <c r="B76" s="253" t="inlineStr">
+      <c r="B76" s="257" t="inlineStr">
         <is>
           <t>Retiro y transporte aguas efluentes</t>
         </is>
       </c>
-      <c r="C76" s="253" t="inlineStr">
+      <c r="C76" s="257" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="D76" s="253" t="n">
+      <c r="D76" s="257" t="n">
         <v>1000</v>
       </c>
-      <c r="F76" s="253" t="inlineStr">
+      <c r="F76" s="257" t="inlineStr">
         <is>
           <t>Cuadro precios STM rev.1 06/04/2026</t>
         </is>
@@ -15369,2093 +15891,2093 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="254" t="inlineStr">
+      <c r="A1" s="258" t="inlineStr">
         <is>
           <t>MEMORIA DE CÁLCULO — TÚNEL LAT 2×110 kV VITACURA-PROVIDENCIA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="255" t="inlineStr">
+      <c r="A2" s="259" t="inlineStr">
         <is>
           <t>Documento generado: 2026-05-19 | Licitación: 2025-25-TX-SS-RM | Mandante: STM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="244" t="inlineStr">
+      <c r="A4" s="248" t="inlineStr">
         <is>
           <t>1. CONSTANTES GEOMÉTRICAS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="245" t="inlineStr">
+      <c r="A5" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="245" t="inlineStr">
+      <c r="B5" s="249" t="inlineStr">
         <is>
           <t>Constante</t>
         </is>
       </c>
-      <c r="C5" s="245" t="inlineStr">
+      <c r="C5" s="249" t="inlineStr">
         <is>
           <t>Fórmula</t>
         </is>
       </c>
-      <c r="D5" s="245" t="inlineStr">
+      <c r="D5" s="249" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="E5" s="245" t="inlineStr">
+      <c r="E5" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F5" s="245" t="inlineStr">
+      <c r="F5" s="249" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="255" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="251" t="inlineStr">
+      <c r="B6" s="255" t="inlineStr">
         <is>
           <t>Área sección pique</t>
         </is>
       </c>
-      <c r="C6" s="251" t="inlineStr">
+      <c r="C6" s="255" t="inlineStr">
         <is>
           <t>π × r² = π × (4.0/2)²</t>
         </is>
       </c>
-      <c r="D6" s="251" t="inlineStr">
+      <c r="D6" s="255" t="inlineStr">
         <is>
           <t>12.5664</t>
         </is>
       </c>
-      <c r="E6" s="251" t="inlineStr">
+      <c r="E6" s="255" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F6" s="251" t="inlineStr">
+      <c r="F6" s="255" t="inlineStr">
         <is>
           <t>STM38136 Ø interior pique</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="251" t="inlineStr">
+      <c r="A7" s="255" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="251" t="inlineStr">
+      <c r="B7" s="255" t="inlineStr">
         <is>
           <t>Área sección túnel liner</t>
         </is>
       </c>
-      <c r="C7" s="251" t="inlineStr">
+      <c r="C7" s="255" t="inlineStr">
         <is>
           <t>π × r² = π × (2.21/2)²</t>
         </is>
       </c>
-      <c r="D7" s="251" t="inlineStr">
+      <c r="D7" s="255" t="inlineStr">
         <is>
           <t>3.8359</t>
         </is>
       </c>
-      <c r="E7" s="251" t="inlineStr">
+      <c r="E7" s="255" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F7" s="251" t="inlineStr">
+      <c r="F7" s="255" t="inlineStr">
         <is>
           <t>STM38136 Ø interior liner</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="255" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="251" t="inlineStr">
+      <c r="B8" s="255" t="inlineStr">
         <is>
           <t>Radier H30 volumen por metro</t>
         </is>
       </c>
-      <c r="C8" s="251" t="inlineStr">
+      <c r="C8" s="255" t="inlineStr">
         <is>
           <t>ancho × espesor = 2.21 × 0.15</t>
         </is>
       </c>
-      <c r="D8" s="251" t="inlineStr">
+      <c r="D8" s="255" t="inlineStr">
         <is>
           <t>0.3315</t>
         </is>
       </c>
-      <c r="E8" s="251" t="inlineStr">
+      <c r="E8" s="255" t="inlineStr">
         <is>
           <t>m³/m</t>
         </is>
       </c>
-      <c r="F8" s="251" t="inlineStr">
+      <c r="F8" s="255" t="inlineStr">
         <is>
           <t>Diseño estructural radier túnel</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="251" t="inlineStr">
+      <c r="A9" s="255" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="251" t="inlineStr">
+      <c r="B9" s="255" t="inlineStr">
         <is>
           <t>Diámetro fundación pique</t>
         </is>
       </c>
-      <c r="C9" s="251" t="inlineStr">
+      <c r="C9" s="255" t="inlineStr">
         <is>
           <t>4.20 m externo</t>
         </is>
       </c>
-      <c r="D9" s="251" t="inlineStr">
+      <c r="D9" s="255" t="inlineStr">
         <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="E9" s="251" t="inlineStr">
+      <c r="E9" s="255" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F9" s="251" t="inlineStr">
+      <c r="F9" s="255" t="inlineStr">
         <is>
           <t>STM38020 detalle típico</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="255" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="251" t="inlineStr">
+      <c r="B10" s="255" t="inlineStr">
         <is>
           <t>Espesor liner túnel (PL)</t>
         </is>
       </c>
-      <c r="C10" s="251" t="inlineStr">
+      <c r="C10" s="255" t="inlineStr">
         <is>
           <t>5 mm</t>
         </is>
       </c>
-      <c r="D10" s="251" t="inlineStr">
+      <c r="D10" s="255" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="E10" s="251" t="inlineStr">
+      <c r="E10" s="255" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F10" s="251" t="inlineStr">
+      <c r="F10" s="255" t="inlineStr">
         <is>
           <t>STM38020 nota técnica</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="244" t="inlineStr">
+      <c r="A12" s="248" t="inlineStr">
         <is>
           <t>2. PROFUNDIDADES DE PIQUES — NV terreno - NV invert liner</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="245" t="inlineStr">
+      <c r="A13" s="249" t="inlineStr">
         <is>
           <t>Pique</t>
         </is>
       </c>
-      <c r="B13" s="245" t="inlineStr">
+      <c r="B13" s="249" t="inlineStr">
         <is>
           <t>NV terreno (m.s.n.m)</t>
         </is>
       </c>
-      <c r="C13" s="245" t="inlineStr">
+      <c r="C13" s="249" t="inlineStr">
         <is>
           <t>NV liner invert (m.s.n.m)</t>
         </is>
       </c>
-      <c r="D13" s="245" t="inlineStr">
+      <c r="D13" s="249" t="inlineStr">
         <is>
           <t>Profundidad (m)</t>
         </is>
       </c>
-      <c r="E13" s="245" t="inlineStr">
+      <c r="E13" s="249" t="inlineStr">
         <is>
           <t>Excavación (m³)</t>
         </is>
       </c>
-      <c r="F13" s="245" t="inlineStr">
+      <c r="F13" s="249" t="inlineStr">
         <is>
           <t>Fuente plano</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="246" t="inlineStr">
+      <c r="A14" s="250" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B14" s="246" t="inlineStr">
+      <c r="B14" s="250" t="inlineStr">
         <is>
           <t>625.06</t>
         </is>
       </c>
-      <c r="C14" s="246" t="inlineStr">
+      <c r="C14" s="250" t="inlineStr">
         <is>
           <t>604.97</t>
         </is>
       </c>
-      <c r="D14" s="246" t="inlineStr">
+      <c r="D14" s="250" t="inlineStr">
         <is>
           <t>20.09</t>
         </is>
       </c>
-      <c r="E14" s="246" t="n">
+      <c r="E14" s="250" t="n">
         <v>252.46</v>
       </c>
-      <c r="F14" s="246" t="inlineStr">
+      <c r="F14" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="246" t="inlineStr">
+      <c r="A15" s="250" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B15" s="246" t="inlineStr">
+      <c r="B15" s="250" t="inlineStr">
         <is>
           <t>621.50</t>
         </is>
       </c>
-      <c r="C15" s="246" t="inlineStr">
+      <c r="C15" s="250" t="inlineStr">
         <is>
           <t>602.83</t>
         </is>
       </c>
-      <c r="D15" s="246" t="inlineStr">
+      <c r="D15" s="250" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="E15" s="246" t="n">
+      <c r="E15" s="250" t="n">
         <v>234.61</v>
       </c>
-      <c r="F15" s="246" t="inlineStr">
+      <c r="F15" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="246" t="inlineStr">
+      <c r="A16" s="250" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B16" s="246" t="inlineStr">
+      <c r="B16" s="250" t="inlineStr">
         <is>
           <t>619.18</t>
         </is>
       </c>
-      <c r="C16" s="246" t="inlineStr">
+      <c r="C16" s="250" t="inlineStr">
         <is>
           <t>601.88</t>
         </is>
       </c>
-      <c r="D16" s="246" t="inlineStr">
+      <c r="D16" s="250" t="inlineStr">
         <is>
           <t>17.30</t>
         </is>
       </c>
-      <c r="E16" s="246" t="n">
+      <c r="E16" s="250" t="n">
         <v>217.4</v>
       </c>
-      <c r="F16" s="246" t="inlineStr">
+      <c r="F16" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="246" t="inlineStr">
+      <c r="A17" s="250" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B17" s="246" t="inlineStr">
+      <c r="B17" s="250" t="inlineStr">
         <is>
           <t>612.91</t>
         </is>
       </c>
-      <c r="C17" s="246" t="inlineStr">
+      <c r="C17" s="250" t="inlineStr">
         <is>
           <t>597.93</t>
         </is>
       </c>
-      <c r="D17" s="246" t="inlineStr">
+      <c r="D17" s="250" t="inlineStr">
         <is>
           <t>14.98</t>
         </is>
       </c>
-      <c r="E17" s="246" t="n">
+      <c r="E17" s="250" t="n">
         <v>188.24</v>
       </c>
-      <c r="F17" s="246" t="inlineStr">
+      <c r="F17" s="250" t="inlineStr">
         <is>
           <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="246" t="inlineStr">
+      <c r="A18" s="250" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B18" s="246" t="inlineStr">
+      <c r="B18" s="250" t="inlineStr">
         <is>
           <t>610.70</t>
         </is>
       </c>
-      <c r="C18" s="246" t="inlineStr">
+      <c r="C18" s="250" t="inlineStr">
         <is>
           <t>595.46</t>
         </is>
       </c>
-      <c r="D18" s="246" t="inlineStr">
+      <c r="D18" s="250" t="inlineStr">
         <is>
           <t>15.24</t>
         </is>
       </c>
-      <c r="E18" s="246" t="n">
+      <c r="E18" s="250" t="n">
         <v>191.51</v>
       </c>
-      <c r="F18" s="246" t="inlineStr">
+      <c r="F18" s="250" t="inlineStr">
         <is>
           <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="246" t="inlineStr">
+      <c r="A19" s="250" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B19" s="246" t="inlineStr">
+      <c r="B19" s="250" t="inlineStr">
         <is>
           <t>607.39</t>
         </is>
       </c>
-      <c r="C19" s="246" t="inlineStr">
+      <c r="C19" s="250" t="inlineStr">
         <is>
           <t>591.88</t>
         </is>
       </c>
-      <c r="D19" s="246" t="inlineStr">
+      <c r="D19" s="250" t="inlineStr">
         <is>
           <t>15.51</t>
         </is>
       </c>
-      <c r="E19" s="246" t="n">
+      <c r="E19" s="250" t="n">
         <v>194.9</v>
       </c>
-      <c r="F19" s="246" t="inlineStr">
+      <c r="F19" s="250" t="inlineStr">
         <is>
           <t>STM38022</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="246" t="inlineStr">
+      <c r="A20" s="250" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B20" s="246" t="inlineStr">
+      <c r="B20" s="250" t="inlineStr">
         <is>
           <t>603.15</t>
         </is>
       </c>
-      <c r="C20" s="246" t="inlineStr">
+      <c r="C20" s="250" t="inlineStr">
         <is>
           <t>587.53</t>
         </is>
       </c>
-      <c r="D20" s="246" t="inlineStr">
+      <c r="D20" s="250" t="inlineStr">
         <is>
           <t>15.62</t>
         </is>
       </c>
-      <c r="E20" s="246" t="n">
+      <c r="E20" s="250" t="n">
         <v>196.29</v>
       </c>
-      <c r="F20" s="246" t="inlineStr">
+      <c r="F20" s="250" t="inlineStr">
         <is>
           <t>STM38022</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="246" t="inlineStr">
+      <c r="A21" s="250" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B21" s="246" t="inlineStr">
+      <c r="B21" s="250" t="inlineStr">
         <is>
           <t>599.00</t>
         </is>
       </c>
-      <c r="C21" s="246" t="inlineStr">
+      <c r="C21" s="250" t="inlineStr">
         <is>
           <t>584.59</t>
         </is>
       </c>
-      <c r="D21" s="246" t="inlineStr">
+      <c r="D21" s="250" t="inlineStr">
         <is>
           <t>14.41</t>
         </is>
       </c>
-      <c r="E21" s="246" t="n">
+      <c r="E21" s="250" t="n">
         <v>181.08</v>
       </c>
-      <c r="F21" s="246" t="inlineStr">
+      <c r="F21" s="250" t="inlineStr">
         <is>
           <t>STM38023</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="246" t="inlineStr">
+      <c r="A22" s="250" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B22" s="246" t="inlineStr">
+      <c r="B22" s="250" t="inlineStr">
         <is>
           <t>591.18</t>
         </is>
       </c>
-      <c r="C22" s="246" t="inlineStr">
+      <c r="C22" s="250" t="inlineStr">
         <is>
           <t>582.12</t>
         </is>
       </c>
-      <c r="D22" s="246" t="inlineStr">
+      <c r="D22" s="250" t="inlineStr">
         <is>
           <t>9.06</t>
         </is>
       </c>
-      <c r="E22" s="246" t="n">
+      <c r="E22" s="250" t="n">
         <v>113.85</v>
       </c>
-      <c r="F22" s="246" t="inlineStr">
+      <c r="F22" s="250" t="inlineStr">
         <is>
           <t>STM38023</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="243" t="inlineStr">
+      <c r="A23" s="247" t="inlineStr">
         <is>
           <t>⚠ Discrepancia P9: STM38109 §2.4 reporta 9.67m (referencia portal vs NV terreno). Diferencia 0.61m × 12.57m² = ~7.7 m³ excavación adicional si se usa cota portal.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="244" t="inlineStr">
+      <c r="A25" s="248" t="inlineStr">
         <is>
           <t>3. LONGITUDES DE TRAMOS — DM piques sucesivos</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="245" t="inlineStr">
+      <c r="A26" s="249" t="inlineStr">
         <is>
           <t>Tramo</t>
         </is>
       </c>
-      <c r="B26" s="245" t="inlineStr">
+      <c r="B26" s="249" t="inlineStr">
         <is>
           <t>Entre piques</t>
         </is>
       </c>
-      <c r="C26" s="245" t="inlineStr">
+      <c r="C26" s="249" t="inlineStr">
         <is>
           <t>DM inicio (m)</t>
         </is>
       </c>
-      <c r="D26" s="245" t="inlineStr">
+      <c r="D26" s="249" t="inlineStr">
         <is>
           <t>DM fin (m)</t>
         </is>
       </c>
-      <c r="E26" s="245" t="inlineStr">
+      <c r="E26" s="249" t="inlineStr">
         <is>
           <t>Longitud (m)</t>
         </is>
       </c>
-      <c r="F26" s="245" t="inlineStr">
+      <c r="F26" s="249" t="inlineStr">
         <is>
           <t>Fuente plano</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="246" t="inlineStr">
+      <c r="A27" s="250" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B27" s="246" t="inlineStr">
+      <c r="B27" s="250" t="inlineStr">
         <is>
           <t>P1-P2</t>
         </is>
       </c>
-      <c r="C27" s="246" t="inlineStr">
+      <c r="C27" s="250" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D27" s="246" t="inlineStr">
+      <c r="D27" s="250" t="inlineStr">
         <is>
           <t>389.0</t>
         </is>
       </c>
-      <c r="E27" s="246" t="inlineStr">
+      <c r="E27" s="250" t="inlineStr">
         <is>
           <t>389.0</t>
         </is>
       </c>
-      <c r="F27" s="246" t="inlineStr">
+      <c r="F27" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="246" t="inlineStr">
+      <c r="A28" s="250" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B28" s="246" t="inlineStr">
+      <c r="B28" s="250" t="inlineStr">
         <is>
           <t>P2-P3</t>
         </is>
       </c>
-      <c r="C28" s="246" t="inlineStr">
+      <c r="C28" s="250" t="inlineStr">
         <is>
           <t>389.0</t>
         </is>
       </c>
-      <c r="D28" s="246" t="inlineStr">
+      <c r="D28" s="250" t="inlineStr">
         <is>
           <t>560.6</t>
         </is>
       </c>
-      <c r="E28" s="246" t="inlineStr">
+      <c r="E28" s="250" t="inlineStr">
         <is>
           <t>171.6</t>
         </is>
       </c>
-      <c r="F28" s="246" t="inlineStr">
+      <c r="F28" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="246" t="inlineStr">
+      <c r="A29" s="250" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B29" s="246" t="inlineStr">
+      <c r="B29" s="250" t="inlineStr">
         <is>
           <t>P3-P4</t>
         </is>
       </c>
-      <c r="C29" s="246" t="inlineStr">
+      <c r="C29" s="250" t="inlineStr">
         <is>
           <t>560.6</t>
         </is>
       </c>
-      <c r="D29" s="246" t="inlineStr">
+      <c r="D29" s="250" t="inlineStr">
         <is>
           <t>955.7</t>
         </is>
       </c>
-      <c r="E29" s="246" t="inlineStr">
+      <c r="E29" s="250" t="inlineStr">
         <is>
           <t>395.1</t>
         </is>
       </c>
-      <c r="F29" s="246" t="inlineStr">
+      <c r="F29" s="250" t="inlineStr">
         <is>
           <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="246" t="inlineStr">
+      <c r="A30" s="250" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B30" s="246" t="inlineStr">
+      <c r="B30" s="250" t="inlineStr">
         <is>
           <t>P4-P5</t>
         </is>
       </c>
-      <c r="C30" s="246" t="inlineStr">
+      <c r="C30" s="250" t="inlineStr">
         <is>
           <t>955.7</t>
         </is>
       </c>
-      <c r="D30" s="246" t="inlineStr">
+      <c r="D30" s="250" t="inlineStr">
         <is>
           <t>1161.6</t>
         </is>
       </c>
-      <c r="E30" s="246" t="inlineStr">
+      <c r="E30" s="250" t="inlineStr">
         <is>
           <t>205.9</t>
         </is>
       </c>
-      <c r="F30" s="246" t="inlineStr">
+      <c r="F30" s="250" t="inlineStr">
         <is>
           <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="246" t="inlineStr">
+      <c r="A31" s="250" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B31" s="246" t="inlineStr">
+      <c r="B31" s="250" t="inlineStr">
         <is>
           <t>P5-P6</t>
         </is>
       </c>
-      <c r="C31" s="246" t="inlineStr">
+      <c r="C31" s="250" t="inlineStr">
         <is>
           <t>1161.6</t>
         </is>
       </c>
-      <c r="D31" s="246" t="inlineStr">
+      <c r="D31" s="250" t="inlineStr">
         <is>
           <t>1459.4</t>
         </is>
       </c>
-      <c r="E31" s="246" t="inlineStr">
+      <c r="E31" s="250" t="inlineStr">
         <is>
           <t>297.8</t>
         </is>
       </c>
-      <c r="F31" s="246" t="inlineStr">
+      <c r="F31" s="250" t="inlineStr">
         <is>
           <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="246" t="inlineStr">
+      <c r="A32" s="250" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B32" s="246" t="inlineStr">
+      <c r="B32" s="250" t="inlineStr">
         <is>
           <t>P6-P7</t>
         </is>
       </c>
-      <c r="C32" s="246" t="inlineStr">
+      <c r="C32" s="250" t="inlineStr">
         <is>
           <t>1459.4</t>
         </is>
       </c>
-      <c r="D32" s="246" t="inlineStr">
+      <c r="D32" s="250" t="inlineStr">
         <is>
           <t>1777.4</t>
         </is>
       </c>
-      <c r="E32" s="246" t="inlineStr">
+      <c r="E32" s="250" t="inlineStr">
         <is>
           <t>318.0</t>
         </is>
       </c>
-      <c r="F32" s="246" t="inlineStr">
+      <c r="F32" s="250" t="inlineStr">
         <is>
           <t>STM38022</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="246" t="inlineStr">
+      <c r="A33" s="250" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B33" s="246" t="inlineStr">
+      <c r="B33" s="250" t="inlineStr">
         <is>
           <t>P7-P8</t>
         </is>
       </c>
-      <c r="C33" s="246" t="inlineStr">
+      <c r="C33" s="250" t="inlineStr">
         <is>
           <t>1777.4</t>
         </is>
       </c>
-      <c r="D33" s="246" t="inlineStr">
+      <c r="D33" s="250" t="inlineStr">
         <is>
           <t>2145.1</t>
         </is>
       </c>
-      <c r="E33" s="246" t="inlineStr">
+      <c r="E33" s="250" t="inlineStr">
         <is>
           <t>367.7</t>
         </is>
       </c>
-      <c r="F33" s="246" t="inlineStr">
+      <c r="F33" s="250" t="inlineStr">
         <is>
           <t>STM38022</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="246" t="inlineStr">
+      <c r="A34" s="250" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B34" s="246" t="inlineStr">
+      <c r="B34" s="250" t="inlineStr">
         <is>
           <t>P8-P9</t>
         </is>
       </c>
-      <c r="C34" s="246" t="inlineStr">
+      <c r="C34" s="250" t="inlineStr">
         <is>
           <t>2145.1</t>
         </is>
       </c>
-      <c r="D34" s="246" t="inlineStr">
+      <c r="D34" s="250" t="inlineStr">
         <is>
           <t>2454.2</t>
         </is>
       </c>
-      <c r="E34" s="246" t="inlineStr">
+      <c r="E34" s="250" t="inlineStr">
         <is>
           <t>309.1</t>
         </is>
       </c>
-      <c r="F34" s="246" t="inlineStr">
+      <c r="F34" s="250" t="inlineStr">
         <is>
           <t>STM38023</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="244" t="inlineStr">
+      <c r="A36" s="248" t="inlineStr">
         <is>
           <t>4. FÓRMULAS POR PARTIDA</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="245" t="inlineStr">
+      <c r="A37" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B37" s="245" t="inlineStr">
+      <c r="B37" s="249" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="C37" s="245" t="inlineStr">
+      <c r="C37" s="249" t="inlineStr">
         <is>
           <t>Fórmula aplicada</t>
         </is>
       </c>
-      <c r="D37" s="245" t="inlineStr">
+      <c r="D37" s="249" t="inlineStr">
         <is>
           <t>Cantidad total</t>
         </is>
       </c>
-      <c r="E37" s="245" t="inlineStr">
+      <c r="E37" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F37" s="245" t="inlineStr">
+      <c r="F37" s="249" t="inlineStr">
         <is>
           <t>Validación</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="251" t="inlineStr">
+      <c r="A38" s="255" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B38" s="251" t="inlineStr">
+      <c r="B38" s="255" t="inlineStr">
         <is>
           <t>Excavación piques</t>
         </is>
       </c>
-      <c r="C38" s="251" t="inlineStr">
+      <c r="C38" s="255" t="inlineStr">
         <is>
           <t>Σ (12.5664 m² × prof_i) para i=1..9</t>
         </is>
       </c>
-      <c r="D38" s="251" t="n">
+      <c r="D38" s="255" t="n">
         <v>1770.34</v>
       </c>
-      <c r="E38" s="251" t="inlineStr">
+      <c r="E38" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F38" s="251" t="inlineStr">
+      <c r="F38" s="255" t="inlineStr">
         <is>
           <t>✓ Coincide con suma manual</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="251" t="inlineStr">
+      <c r="A39" s="255" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B39" s="251" t="inlineStr">
+      <c r="B39" s="255" t="inlineStr">
         <is>
           <t>Retiro excavación piques</t>
         </is>
       </c>
-      <c r="C39" s="251">
+      <c r="C39" s="255">
         <f> Excavación pique (igual volumen al botadero)</f>
         <v/>
       </c>
-      <c r="D39" s="251" t="n">
+      <c r="D39" s="255" t="n">
         <v>1770.34</v>
       </c>
-      <c r="E39" s="251" t="inlineStr">
+      <c r="E39" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F39" s="251" t="inlineStr">
+      <c r="F39" s="255" t="inlineStr">
         <is>
           <t>✓ = Excavación</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="251" t="inlineStr">
+      <c r="A40" s="255" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B40" s="251" t="inlineStr">
+      <c r="B40" s="255" t="inlineStr">
         <is>
           <t>Montaje liner pique</t>
         </is>
       </c>
-      <c r="C40" s="251" t="inlineStr">
+      <c r="C40" s="255" t="inlineStr">
         <is>
           <t>Σ profundidad_i para i=1..9</t>
         </is>
       </c>
-      <c r="D40" s="251" t="n">
+      <c r="D40" s="255" t="n">
         <v>140.9</v>
       </c>
-      <c r="E40" s="251" t="inlineStr">
+      <c r="E40" s="255" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F40" s="251">
+      <c r="F40" s="255">
         <f> longitud anillo × cantidad anillos</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="251" t="inlineStr">
+      <c r="A41" s="255" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B41" s="251" t="inlineStr">
+      <c r="B41" s="255" t="inlineStr">
         <is>
           <t>Montaje escalas+plataformas</t>
         </is>
       </c>
-      <c r="C41" s="251" t="inlineStr">
+      <c r="C41" s="255" t="inlineStr">
         <is>
           <t>1 gl × 9 piques (Aporte STM)</t>
         </is>
       </c>
-      <c r="D41" s="251" t="n">
+      <c r="D41" s="255" t="n">
         <v>9</v>
       </c>
-      <c r="E41" s="251" t="inlineStr">
+      <c r="E41" s="255" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="F41" s="251" t="inlineStr">
+      <c r="F41" s="255" t="inlineStr">
         <is>
           <t>✓ Una unidad global por pique</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="251" t="inlineStr">
+      <c r="A42" s="255" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B42" s="251" t="inlineStr">
+      <c r="B42" s="255" t="inlineStr">
         <is>
           <t>Brocal definitivo</t>
         </is>
       </c>
-      <c r="C42" s="251" t="inlineStr">
+      <c r="C42" s="255" t="inlineStr">
         <is>
           <t>1 gl × 9 piques</t>
         </is>
       </c>
-      <c r="D42" s="251" t="n">
+      <c r="D42" s="255" t="n">
         <v>9</v>
       </c>
-      <c r="E42" s="251" t="inlineStr">
+      <c r="E42" s="255" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="F42" s="251" t="inlineStr">
+      <c r="F42" s="255" t="inlineStr">
         <is>
           <t>P1/P9 → ítem .15; P2-8 → ítem .14</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="251" t="inlineStr">
+      <c r="A43" s="255" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B43" s="251" t="inlineStr">
+      <c r="B43" s="255" t="inlineStr">
         <is>
           <t>Montaje estructura cables (SS)</t>
         </is>
       </c>
-      <c r="C43" s="251" t="inlineStr">
+      <c r="C43" s="255" t="inlineStr">
         <is>
           <t>1 gl × 2 piques SS (P1 y P9)</t>
         </is>
       </c>
-      <c r="D43" s="251" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="251" t="inlineStr">
+      <c r="D43" s="255" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="255" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="F43" s="251" t="inlineStr">
+      <c r="F43" s="255" t="inlineStr">
         <is>
           <t>Solo SS Vitacura + SS Providencia</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="251" t="inlineStr">
+      <c r="A44" s="255" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B44" s="251" t="inlineStr">
+      <c r="B44" s="255" t="inlineStr">
         <is>
           <t>Excavación túnel</t>
         </is>
       </c>
-      <c r="C44" s="251" t="inlineStr">
+      <c r="C44" s="255" t="inlineStr">
         <is>
           <t>Σ (3.8359 m² × longitud_i) para i=1..8</t>
         </is>
       </c>
-      <c r="D44" s="251" t="n">
+      <c r="D44" s="255" t="n">
         <v>9414.219999999999</v>
       </c>
-      <c r="E44" s="251" t="inlineStr">
+      <c r="E44" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F44" s="251" t="inlineStr">
+      <c r="F44" s="255" t="inlineStr">
         <is>
           <t>Verifica: 3.8359 × 2454.2 = 9414.2 ✓</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="251" t="inlineStr">
+      <c r="A45" s="255" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B45" s="251" t="inlineStr">
+      <c r="B45" s="255" t="inlineStr">
         <is>
           <t>Radier túnel H30</t>
         </is>
       </c>
-      <c r="C45" s="251" t="inlineStr">
+      <c r="C45" s="255" t="inlineStr">
         <is>
           <t>Σ (0.3315 m³/m × longitud_i) para i=1..8</t>
         </is>
       </c>
-      <c r="D45" s="251" t="n">
+      <c r="D45" s="255" t="n">
         <v>813.58</v>
       </c>
-      <c r="E45" s="251" t="inlineStr">
+      <c r="E45" s="255" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F45" s="251" t="inlineStr">
+      <c r="F45" s="255" t="inlineStr">
         <is>
           <t>Verifica: 0.3315 × 2454.2 = 813.6 ✓</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="251" t="inlineStr">
+      <c r="A46" s="255" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B46" s="251" t="inlineStr">
+      <c r="B46" s="255" t="inlineStr">
         <is>
           <t>Instalación cables</t>
         </is>
       </c>
-      <c r="C46" s="251" t="inlineStr">
+      <c r="C46" s="255" t="inlineStr">
         <is>
           <t>Σ (6 cables × longitud_i) para i=1..8</t>
         </is>
       </c>
-      <c r="D46" s="251" t="n">
-        <v>14725.2</v>
-      </c>
-      <c r="E46" s="251" t="inlineStr">
+      <c r="D46" s="255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="255" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="F46" s="251" t="inlineStr">
+      <c r="F46" s="255" t="inlineStr">
         <is>
           <t>⚠ Asumido: LAT 2×110kV = 2 circuitos × 3 fases</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="244" t="inlineStr">
+      <c r="A48" s="248" t="inlineStr">
         <is>
           <t>5. EQUIPAMIENTO ELÉCTRICO (Aporte STM — Sección 2 licitación)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="245" t="inlineStr">
+      <c r="A49" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B49" s="245" t="inlineStr">
+      <c r="B49" s="249" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="C49" s="245" t="inlineStr">
+      <c r="C49" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D49" s="245" t="inlineStr">
+      <c r="D49" s="249" t="inlineStr">
         <is>
           <t>Modelo / specs</t>
         </is>
       </c>
-      <c r="E49" s="245" t="inlineStr">
+      <c r="E49" s="249" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="F49" s="245" t="inlineStr">
+      <c r="F49" s="249" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="246" t="inlineStr">
+      <c r="A50" s="250" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B50" s="246" t="inlineStr">
+      <c r="B50" s="250" t="inlineStr">
         <is>
           <t>Jet Fan túnel</t>
         </is>
       </c>
-      <c r="C50" s="246" t="inlineStr">
+      <c r="C50" s="250" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D50" s="246" t="inlineStr">
+      <c r="D50" s="250" t="inlineStr">
         <is>
           <t>S&amp;P TJHT2/4-315-CN (0.8 kW, 24 N, 4500 m³/h)</t>
         </is>
       </c>
-      <c r="E50" s="246" t="inlineStr">
+      <c r="E50" s="250" t="inlineStr">
         <is>
           <t>Fan1 DM+70 → Fan23 DM+2380, cada 105 m</t>
         </is>
       </c>
-      <c r="F50" s="246" t="inlineStr">
+      <c r="F50" s="250" t="inlineStr">
         <is>
           <t>STM38109 §4.5 + Tabla 4.2 (REV.E 28-01-2026)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="246" t="inlineStr">
+      <c r="A51" s="250" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B51" s="246" t="inlineStr">
+      <c r="B51" s="250" t="inlineStr">
         <is>
           <t>Extractor pique</t>
         </is>
       </c>
-      <c r="C51" s="246" t="inlineStr">
+      <c r="C51" s="250" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D51" s="246" t="inlineStr">
+      <c r="D51" s="250" t="inlineStr">
         <is>
           <t>Soler-Palau TGT/6-1409 (37 kW, 132000 m³/h, Ø1409 mm)</t>
         </is>
       </c>
-      <c r="E51" s="246" t="inlineStr">
+      <c r="E51" s="250" t="inlineStr">
         <is>
           <t>bocas P1 (SS Vitacura) y P9 (SS Providencia)</t>
         </is>
       </c>
-      <c r="F51" s="246" t="inlineStr">
+      <c r="F51" s="250" t="inlineStr">
         <is>
           <t>STM38110 §3.1 + §3.14</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="244" t="inlineStr">
+      <c r="A53" s="248" t="inlineStr">
         <is>
           <t>6. SUPUESTOS CRÍTICOS Y VALIDACIONES PENDIENTES</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="245" t="inlineStr">
+      <c r="A54" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B54" s="245" t="inlineStr">
+      <c r="B54" s="249" t="inlineStr">
         <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C54" s="245" t="inlineStr">
+      <c r="C54" s="249" t="inlineStr">
         <is>
           <t>Valor usado</t>
         </is>
       </c>
-      <c r="D54" s="245" t="inlineStr">
+      <c r="D54" s="249" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="E54" s="245" t="inlineStr">
+      <c r="E54" s="249" t="inlineStr">
         <is>
           <t>Impacto si cambia</t>
         </is>
       </c>
-      <c r="F54" s="245" t="inlineStr">
+      <c r="F54" s="249" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="251" t="inlineStr">
+      <c r="A55" s="255" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B55" s="251" t="inlineStr">
+      <c r="B55" s="255" t="inlineStr">
         <is>
           <t>N° túneles paralelos</t>
         </is>
       </c>
-      <c r="C55" s="251" t="inlineStr">
+      <c r="C55" s="255" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" s="251" t="inlineStr">
+      <c r="D55" s="255" t="inlineStr">
         <is>
           <t>Diseño STM</t>
         </is>
       </c>
-      <c r="E55" s="251" t="inlineStr">
+      <c r="E55" s="255" t="inlineStr">
         <is>
           <t>Multiplicar Sec 5 por N</t>
         </is>
       </c>
-      <c r="F55" s="251" t="inlineStr">
+      <c r="F55" s="255" t="inlineStr">
         <is>
           <t>✓ Confirmado 1</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="251" t="inlineStr">
+      <c r="A56" s="255" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B56" s="251" t="inlineStr">
+      <c r="B56" s="255" t="inlineStr">
         <is>
           <t>N° cables LAT por tramo</t>
         </is>
       </c>
-      <c r="C56" s="251" t="inlineStr">
+      <c r="C56" s="255" t="inlineStr">
         <is>
           <t>6 (2×3 fases)</t>
         </is>
       </c>
-      <c r="D56" s="251" t="inlineStr">
+      <c r="D56" s="255" t="inlineStr">
         <is>
           <t>Estándar LAT 2×110kV</t>
         </is>
       </c>
-      <c r="E56" s="251" t="inlineStr">
+      <c r="E56" s="255" t="inlineStr">
         <is>
           <t>Ajustar 5.x.8 proporcional</t>
         </is>
       </c>
-      <c r="F56" s="251" t="inlineStr">
+      <c r="F56" s="255" t="inlineStr">
         <is>
           <t>⚠ Confirmar plano eléctrico</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="251" t="inlineStr">
+      <c r="A57" s="255" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B57" s="251" t="inlineStr">
+      <c r="B57" s="255" t="inlineStr">
         <is>
           <t>Profundidad P9</t>
         </is>
       </c>
-      <c r="C57" s="251" t="inlineStr">
+      <c r="C57" s="255" t="inlineStr">
         <is>
           <t>9.06 m (NV)</t>
         </is>
       </c>
-      <c r="D57" s="251" t="inlineStr">
+      <c r="D57" s="255" t="inlineStr">
         <is>
           <t>STM38023 vs STM38109 (9.67m)</t>
         </is>
       </c>
-      <c r="E57" s="251" t="inlineStr">
+      <c r="E57" s="255" t="inlineStr">
         <is>
           <t>Δ excav P9 = 7.7 m³</t>
         </is>
       </c>
-      <c r="F57" s="251" t="inlineStr">
+      <c r="F57" s="255" t="inlineStr">
         <is>
           <t>⚠ Discrepancia 0.61m</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="251" t="inlineStr">
+      <c r="A58" s="255" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B58" s="251" t="inlineStr">
+      <c r="B58" s="255" t="inlineStr">
         <is>
           <t>Diámetro liner interior</t>
         </is>
       </c>
-      <c r="C58" s="251" t="inlineStr">
+      <c r="C58" s="255" t="inlineStr">
         <is>
           <t>2.21 m</t>
         </is>
       </c>
-      <c r="D58" s="251" t="inlineStr">
+      <c r="D58" s="255" t="inlineStr">
         <is>
           <t>STM38136 vs STM38109 (2.10m)</t>
         </is>
       </c>
-      <c r="E58" s="251" t="inlineStr">
+      <c r="E58" s="255" t="inlineStr">
         <is>
           <t>Δ sección = 0.38 m² (10%)</t>
         </is>
       </c>
-      <c r="F58" s="251" t="inlineStr">
+      <c r="F58" s="255" t="inlineStr">
         <is>
           <t>✓ 2.21m incluye espesor anillos</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="251" t="inlineStr">
+      <c r="A59" s="255" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B59" s="251" t="inlineStr">
+      <c r="B59" s="255" t="inlineStr">
         <is>
           <t>Longitud túnel total</t>
         </is>
       </c>
-      <c r="C59" s="251" t="inlineStr">
+      <c r="C59" s="255" t="inlineStr">
         <is>
           <t>2454.2 m</t>
         </is>
       </c>
-      <c r="D59" s="251" t="inlineStr">
+      <c r="D59" s="255" t="inlineStr">
         <is>
           <t>STM38020-23 suma DM</t>
         </is>
       </c>
-      <c r="E59" s="251" t="inlineStr">
+      <c r="E59" s="255" t="inlineStr">
         <is>
           <t>STM38109 redondea a 2450m</t>
         </is>
       </c>
-      <c r="F59" s="251" t="inlineStr">
+      <c r="F59" s="255" t="inlineStr">
         <is>
           <t>✓ Diferencia 4.2m (0.17%)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="251" t="inlineStr">
+      <c r="A60" s="255" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B60" s="251" t="inlineStr">
+      <c r="B60" s="255" t="inlineStr">
         <is>
           <t>Cantidades 4.x.10-12 (shotcrete/malla/pernos)</t>
         </is>
       </c>
-      <c r="C60" s="251" t="inlineStr">
+      <c r="C60" s="255" t="inlineStr">
         <is>
           <t>No cubicado</t>
         </is>
       </c>
-      <c r="D60" s="251" t="inlineStr">
+      <c r="D60" s="255" t="inlineStr">
         <is>
           <t>Requiere RMR/Q rock mass</t>
         </is>
       </c>
-      <c r="E60" s="251" t="inlineStr">
+      <c r="E60" s="255" t="inlineStr">
         <is>
           <t>Eventual según geotecnia</t>
         </is>
       </c>
-      <c r="F60" s="251" t="inlineStr">
+      <c r="F60" s="255" t="inlineStr">
         <is>
           <t>⚠ Pendiente STM38019 RMR</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="251" t="inlineStr">
+      <c r="A61" s="255" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B61" s="251" t="inlineStr">
+      <c r="B61" s="255" t="inlineStr">
         <is>
           <t>UF referencial</t>
         </is>
       </c>
-      <c r="C61" s="251" t="inlineStr">
+      <c r="C61" s="255" t="inlineStr">
         <is>
           <t>38.500 CLP</t>
         </is>
       </c>
-      <c r="D61" s="251" t="inlineStr">
+      <c r="D61" s="255" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="E61" s="251" t="inlineStr">
+      <c r="E61" s="255" t="inlineStr">
         <is>
           <t>Actualizar al mes oferta</t>
         </is>
       </c>
-      <c r="F61" s="251" t="inlineStr">
+      <c r="F61" s="255" t="inlineStr">
         <is>
           <t>✓ Configurable</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="251" t="inlineStr">
+      <c r="A62" s="255" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B62" s="251" t="inlineStr">
+      <c r="B62" s="255" t="inlineStr">
         <is>
           <t>Altura excavación = profundidad NV</t>
         </is>
       </c>
-      <c r="C62" s="251" t="inlineStr">
+      <c r="C62" s="255" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="D62" s="251" t="inlineStr">
+      <c r="D62" s="255" t="inlineStr">
         <is>
           <t>Convención técnica</t>
         </is>
       </c>
-      <c r="E62" s="251" t="inlineStr">
+      <c r="E62" s="255" t="inlineStr">
         <is>
           <t>Si sump existe → +volumen</t>
         </is>
       </c>
-      <c r="F62" s="251" t="inlineStr">
+      <c r="F62" s="255" t="inlineStr">
         <is>
           <t>⚠ STM38023 nota 'Nivel -3.50' en P9</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="244" t="inlineStr">
+      <c r="A64" s="248" t="inlineStr">
         <is>
           <t>7. TRAZABILIDAD DE FUENTES (documentos consultados)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="245" t="inlineStr">
+      <c r="A65" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B65" s="245" t="inlineStr">
+      <c r="B65" s="249" t="inlineStr">
         <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="C65" s="245" t="inlineStr">
+      <c r="C65" s="249" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
       </c>
-      <c r="D65" s="245" t="inlineStr">
+      <c r="D65" s="249" t="inlineStr">
         <is>
           <t>Datos extraídos</t>
         </is>
       </c>
-      <c r="E65" s="245" t="inlineStr">
+      <c r="E65" s="249" t="inlineStr">
         <is>
           <t>Hoja relevante</t>
         </is>
       </c>
-      <c r="F65" s="245" t="inlineStr">
+      <c r="F65" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="251" t="inlineStr">
+      <c r="A66" s="255" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B66" s="251" t="inlineStr">
+      <c r="B66" s="255" t="inlineStr">
         <is>
           <t>STM38020 Planta y Perfil</t>
         </is>
       </c>
-      <c r="C66" s="251" t="inlineStr">
+      <c r="C66" s="255" t="inlineStr">
         <is>
           <t>REV.0</t>
         </is>
       </c>
-      <c r="D66" s="251" t="inlineStr">
+      <c r="D66" s="255" t="inlineStr">
         <is>
           <t>P1, P2, P3 NV + DM tramos T1-T3</t>
         </is>
       </c>
-      <c r="E66" s="251" t="inlineStr">
+      <c r="E66" s="255" t="inlineStr">
         <is>
           <t>Detalle Costo Directo</t>
         </is>
       </c>
-      <c r="F66" s="251" t="inlineStr"/>
+      <c r="F66" s="255" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="251" t="inlineStr">
+      <c r="A67" s="255" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B67" s="251" t="inlineStr">
+      <c r="B67" s="255" t="inlineStr">
         <is>
           <t>STM38021 Planta y Perfil</t>
         </is>
       </c>
-      <c r="C67" s="251" t="inlineStr">
+      <c r="C67" s="255" t="inlineStr">
         <is>
           <t>REV.0</t>
         </is>
       </c>
-      <c r="D67" s="251" t="inlineStr">
+      <c r="D67" s="255" t="inlineStr">
         <is>
           <t>P4, P5 NV + DM tramos T3-T5</t>
         </is>
       </c>
-      <c r="E67" s="251" t="inlineStr">
+      <c r="E67" s="255" t="inlineStr">
         <is>
           <t>Detalle Costo Directo</t>
         </is>
       </c>
-      <c r="F67" s="251" t="inlineStr"/>
+      <c r="F67" s="255" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="251" t="inlineStr">
+      <c r="A68" s="255" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B68" s="251" t="inlineStr">
+      <c r="B68" s="255" t="inlineStr">
         <is>
           <t>STM38022 Planta y Perfil</t>
         </is>
       </c>
-      <c r="C68" s="251" t="inlineStr">
+      <c r="C68" s="255" t="inlineStr">
         <is>
           <t>REV.0</t>
         </is>
       </c>
-      <c r="D68" s="251" t="inlineStr">
+      <c r="D68" s="255" t="inlineStr">
         <is>
           <t>P6, P7 NV + DM tramos T5-T7</t>
         </is>
       </c>
-      <c r="E68" s="251" t="inlineStr">
+      <c r="E68" s="255" t="inlineStr">
         <is>
           <t>Detalle Costo Directo</t>
         </is>
       </c>
-      <c r="F68" s="251" t="inlineStr"/>
+      <c r="F68" s="255" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="251" t="inlineStr">
+      <c r="A69" s="255" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="B69" s="251" t="inlineStr">
+      <c r="B69" s="255" t="inlineStr">
         <is>
           <t>STM38023 Planta y Perfil</t>
         </is>
       </c>
-      <c r="C69" s="251" t="inlineStr">
+      <c r="C69" s="255" t="inlineStr">
         <is>
           <t>REV.0</t>
         </is>
       </c>
-      <c r="D69" s="251" t="inlineStr">
+      <c r="D69" s="255" t="inlineStr">
         <is>
           <t>P8, P9 NV + DM tramos T7-T8</t>
         </is>
       </c>
-      <c r="E69" s="251" t="inlineStr">
+      <c r="E69" s="255" t="inlineStr">
         <is>
           <t>Detalle Costo Directo</t>
         </is>
       </c>
-      <c r="F69" s="251" t="inlineStr"/>
+      <c r="F69" s="255" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="251" t="inlineStr">
+      <c r="A70" s="255" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B70" s="251" t="inlineStr">
+      <c r="B70" s="255" t="inlineStr">
         <is>
           <t>STM38109 Memoria Ventilación</t>
         </is>
       </c>
-      <c r="C70" s="251" t="inlineStr">
+      <c r="C70" s="255" t="inlineStr">
         <is>
           <t>REV.E 28-01-2026</t>
         </is>
       </c>
-      <c r="D70" s="251" t="inlineStr">
+      <c r="D70" s="255" t="inlineStr">
         <is>
           <t>23 jet fans S&amp;P TJHT2/4-315-CN, ubicación Tabla 4.2</t>
         </is>
       </c>
-      <c r="E70" s="251" t="inlineStr">
+      <c r="E70" s="255" t="inlineStr">
         <is>
           <t>Sec 5 supuestos</t>
         </is>
       </c>
-      <c r="F70" s="251" t="inlineStr"/>
+      <c r="F70" s="255" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="251" t="inlineStr">
+      <c r="A71" s="255" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B71" s="251" t="inlineStr">
+      <c r="B71" s="255" t="inlineStr">
         <is>
           <t>STM38110 ETP Equipos Ventilación</t>
         </is>
       </c>
-      <c r="C71" s="251" t="inlineStr">
+      <c r="C71" s="255" t="inlineStr">
         <is>
           <t>REV.0 14-11-2025</t>
         </is>
       </c>
-      <c r="D71" s="251" t="inlineStr">
+      <c r="D71" s="255" t="inlineStr">
         <is>
           <t>2 extractores Soler-Palau TGT/6-1409, modelo jet fan</t>
         </is>
       </c>
-      <c r="E71" s="251" t="inlineStr">
+      <c r="E71" s="255" t="inlineStr">
         <is>
           <t>Sec 5 supuestos</t>
         </is>
       </c>
-      <c r="F71" s="251" t="inlineStr"/>
+      <c r="F71" s="255" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="251" t="inlineStr">
+      <c r="A72" s="255" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="B72" s="251" t="inlineStr">
+      <c r="B72" s="255" t="inlineStr">
         <is>
           <t>STM38019 Geotécnica</t>
         </is>
       </c>
-      <c r="C72" s="251" t="inlineStr">
+      <c r="C72" s="255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D72" s="251" t="inlineStr">
+      <c r="D72" s="255" t="inlineStr">
         <is>
           <t>Estratigrafía H1-H3 (Relleno/Grava 2°/Grava 1°)</t>
         </is>
       </c>
-      <c r="E72" s="251" t="inlineStr">
+      <c r="E72" s="255" t="inlineStr">
         <is>
           <t>Pendiente RMR para 4.x.10-12</t>
         </is>
       </c>
-      <c r="F72" s="251" t="inlineStr"/>
+      <c r="F72" s="255" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="251" t="inlineStr">
+      <c r="A73" s="255" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="B73" s="251" t="inlineStr">
+      <c r="B73" s="255" t="inlineStr">
         <is>
           <t>STM38136 Planos eléctricos</t>
         </is>
       </c>
-      <c r="C73" s="251" t="inlineStr">
+      <c r="C73" s="255" t="inlineStr">
         <is>
           <t>REV.1 06/04/2026</t>
         </is>
       </c>
-      <c r="D73" s="251" t="inlineStr">
+      <c r="D73" s="255" t="inlineStr">
         <is>
           <t>Ø interior pique 4.0m, Ø interior liner 2.21m</t>
         </is>
       </c>
-      <c r="E73" s="251" t="inlineStr">
+      <c r="E73" s="255" t="inlineStr">
         <is>
           <t>Sec 1 constantes</t>
         </is>
       </c>
-      <c r="F73" s="251" t="inlineStr"/>
+      <c r="F73" s="255" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="251" t="inlineStr">
+      <c r="A74" s="255" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="B74" s="251" t="inlineStr">
+      <c r="B74" s="255" t="inlineStr">
         <is>
           <t>BAE Licitación 2025-25-TX-SS-RM</t>
         </is>
       </c>
-      <c r="C74" s="251" t="inlineStr">
+      <c r="C74" s="255" t="inlineStr">
         <is>
           <t>REV.0 13/04/2026</t>
         </is>
       </c>
-      <c r="D74" s="251" t="inlineStr">
+      <c r="D74" s="255" t="inlineStr">
         <is>
           <t>Estructura items 4.x y 5.x</t>
         </is>
       </c>
-      <c r="E74" s="251" t="inlineStr">
+      <c r="E74" s="255" t="inlineStr">
         <is>
           <t>A) Detalle</t>
         </is>
       </c>
-      <c r="F74" s="251" t="inlineStr"/>
+      <c r="F74" s="255" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="251" t="inlineStr">
+      <c r="A75" s="255" t="inlineStr">
         <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="B75" s="251" t="inlineStr">
+      <c r="B75" s="255" t="inlineStr">
         <is>
           <t>IF SS Vitacura</t>
         </is>
       </c>
-      <c r="C75" s="251" t="inlineStr">
+      <c r="C75" s="255" t="inlineStr">
         <is>
           <t>20251009 (3 etapas)</t>
         </is>
       </c>
-      <c r="D75" s="251" t="inlineStr">
+      <c r="D75" s="255" t="inlineStr">
         <is>
           <t>Composición Instalación de Faenas</t>
         </is>
       </c>
-      <c r="E75" s="251" t="inlineStr">
+      <c r="E75" s="255" t="inlineStr">
         <is>
           <t>Sec 3 supuestos suma alzada</t>
         </is>
       </c>
-      <c r="F75" s="251" t="inlineStr"/>
+      <c r="F75" s="255" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="244" t="inlineStr">
+      <c r="A77" s="248" t="inlineStr">
         <is>
           <t>8. RESUMEN TOTALES CUBICADOS</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="245" t="inlineStr">
+      <c r="A78" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B78" s="245" t="inlineStr">
+      <c r="B78" s="249" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C78" s="245" t="inlineStr">
+      <c r="C78" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D78" s="245" t="inlineStr">
+      <c r="D78" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="E78" s="245" t="inlineStr">
+      <c r="E78" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F78" s="245" t="inlineStr">
+      <c r="F78" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="246" t="inlineStr">
+      <c r="A79" s="250" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B79" s="246" t="inlineStr">
+      <c r="B79" s="250" t="inlineStr">
         <is>
           <t>Excavación piques (suma)</t>
         </is>
       </c>
-      <c r="C79" s="246" t="n">
+      <c r="C79" s="250" t="n">
         <v>1770.34</v>
       </c>
-      <c r="D79" s="246" t="inlineStr">
+      <c r="D79" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E79" s="246" t="inlineStr"/>
-      <c r="F79" s="246" t="inlineStr"/>
+      <c r="E79" s="250" t="inlineStr"/>
+      <c r="F79" s="250" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="246" t="inlineStr">
+      <c r="A80" s="250" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B80" s="246" t="inlineStr">
+      <c r="B80" s="250" t="inlineStr">
         <is>
           <t>Excavación túnel (suma)</t>
         </is>
       </c>
-      <c r="C80" s="246" t="n">
+      <c r="C80" s="250" t="n">
         <v>9414.219999999999</v>
       </c>
-      <c r="D80" s="246" t="inlineStr">
+      <c r="D80" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E80" s="246" t="inlineStr"/>
-      <c r="F80" s="246" t="inlineStr"/>
+      <c r="E80" s="250" t="inlineStr"/>
+      <c r="F80" s="250" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="246" t="inlineStr">
+      <c r="A81" s="250" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B81" s="246" t="inlineStr">
+      <c r="B81" s="250" t="inlineStr">
         <is>
           <t>Liner pique (suma profundidades)</t>
         </is>
       </c>
-      <c r="C81" s="246" t="n">
+      <c r="C81" s="250" t="n">
         <v>140.9</v>
       </c>
-      <c r="D81" s="246" t="inlineStr">
+      <c r="D81" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E81" s="246" t="inlineStr"/>
-      <c r="F81" s="246" t="inlineStr"/>
+      <c r="E81" s="250" t="inlineStr"/>
+      <c r="F81" s="250" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="246" t="inlineStr">
+      <c r="A82" s="250" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B82" s="246" t="inlineStr">
+      <c r="B82" s="250" t="inlineStr">
         <is>
           <t>Liner túnel (longitud total)</t>
         </is>
       </c>
-      <c r="C82" s="246" t="n">
+      <c r="C82" s="250" t="n">
         <v>2454.2</v>
       </c>
-      <c r="D82" s="246" t="inlineStr">
+      <c r="D82" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E82" s="246" t="inlineStr"/>
-      <c r="F82" s="246" t="inlineStr"/>
+      <c r="E82" s="250" t="inlineStr"/>
+      <c r="F82" s="250" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="246" t="inlineStr">
+      <c r="A83" s="250" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B83" s="246" t="inlineStr">
+      <c r="B83" s="250" t="inlineStr">
         <is>
           <t>Radier H30</t>
         </is>
       </c>
-      <c r="C83" s="246" t="n">
+      <c r="C83" s="250" t="n">
         <v>813.58</v>
       </c>
-      <c r="D83" s="246" t="inlineStr">
+      <c r="D83" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E83" s="246" t="inlineStr"/>
-      <c r="F83" s="246" t="inlineStr"/>
+      <c r="E83" s="250" t="inlineStr"/>
+      <c r="F83" s="250" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="246" t="inlineStr">
+      <c r="A84" s="250" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="B84" s="246" t="inlineStr">
+      <c r="B84" s="250" t="inlineStr">
         <is>
           <t>Cables instalados (6 × longitud)</t>
         </is>
       </c>
-      <c r="C84" s="246" t="n">
-        <v>14725.2</v>
-      </c>
-      <c r="D84" s="246" t="inlineStr">
+      <c r="C84" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="250" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E84" s="246" t="inlineStr"/>
-      <c r="F84" s="246" t="inlineStr"/>
+      <c r="E84" s="250" t="inlineStr"/>
+      <c r="F84" s="250" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="246" t="inlineStr">
+      <c r="A85" s="250" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="B85" s="246" t="inlineStr">
+      <c r="B85" s="250" t="inlineStr">
         <is>
           <t>Estructura cables SS</t>
         </is>
       </c>
-      <c r="C85" s="246" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" s="246" t="inlineStr">
+      <c r="C85" s="250" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D85" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E85" s="246" t="inlineStr">
+      <c r="E85" s="250" t="inlineStr">
         <is>
           <t>(solo P1+P9)</t>
         </is>
       </c>
-      <c r="F85" s="246" t="inlineStr"/>
+      <c r="F85" s="250" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="246" t="inlineStr">
+      <c r="A86" s="250" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="B86" s="246" t="inlineStr">
+      <c r="B86" s="250" t="inlineStr">
         <is>
           <t>Escalas+plataformas</t>
         </is>
       </c>
-      <c r="C86" s="246" t="n">
+      <c r="C86" s="250" t="n">
         <v>9</v>
       </c>
-      <c r="D86" s="246" t="inlineStr">
+      <c r="D86" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E86" s="246" t="inlineStr"/>
-      <c r="F86" s="246" t="inlineStr"/>
+      <c r="E86" s="250" t="inlineStr"/>
+      <c r="F86" s="250" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="246" t="inlineStr">
+      <c r="A87" s="250" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="B87" s="246" t="inlineStr">
+      <c r="B87" s="250" t="inlineStr">
         <is>
           <t>Brocales definitivos</t>
         </is>
       </c>
-      <c r="C87" s="246" t="n">
+      <c r="C87" s="250" t="n">
         <v>9</v>
       </c>
-      <c r="D87" s="246" t="inlineStr">
+      <c r="D87" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E87" s="246" t="inlineStr"/>
-      <c r="F87" s="246" t="inlineStr"/>
+      <c r="E87" s="250" t="inlineStr"/>
+      <c r="F87" s="250" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/output/licitacion_vitacura.xlsx
+++ b/output/licitacion_vitacura.xlsx
@@ -618,7 +618,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1355,6 +1355,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15879,7 +15882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16849,12 +16852,12 @@
       </c>
       <c r="B41" s="255" t="inlineStr">
         <is>
-          <t>Montaje escalas+plataformas</t>
+          <t>Refuerzo losa anillo fondo (.4)</t>
         </is>
       </c>
       <c r="C41" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques (Aporte STM)</t>
+          <t>1 gl × 9 piques (suma alzada por pique)</t>
         </is>
       </c>
       <c r="D41" s="255" t="n">
@@ -16867,7 +16870,7 @@
       </c>
       <c r="F41" s="255" t="inlineStr">
         <is>
-          <t>✓ Una unidad global por pique</t>
+          <t>Cant 1 gl/pique — precio cotizar</t>
         </is>
       </c>
     </row>
@@ -16879,16 +16882,16 @@
       </c>
       <c r="B42" s="255" t="inlineStr">
         <is>
-          <t>Brocal definitivo</t>
+          <t>Dren / Terminaciones / Cobertura / Refuerzo apertura</t>
         </is>
       </c>
       <c r="C42" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques</t>
+          <t>1 gl × 9 piques cada uno (items .5, .6, .7, .9)</t>
         </is>
       </c>
       <c r="D42" s="255" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E42" s="255" t="inlineStr">
         <is>
@@ -16897,7 +16900,7 @@
       </c>
       <c r="F42" s="255" t="inlineStr">
         <is>
-          <t>P1/P9 → ítem .15; P2-8 → ítem .14</t>
+          <t>4 items × 9 piques = 36 gl en total</t>
         </is>
       </c>
     </row>
@@ -16909,16 +16912,16 @@
       </c>
       <c r="B43" s="255" t="inlineStr">
         <is>
-          <t>Montaje estructura cables (SS)</t>
+          <t>Montaje escalas+plataformas (.8)</t>
         </is>
       </c>
       <c r="C43" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 2 piques SS (P1 y P9)</t>
+          <t>1 gl × 9 piques (Aporte STM)</t>
         </is>
       </c>
       <c r="D43" s="255" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="E43" s="255" t="inlineStr">
         <is>
@@ -16927,84 +16930,84 @@
       </c>
       <c r="F43" s="255" t="inlineStr">
         <is>
-          <t>Solo SS Vitacura + SS Providencia</t>
+          <t>✓ Una unidad global por pique</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="255" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B44" s="255" t="inlineStr">
         <is>
-          <t>Excavación túnel</t>
+          <t>Estructura soporte cables SS (.13)</t>
         </is>
       </c>
       <c r="C44" s="255" t="inlineStr">
         <is>
-          <t>Σ (3.8359 m² × longitud_i) para i=1..8</t>
+          <t>500 kg × 2 piques (P1, P9) — estimado acero galvanizado</t>
         </is>
       </c>
       <c r="D44" s="255" t="n">
-        <v>9414.219999999999</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="255" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F44" s="255" t="inlineStr">
         <is>
-          <t>Verifica: 3.8359 × 2454.2 = 9414.2 ✓</t>
+          <t>Solo SS Vitacura + SS Providencia</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="255" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B45" s="255" t="inlineStr">
         <is>
-          <t>Radier túnel H30</t>
+          <t>Brocal definitivo (.14 / .15)</t>
         </is>
       </c>
       <c r="C45" s="255" t="inlineStr">
         <is>
-          <t>Σ (0.3315 m³/m × longitud_i) para i=1..8</t>
+          <t>1 gl × 9 piques</t>
         </is>
       </c>
       <c r="D45" s="255" t="n">
-        <v>813.58</v>
+        <v>9</v>
       </c>
       <c r="E45" s="255" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="F45" s="255" t="inlineStr">
         <is>
-          <t>Verifica: 0.3315 × 2454.2 = 813.6 ✓</t>
+          <t>P1/P9 → ítem .15; P2-8 → ítem .14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="255" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B46" s="255" t="inlineStr">
         <is>
-          <t>Instalación cables</t>
+          <t>Shotcrete / Malla / Pernos (.10, .11, .12)</t>
         </is>
       </c>
       <c r="C46" s="255" t="inlineStr">
         <is>
-          <t>Σ (6 cables × longitud_i) para i=1..8</t>
+          <t>Sin cant — depende RMR geotecnico (STM38019 pendiente)</t>
         </is>
       </c>
       <c r="D46" s="255" t="n">
@@ -17012,122 +17015,169 @@
       </c>
       <c r="E46" s="255" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="255" t="inlineStr">
         <is>
-          <t>⚠ Asumido: LAT 2×110kV = 2 circuitos × 3 fases</t>
+          <t>⚠ Precios listados, cantidades en blanco</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="255" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B47" s="255" t="inlineStr">
+        <is>
+          <t>Excavación túnel</t>
+        </is>
+      </c>
+      <c r="C47" s="255" t="inlineStr">
+        <is>
+          <t>Σ (3.8359 m² × longitud_i) para i=1..8</t>
+        </is>
+      </c>
+      <c r="D47" s="255" t="n">
+        <v>9414.219999999999</v>
+      </c>
+      <c r="E47" s="255" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F47" s="255" t="inlineStr">
+        <is>
+          <t>Verifica: 3.8359 × 2454.2 = 9414.2 ✓</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="248" t="inlineStr">
-        <is>
-          <t>5. EQUIPAMIENTO ELÉCTRICO (Aporte STM — Sección 2 licitación)</t>
+      <c r="A48" s="255" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B48" s="255" t="inlineStr">
+        <is>
+          <t>Radier túnel H30</t>
+        </is>
+      </c>
+      <c r="C48" s="255" t="inlineStr">
+        <is>
+          <t>Σ (0.3315 m³/m × longitud_i) para i=1..8</t>
+        </is>
+      </c>
+      <c r="D48" s="255" t="n">
+        <v>813.58</v>
+      </c>
+      <c r="E48" s="255" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F48" s="255" t="inlineStr">
+        <is>
+          <t>Verifica: 0.3315 × 2454.2 = 813.6 ✓</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="249" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B49" s="249" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="C49" s="249" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="D49" s="249" t="inlineStr">
-        <is>
-          <t>Modelo / specs</t>
-        </is>
-      </c>
-      <c r="E49" s="249" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="F49" s="249" t="inlineStr">
-        <is>
-          <t>Fuente</t>
+      <c r="A49" s="255" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B49" s="255" t="inlineStr">
+        <is>
+          <t>Monitoreo de Pernos (.8)</t>
+        </is>
+      </c>
+      <c r="C49" s="255" t="inlineStr">
+        <is>
+          <t>1 gl × 8 tramos</t>
+        </is>
+      </c>
+      <c r="D49" s="255" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="255" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="F49" s="255" t="inlineStr">
+        <is>
+          <t>Item .8 del template (NO instalación cables)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="250" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B50" s="250" t="inlineStr">
-        <is>
-          <t>Jet Fan túnel</t>
-        </is>
-      </c>
-      <c r="C50" s="250" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D50" s="250" t="inlineStr">
-        <is>
-          <t>S&amp;P TJHT2/4-315-CN (0.8 kW, 24 N, 4500 m³/h)</t>
-        </is>
-      </c>
-      <c r="E50" s="250" t="inlineStr">
-        <is>
-          <t>Fan1 DM+70 → Fan23 DM+2380, cada 105 m</t>
-        </is>
-      </c>
-      <c r="F50" s="250" t="inlineStr">
-        <is>
-          <t>STM38109 §4.5 + Tabla 4.2 (REV.E 28-01-2026)</t>
+      <c r="A50" s="255" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B50" s="255" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables AT túnel (.12)</t>
+        </is>
+      </c>
+      <c r="C50" s="255" t="inlineStr">
+        <is>
+          <t>20 kg/ml × longitud_i para i=1..8 (acero galvanizado)</t>
+        </is>
+      </c>
+      <c r="D50" s="255" t="n">
+        <v>49084</v>
+      </c>
+      <c r="E50" s="255" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F50" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Estimado 20 kg/ml — confirmar diseño bandejas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="250" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B51" s="250" t="inlineStr">
-        <is>
-          <t>Extractor pique</t>
-        </is>
-      </c>
-      <c r="C51" s="250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D51" s="250" t="inlineStr">
-        <is>
-          <t>Soler-Palau TGT/6-1409 (37 kW, 132000 m³/h, Ø1409 mm)</t>
-        </is>
-      </c>
-      <c r="E51" s="250" t="inlineStr">
-        <is>
-          <t>bocas P1 (SS Vitacura) y P9 (SS Providencia)</t>
-        </is>
-      </c>
-      <c r="F51" s="250" t="inlineStr">
-        <is>
-          <t>STM38110 §3.1 + §3.14</t>
+      <c r="A51" s="255" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B51" s="255" t="inlineStr">
+        <is>
+          <t>Pernos frente / Shotcrete / Paraguas (.4, .5, .6)</t>
+        </is>
+      </c>
+      <c r="C51" s="255" t="inlineStr">
+        <is>
+          <t>Cantidades del template original (eventuales)</t>
+        </is>
+      </c>
+      <c r="D51" s="255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="255" t="inlineStr">
+        <is>
+          <t>Cant 'eventual' del cuadro precios STM</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="248" t="inlineStr">
         <is>
-          <t>6. SUPUESTOS CRÍTICOS Y VALIDACIONES PENDIENTES</t>
+          <t>5. EQUIPAMIENTO ELÉCTRICO (Aporte STM — Sección 2 licitación)</t>
         </is>
       </c>
     </row>
@@ -17139,858 +17189,1577 @@
       </c>
       <c r="B54" s="249" t="inlineStr">
         <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C54" s="249" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="D54" s="249" t="inlineStr">
+        <is>
+          <t>Modelo / specs</t>
+        </is>
+      </c>
+      <c r="E54" s="249" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="F54" s="249" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="250" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B55" s="250" t="inlineStr">
+        <is>
+          <t>Jet Fan túnel</t>
+        </is>
+      </c>
+      <c r="C55" s="250" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D55" s="250" t="inlineStr">
+        <is>
+          <t>S&amp;P TJHT2/4-315-CN (0.8 kW, 24 N, 4500 m³/h)</t>
+        </is>
+      </c>
+      <c r="E55" s="250" t="inlineStr">
+        <is>
+          <t>Fan1 DM+70 → Fan23 DM+2380, cada 105 m</t>
+        </is>
+      </c>
+      <c r="F55" s="250" t="inlineStr">
+        <is>
+          <t>STM38109 §4.5 + Tabla 4.2 (REV.E 28-01-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="250" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B56" s="250" t="inlineStr">
+        <is>
+          <t>Extractor pique</t>
+        </is>
+      </c>
+      <c r="C56" s="250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" s="250" t="inlineStr">
+        <is>
+          <t>Soler-Palau TGT/6-1409 (37 kW, 132000 m³/h, Ø1409 mm)</t>
+        </is>
+      </c>
+      <c r="E56" s="250" t="inlineStr">
+        <is>
+          <t>bocas P1 (SS Vitacura) y P9 (SS Providencia)</t>
+        </is>
+      </c>
+      <c r="F56" s="250" t="inlineStr">
+        <is>
+          <t>STM38110 §3.1 + §3.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="248" t="inlineStr">
+        <is>
+          <t>6. SUPUESTOS CRÍTICOS Y VALIDACIONES PENDIENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="249" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B59" s="249" t="inlineStr">
+        <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C54" s="249" t="inlineStr">
+      <c r="C59" s="249" t="inlineStr">
         <is>
           <t>Valor usado</t>
         </is>
       </c>
-      <c r="D54" s="249" t="inlineStr">
+      <c r="D59" s="249" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="E54" s="249" t="inlineStr">
+      <c r="E59" s="249" t="inlineStr">
         <is>
           <t>Impacto si cambia</t>
         </is>
       </c>
-      <c r="F54" s="249" t="inlineStr">
+      <c r="F59" s="249" t="inlineStr">
         <is>
           <t>Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="255" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B55" s="255" t="inlineStr">
-        <is>
-          <t>N° túneles paralelos</t>
-        </is>
-      </c>
-      <c r="C55" s="255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D55" s="255" t="inlineStr">
-        <is>
-          <t>Diseño STM</t>
-        </is>
-      </c>
-      <c r="E55" s="255" t="inlineStr">
-        <is>
-          <t>Multiplicar Sec 5 por N</t>
-        </is>
-      </c>
-      <c r="F55" s="255" t="inlineStr">
-        <is>
-          <t>✓ Confirmado 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="255" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B56" s="255" t="inlineStr">
-        <is>
-          <t>N° cables LAT por tramo</t>
-        </is>
-      </c>
-      <c r="C56" s="255" t="inlineStr">
-        <is>
-          <t>6 (2×3 fases)</t>
-        </is>
-      </c>
-      <c r="D56" s="255" t="inlineStr">
-        <is>
-          <t>Estándar LAT 2×110kV</t>
-        </is>
-      </c>
-      <c r="E56" s="255" t="inlineStr">
-        <is>
-          <t>Ajustar 5.x.8 proporcional</t>
-        </is>
-      </c>
-      <c r="F56" s="255" t="inlineStr">
-        <is>
-          <t>⚠ Confirmar plano eléctrico</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="255" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B57" s="255" t="inlineStr">
-        <is>
-          <t>Profundidad P9</t>
-        </is>
-      </c>
-      <c r="C57" s="255" t="inlineStr">
-        <is>
-          <t>9.06 m (NV)</t>
-        </is>
-      </c>
-      <c r="D57" s="255" t="inlineStr">
-        <is>
-          <t>STM38023 vs STM38109 (9.67m)</t>
-        </is>
-      </c>
-      <c r="E57" s="255" t="inlineStr">
-        <is>
-          <t>Δ excav P9 = 7.7 m³</t>
-        </is>
-      </c>
-      <c r="F57" s="255" t="inlineStr">
-        <is>
-          <t>⚠ Discrepancia 0.61m</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="255" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="B58" s="255" t="inlineStr">
-        <is>
-          <t>Diámetro liner interior</t>
-        </is>
-      </c>
-      <c r="C58" s="255" t="inlineStr">
-        <is>
-          <t>2.21 m</t>
-        </is>
-      </c>
-      <c r="D58" s="255" t="inlineStr">
-        <is>
-          <t>STM38136 vs STM38109 (2.10m)</t>
-        </is>
-      </c>
-      <c r="E58" s="255" t="inlineStr">
-        <is>
-          <t>Δ sección = 0.38 m² (10%)</t>
-        </is>
-      </c>
-      <c r="F58" s="255" t="inlineStr">
-        <is>
-          <t>✓ 2.21m incluye espesor anillos</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="255" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="B59" s="255" t="inlineStr">
-        <is>
-          <t>Longitud túnel total</t>
-        </is>
-      </c>
-      <c r="C59" s="255" t="inlineStr">
-        <is>
-          <t>2454.2 m</t>
-        </is>
-      </c>
-      <c r="D59" s="255" t="inlineStr">
-        <is>
-          <t>STM38020-23 suma DM</t>
-        </is>
-      </c>
-      <c r="E59" s="255" t="inlineStr">
-        <is>
-          <t>STM38109 redondea a 2450m</t>
-        </is>
-      </c>
-      <c r="F59" s="255" t="inlineStr">
-        <is>
-          <t>✓ Diferencia 4.2m (0.17%)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="255" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B60" s="255" t="inlineStr">
         <is>
-          <t>Cantidades 4.x.10-12 (shotcrete/malla/pernos)</t>
+          <t>N° túneles paralelos</t>
         </is>
       </c>
       <c r="C60" s="255" t="inlineStr">
         <is>
-          <t>No cubicado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D60" s="255" t="inlineStr">
         <is>
-          <t>Requiere RMR/Q rock mass</t>
+          <t>Diseño STM</t>
         </is>
       </c>
       <c r="E60" s="255" t="inlineStr">
         <is>
-          <t>Eventual según geotecnia</t>
+          <t>Multiplicar Sec 5 por N</t>
         </is>
       </c>
       <c r="F60" s="255" t="inlineStr">
         <is>
-          <t>⚠ Pendiente STM38019 RMR</t>
+          <t>✓ Confirmado 1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="255" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B61" s="255" t="inlineStr">
         <is>
-          <t>UF referencial</t>
+          <t>Estructura soporte cables AT túnel (5.x.12)</t>
         </is>
       </c>
       <c r="C61" s="255" t="inlineStr">
         <is>
-          <t>38.500 CLP</t>
+          <t>20 kg/ml × 2454m = 49.084 kg</t>
         </is>
       </c>
       <c r="D61" s="255" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Estimado: 6 cables LAT 2×110kV, bandejas+soportes acero galv.</t>
         </is>
       </c>
       <c r="E61" s="255" t="inlineStr">
         <is>
-          <t>Actualizar al mes oferta</t>
+          <t>Si diseño real difiere → ajustar kg/ml</t>
         </is>
       </c>
       <c r="F61" s="255" t="inlineStr">
         <is>
-          <t>✓ Configurable</t>
+          <t>⚠ Confirmar plano bandejas</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="255" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B62" s="255" t="inlineStr">
         <is>
-          <t>Altura excavación = profundidad NV</t>
+          <t>Estructura soporte cables SS (4.x.13)</t>
         </is>
       </c>
       <c r="C62" s="255" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>500 kg × 2 (P1, P9) = 1.000 kg</t>
         </is>
       </c>
       <c r="D62" s="255" t="inlineStr">
         <is>
-          <t>Convención técnica</t>
+          <t>Estimado por SS — racks, bandejas, terminales</t>
         </is>
       </c>
       <c r="E62" s="255" t="inlineStr">
         <is>
-          <t>Si sump existe → +volumen</t>
+          <t>Verificar plano SS Vitacura/Providencia</t>
         </is>
       </c>
       <c r="F62" s="255" t="inlineStr">
         <is>
-          <t>⚠ STM38023 nota 'Nivel -3.50' en P9</t>
+          <t>⚠ Estimado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="255" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B63" s="255" t="inlineStr">
+        <is>
+          <t>Profundidad P9</t>
+        </is>
+      </c>
+      <c r="C63" s="255" t="inlineStr">
+        <is>
+          <t>9.06 m (NV)</t>
+        </is>
+      </c>
+      <c r="D63" s="255" t="inlineStr">
+        <is>
+          <t>STM38023 vs STM38109 (9.67m)</t>
+        </is>
+      </c>
+      <c r="E63" s="255" t="inlineStr">
+        <is>
+          <t>Δ excav P9 = 7.7 m³</t>
+        </is>
+      </c>
+      <c r="F63" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Discrepancia 0.61m</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="248" t="inlineStr">
-        <is>
-          <t>7. TRAZABILIDAD DE FUENTES (documentos consultados)</t>
+      <c r="A64" s="255" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B64" s="255" t="inlineStr">
+        <is>
+          <t>Diámetro liner interior</t>
+        </is>
+      </c>
+      <c r="C64" s="255" t="inlineStr">
+        <is>
+          <t>2.21 m</t>
+        </is>
+      </c>
+      <c r="D64" s="255" t="inlineStr">
+        <is>
+          <t>STM38136 vs STM38109 (2.10m)</t>
+        </is>
+      </c>
+      <c r="E64" s="255" t="inlineStr">
+        <is>
+          <t>Δ sección = 0.38 m² (10%)</t>
+        </is>
+      </c>
+      <c r="F64" s="255" t="inlineStr">
+        <is>
+          <t>✓ 2.21m incluye espesor anillos</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="249" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B65" s="249" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="C65" s="249" t="inlineStr">
-        <is>
-          <t>Revisión</t>
-        </is>
-      </c>
-      <c r="D65" s="249" t="inlineStr">
-        <is>
-          <t>Datos extraídos</t>
-        </is>
-      </c>
-      <c r="E65" s="249" t="inlineStr">
-        <is>
-          <t>Hoja relevante</t>
-        </is>
-      </c>
-      <c r="F65" s="249" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A65" s="255" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="B65" s="255" t="inlineStr">
+        <is>
+          <t>Longitud túnel total</t>
+        </is>
+      </c>
+      <c r="C65" s="255" t="inlineStr">
+        <is>
+          <t>2454.2 m</t>
+        </is>
+      </c>
+      <c r="D65" s="255" t="inlineStr">
+        <is>
+          <t>STM38020-23 suma DM</t>
+        </is>
+      </c>
+      <c r="E65" s="255" t="inlineStr">
+        <is>
+          <t>STM38109 redondea a 2450m</t>
+        </is>
+      </c>
+      <c r="F65" s="255" t="inlineStr">
+        <is>
+          <t>✓ Diferencia 4.2m (0.17%)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="255" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B66" s="255" t="inlineStr">
         <is>
-          <t>STM38020 Planta y Perfil</t>
+          <t>Cantidades 4.x.10-12 (shotcrete/malla/pernos)</t>
         </is>
       </c>
       <c r="C66" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>No cubicado — solo precio UF/u</t>
         </is>
       </c>
       <c r="D66" s="255" t="inlineStr">
         <is>
-          <t>P1, P2, P3 NV + DM tramos T1-T3</t>
+          <t>Requiere RMR/Q rock mass STM38019</t>
         </is>
       </c>
       <c r="E66" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F66" s="255" t="inlineStr"/>
+          <t>Eventual según geotecnia</t>
+        </is>
+      </c>
+      <c r="F66" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Pendiente RMR</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="255" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B67" s="255" t="inlineStr">
         <is>
-          <t>STM38021 Planta y Perfil</t>
+          <t>Items 4.x.4-7, 4.x.9 (suma alzada)</t>
         </is>
       </c>
       <c r="C67" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>1 gl × 9 piques cada uno</t>
         </is>
       </c>
       <c r="D67" s="255" t="inlineStr">
         <is>
-          <t>P4, P5 NV + DM tramos T3-T5</t>
+          <t>Refuerzo losa, dren, terminaciones, cobertura, refuerzo apertura</t>
         </is>
       </c>
       <c r="E67" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F67" s="255" t="inlineStr"/>
+          <t>Precios referenciales — cotizar</t>
+        </is>
+      </c>
+      <c r="F67" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Suma alzada</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="255" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="B68" s="255" t="inlineStr">
         <is>
-          <t>STM38022 Planta y Perfil</t>
+          <t>Monitoreo Pernos (5.x.8)</t>
         </is>
       </c>
       <c r="C68" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>1 gl × 8 tramos</t>
         </is>
       </c>
       <c r="D68" s="255" t="inlineStr">
         <is>
-          <t>P6, P7 NV + DM tramos T5-T7</t>
+          <t>Item correcto del template (NO instalación cables — bug v3)</t>
         </is>
       </c>
       <c r="E68" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F68" s="255" t="inlineStr"/>
+          <t>Cant 1 gl/tramo es estándar</t>
+        </is>
+      </c>
+      <c r="F68" s="255" t="inlineStr">
+        <is>
+          <t>✓ Corregido v4</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="255" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="B69" s="255" t="inlineStr">
         <is>
-          <t>STM38023 Planta y Perfil</t>
+          <t>UF referencial</t>
         </is>
       </c>
       <c r="C69" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>38.500 CLP</t>
         </is>
       </c>
       <c r="D69" s="255" t="inlineStr">
         <is>
-          <t>P8, P9 NV + DM tramos T7-T8</t>
+          <t>Mayo 2026</t>
         </is>
       </c>
       <c r="E69" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F69" s="255" t="inlineStr"/>
+          <t>Actualizar al mes oferta</t>
+        </is>
+      </c>
+      <c r="F69" s="255" t="inlineStr">
+        <is>
+          <t>✓ Configurable</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="255" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="B70" s="255" t="inlineStr">
         <is>
-          <t>STM38109 Memoria Ventilación</t>
+          <t>Altura excavación = profundidad NV</t>
         </is>
       </c>
       <c r="C70" s="255" t="inlineStr">
         <is>
-          <t>REV.E 28-01-2026</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D70" s="255" t="inlineStr">
         <is>
-          <t>23 jet fans S&amp;P TJHT2/4-315-CN, ubicación Tabla 4.2</t>
+          <t>Convención técnica</t>
         </is>
       </c>
       <c r="E70" s="255" t="inlineStr">
         <is>
-          <t>Sec 5 supuestos</t>
-        </is>
-      </c>
-      <c r="F70" s="255" t="inlineStr"/>
+          <t>Si sump existe → +volumen</t>
+        </is>
+      </c>
+      <c r="F70" s="255" t="inlineStr">
+        <is>
+          <t>⚠ STM38023 nota 'Nivel -3.50' en P9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="255" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="B71" s="255" t="inlineStr">
         <is>
-          <t>STM38110 ETP Equipos Ventilación</t>
+          <t>Plazo proyecto (Costos Indirectos)</t>
         </is>
       </c>
       <c r="C71" s="255" t="inlineStr">
         <is>
-          <t>REV.0 14-11-2025</t>
+          <t>24 meses</t>
         </is>
       </c>
       <c r="D71" s="255" t="inlineStr">
         <is>
-          <t>2 extractores Soler-Palau TGT/6-1409, modelo jet fan</t>
+          <t>Estimado proyecto OOCC tunneling 2.45km + 9 piques</t>
         </is>
       </c>
       <c r="E71" s="255" t="inlineStr">
         <is>
-          <t>Sec 5 supuestos</t>
-        </is>
-      </c>
-      <c r="F71" s="255" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="255" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="B72" s="255" t="inlineStr">
-        <is>
-          <t>STM38019 Geotécnica</t>
-        </is>
-      </c>
-      <c r="C72" s="255" t="inlineStr">
+          <t>Cada mes adicional × 1.300 UF/mes indirecto</t>
+        </is>
+      </c>
+      <c r="F71" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Verificar Bases Técnicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="248" t="inlineStr">
+        <is>
+          <t>7. TRAZABILIDAD DE FUENTES (documentos consultados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="249" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B74" s="249" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="C74" s="249" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="D74" s="249" t="inlineStr">
+        <is>
+          <t>Datos extraídos</t>
+        </is>
+      </c>
+      <c r="E74" s="249" t="inlineStr">
+        <is>
+          <t>Hoja relevante</t>
+        </is>
+      </c>
+      <c r="F74" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D72" s="255" t="inlineStr">
-        <is>
-          <t>Estratigrafía H1-H3 (Relleno/Grava 2°/Grava 1°)</t>
-        </is>
-      </c>
-      <c r="E72" s="255" t="inlineStr">
-        <is>
-          <t>Pendiente RMR para 4.x.10-12</t>
-        </is>
-      </c>
-      <c r="F72" s="255" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="255" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="B73" s="255" t="inlineStr">
-        <is>
-          <t>STM38136 Planos eléctricos</t>
-        </is>
-      </c>
-      <c r="C73" s="255" t="inlineStr">
-        <is>
-          <t>REV.1 06/04/2026</t>
-        </is>
-      </c>
-      <c r="D73" s="255" t="inlineStr">
-        <is>
-          <t>Ø interior pique 4.0m, Ø interior liner 2.21m</t>
-        </is>
-      </c>
-      <c r="E73" s="255" t="inlineStr">
-        <is>
-          <t>Sec 1 constantes</t>
-        </is>
-      </c>
-      <c r="F73" s="255" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="255" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="B74" s="255" t="inlineStr">
-        <is>
-          <t>BAE Licitación 2025-25-TX-SS-RM</t>
-        </is>
-      </c>
-      <c r="C74" s="255" t="inlineStr">
-        <is>
-          <t>REV.0 13/04/2026</t>
-        </is>
-      </c>
-      <c r="D74" s="255" t="inlineStr">
-        <is>
-          <t>Estructura items 4.x y 5.x</t>
-        </is>
-      </c>
-      <c r="E74" s="255" t="inlineStr">
-        <is>
-          <t>A) Detalle</t>
-        </is>
-      </c>
-      <c r="F74" s="255" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="255" t="inlineStr">
         <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B75" s="255" t="inlineStr">
+        <is>
+          <t>STM38020 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C75" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D75" s="255" t="inlineStr">
+        <is>
+          <t>P1, P2, P3 NV + DM tramos T1-T3</t>
+        </is>
+      </c>
+      <c r="E75" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F75" s="255" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="255" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B76" s="255" t="inlineStr">
+        <is>
+          <t>STM38021 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C76" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D76" s="255" t="inlineStr">
+        <is>
+          <t>P4, P5 NV + DM tramos T3-T5</t>
+        </is>
+      </c>
+      <c r="E76" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F76" s="255" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="255" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B77" s="255" t="inlineStr">
+        <is>
+          <t>STM38022 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C77" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D77" s="255" t="inlineStr">
+        <is>
+          <t>P6, P7 NV + DM tramos T5-T7</t>
+        </is>
+      </c>
+      <c r="E77" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F77" s="255" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="255" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B78" s="255" t="inlineStr">
+        <is>
+          <t>STM38023 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C78" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D78" s="255" t="inlineStr">
+        <is>
+          <t>P8, P9 NV + DM tramos T7-T8</t>
+        </is>
+      </c>
+      <c r="E78" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F78" s="255" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="255" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="B79" s="255" t="inlineStr">
+        <is>
+          <t>STM38109 Memoria Ventilación</t>
+        </is>
+      </c>
+      <c r="C79" s="255" t="inlineStr">
+        <is>
+          <t>REV.E 28-01-2026</t>
+        </is>
+      </c>
+      <c r="D79" s="255" t="inlineStr">
+        <is>
+          <t>23 jet fans S&amp;P TJHT2/4-315-CN, ubicación Tabla 4.2</t>
+        </is>
+      </c>
+      <c r="E79" s="255" t="inlineStr">
+        <is>
+          <t>Sec 5 supuestos</t>
+        </is>
+      </c>
+      <c r="F79" s="255" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="255" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B80" s="255" t="inlineStr">
+        <is>
+          <t>STM38110 ETP Equipos Ventilación</t>
+        </is>
+      </c>
+      <c r="C80" s="255" t="inlineStr">
+        <is>
+          <t>REV.0 14-11-2025</t>
+        </is>
+      </c>
+      <c r="D80" s="255" t="inlineStr">
+        <is>
+          <t>2 extractores Soler-Palau TGT/6-1409, modelo jet fan</t>
+        </is>
+      </c>
+      <c r="E80" s="255" t="inlineStr">
+        <is>
+          <t>Sec 5 supuestos</t>
+        </is>
+      </c>
+      <c r="F80" s="255" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="255" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="B81" s="255" t="inlineStr">
+        <is>
+          <t>STM38019 Geotécnica</t>
+        </is>
+      </c>
+      <c r="C81" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="255" t="inlineStr">
+        <is>
+          <t>Estratigrafía H1-H3 (Relleno/Grava 2°/Grava 1°)</t>
+        </is>
+      </c>
+      <c r="E81" s="255" t="inlineStr">
+        <is>
+          <t>Pendiente RMR para 4.x.10-12</t>
+        </is>
+      </c>
+      <c r="F81" s="255" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="255" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="B82" s="255" t="inlineStr">
+        <is>
+          <t>STM38136 Planos eléctricos</t>
+        </is>
+      </c>
+      <c r="C82" s="255" t="inlineStr">
+        <is>
+          <t>REV.1 06/04/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="255" t="inlineStr">
+        <is>
+          <t>Ø interior pique 4.0m, Ø interior liner 2.21m</t>
+        </is>
+      </c>
+      <c r="E82" s="255" t="inlineStr">
+        <is>
+          <t>Sec 1 constantes</t>
+        </is>
+      </c>
+      <c r="F82" s="255" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="255" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="B83" s="255" t="inlineStr">
+        <is>
+          <t>BAE Licitación 2025-25-TX-SS-RM</t>
+        </is>
+      </c>
+      <c r="C83" s="255" t="inlineStr">
+        <is>
+          <t>REV.0 13/04/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="255" t="inlineStr">
+        <is>
+          <t>Estructura items 4.x y 5.x</t>
+        </is>
+      </c>
+      <c r="E83" s="255" t="inlineStr">
+        <is>
+          <t>A) Detalle</t>
+        </is>
+      </c>
+      <c r="F83" s="255" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="255" t="inlineStr">
+        <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="B75" s="255" t="inlineStr">
+      <c r="B84" s="255" t="inlineStr">
         <is>
           <t>IF SS Vitacura</t>
         </is>
       </c>
-      <c r="C75" s="255" t="inlineStr">
+      <c r="C84" s="255" t="inlineStr">
         <is>
           <t>20251009 (3 etapas)</t>
         </is>
       </c>
-      <c r="D75" s="255" t="inlineStr">
+      <c r="D84" s="255" t="inlineStr">
         <is>
           <t>Composición Instalación de Faenas</t>
         </is>
       </c>
-      <c r="E75" s="255" t="inlineStr">
+      <c r="E84" s="255" t="inlineStr">
         <is>
           <t>Sec 3 supuestos suma alzada</t>
         </is>
       </c>
-      <c r="F75" s="255" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="248" t="inlineStr">
+      <c r="F84" s="255" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="248" t="inlineStr">
         <is>
           <t>8. RESUMEN TOTALES CUBICADOS</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="249" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B78" s="249" t="inlineStr">
+      <c r="B87" s="249" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C78" s="249" t="inlineStr">
+      <c r="C87" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D78" s="249" t="inlineStr">
+      <c r="D87" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="E78" s="249" t="inlineStr">
+      <c r="E87" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F78" s="249" t="inlineStr">
+      <c r="F87" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="250" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="250" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B79" s="250" t="inlineStr">
+      <c r="B88" s="250" t="inlineStr">
         <is>
           <t>Excavación piques (suma)</t>
         </is>
       </c>
-      <c r="C79" s="250" t="n">
+      <c r="C88" s="250" t="n">
         <v>1770.34</v>
       </c>
-      <c r="D79" s="250" t="inlineStr">
+      <c r="D88" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E79" s="250" t="inlineStr"/>
-      <c r="F79" s="250" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="250" t="inlineStr">
+      <c r="E88" s="250" t="inlineStr"/>
+      <c r="F88" s="250" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="250" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B80" s="250" t="inlineStr">
+      <c r="B89" s="250" t="inlineStr">
         <is>
           <t>Excavación túnel (suma)</t>
         </is>
       </c>
-      <c r="C80" s="250" t="n">
+      <c r="C89" s="250" t="n">
         <v>9414.219999999999</v>
       </c>
-      <c r="D80" s="250" t="inlineStr">
+      <c r="D89" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E80" s="250" t="inlineStr"/>
-      <c r="F80" s="250" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="250" t="inlineStr">
+      <c r="E89" s="250" t="inlineStr"/>
+      <c r="F89" s="250" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="250" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B81" s="250" t="inlineStr">
+      <c r="B90" s="250" t="inlineStr">
         <is>
           <t>Liner pique (suma profundidades)</t>
         </is>
       </c>
-      <c r="C81" s="250" t="n">
+      <c r="C90" s="250" t="n">
         <v>140.9</v>
       </c>
-      <c r="D81" s="250" t="inlineStr">
+      <c r="D90" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E81" s="250" t="inlineStr"/>
-      <c r="F81" s="250" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="250" t="inlineStr">
+      <c r="E90" s="250" t="inlineStr"/>
+      <c r="F90" s="250" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="250" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B82" s="250" t="inlineStr">
+      <c r="B91" s="250" t="inlineStr">
         <is>
           <t>Liner túnel (longitud total)</t>
         </is>
       </c>
-      <c r="C82" s="250" t="n">
+      <c r="C91" s="250" t="n">
         <v>2454.2</v>
       </c>
-      <c r="D82" s="250" t="inlineStr">
+      <c r="D91" s="250" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E82" s="250" t="inlineStr"/>
-      <c r="F82" s="250" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="250" t="inlineStr">
+      <c r="E91" s="250" t="inlineStr"/>
+      <c r="F91" s="250" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="250" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B83" s="250" t="inlineStr">
+      <c r="B92" s="250" t="inlineStr">
         <is>
           <t>Radier H30</t>
         </is>
       </c>
-      <c r="C83" s="250" t="n">
+      <c r="C92" s="250" t="n">
         <v>813.58</v>
       </c>
-      <c r="D83" s="250" t="inlineStr">
+      <c r="D92" s="250" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E83" s="250" t="inlineStr"/>
-      <c r="F83" s="250" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="250" t="inlineStr">
+      <c r="E92" s="250" t="inlineStr"/>
+      <c r="F92" s="250" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="250" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="B84" s="250" t="inlineStr">
-        <is>
-          <t>Cables instalados (6 × longitud)</t>
-        </is>
-      </c>
-      <c r="C84" s="250" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="250" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="E84" s="250" t="inlineStr"/>
-      <c r="F84" s="250" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="250" t="inlineStr">
+      <c r="B93" s="250" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables AT túnel (5.x.12)</t>
+        </is>
+      </c>
+      <c r="C93" s="250" t="n">
+        <v>49084</v>
+      </c>
+      <c r="D93" s="250" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E93" s="250" t="inlineStr">
+        <is>
+          <t>(20 kg/ml × 2454m)</t>
+        </is>
+      </c>
+      <c r="F93" s="250" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="250" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="B85" s="250" t="inlineStr">
-        <is>
-          <t>Estructura cables SS</t>
-        </is>
-      </c>
-      <c r="C85" s="250" t="n">
+      <c r="B94" s="250" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables SS (4.x.13)</t>
+        </is>
+      </c>
+      <c r="C94" s="250" t="n">
         <v>1000</v>
       </c>
-      <c r="D85" s="250" t="inlineStr">
+      <c r="D94" s="250" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E94" s="250" t="inlineStr">
+        <is>
+          <t>(500 kg × P1+P9 = 1000 kg)</t>
+        </is>
+      </c>
+      <c r="F94" s="250" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="250" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="B95" s="250" t="inlineStr">
+        <is>
+          <t>Escalas+plataformas</t>
+        </is>
+      </c>
+      <c r="C95" s="250" t="n">
+        <v>9</v>
+      </c>
+      <c r="D95" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E85" s="250" t="inlineStr">
-        <is>
-          <t>(solo P1+P9)</t>
-        </is>
-      </c>
-      <c r="F85" s="250" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="250" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="B86" s="250" t="inlineStr">
-        <is>
-          <t>Escalas+plataformas</t>
-        </is>
-      </c>
-      <c r="C86" s="250" t="n">
+      <c r="E95" s="250" t="inlineStr"/>
+      <c r="F95" s="250" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="250" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="B96" s="250" t="inlineStr">
+        <is>
+          <t>Brocales definitivos</t>
+        </is>
+      </c>
+      <c r="C96" s="250" t="n">
         <v>9</v>
       </c>
-      <c r="D86" s="250" t="inlineStr">
+      <c r="D96" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E86" s="250" t="inlineStr"/>
-      <c r="F86" s="250" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="250" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="B87" s="250" t="inlineStr">
-        <is>
-          <t>Brocales definitivos</t>
-        </is>
-      </c>
-      <c r="C87" s="250" t="n">
-        <v>9</v>
-      </c>
-      <c r="D87" s="250" t="inlineStr">
+      <c r="E96" s="250" t="inlineStr"/>
+      <c r="F96" s="250" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="250" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="B97" s="250" t="inlineStr">
+        <is>
+          <t>Monitoreo de Pernos (5.x.8)</t>
+        </is>
+      </c>
+      <c r="C97" s="250" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E87" s="250" t="inlineStr"/>
-      <c r="F87" s="250" t="inlineStr"/>
+      <c r="E97" s="250" t="inlineStr">
+        <is>
+          <t>(1 gl × 8 tramos)</t>
+        </is>
+      </c>
+      <c r="F97" s="250" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="250" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="B98" s="250" t="inlineStr">
+        <is>
+          <t>Items suma alzada piques (4.x.4-7, 4.x.9)</t>
+        </is>
+      </c>
+      <c r="C98" s="250" t="n">
+        <v>45</v>
+      </c>
+      <c r="D98" s="250" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="E98" s="250" t="inlineStr">
+        <is>
+          <t>(5 items × 9 piques = 45 gl)</t>
+        </is>
+      </c>
+      <c r="F98" s="250" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="248" t="inlineStr">
+        <is>
+          <t>9. RACIONALES COSTOS INDIRECTOS, GG Y UTILIDAD (hoja B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="249" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B101" s="249" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C101" s="249" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="D101" s="249" t="inlineStr">
+        <is>
+          <t>Tiempo</t>
+        </is>
+      </c>
+      <c r="E101" s="249" t="inlineStr">
+        <is>
+          <t>Precio UF/u</t>
+        </is>
+      </c>
+      <c r="F101" s="249" t="inlineStr">
+        <is>
+          <t>Subtotal UF / Justificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="260" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B102" s="260" t="inlineStr">
+        <is>
+          <t>Plazo referencial proyecto</t>
+        </is>
+      </c>
+      <c r="C102" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="260" t="inlineStr">
+        <is>
+          <t>24 meses</t>
+        </is>
+      </c>
+      <c r="E102" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="260" t="inlineStr">
+        <is>
+          <t>Estimado tunneling 2.45km — verificar Bases Técnicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="260" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B103" s="260" t="inlineStr">
+        <is>
+          <t>Vigilancia 24h externalizada</t>
+        </is>
+      </c>
+      <c r="C103" s="260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" s="260" t="inlineStr">
+        <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E103" s="260" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F103" s="260" t="inlineStr">
+        <is>
+          <t>2,400 UF — servicio integral 4 guardias rotación</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="260" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B104" s="260" t="inlineStr">
+        <is>
+          <t>Personal indirecto (8 personas, sueldo UF/mes)</t>
+        </is>
+      </c>
+      <c r="C104" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="260" t="inlineStr">
+        <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E104" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="260" t="inlineStr">
+        <is>
+          <t>18,840 UF total. Admin 150, JT 120, 2×Sup 90, Prev 80, MA 70, Topo 80, Tra 55, Bod 50 UF/mes (mid-range Chile 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="260" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B105" s="260" t="inlineStr">
+        <is>
+          <t>Maquinarias y vehículos</t>
+        </is>
+      </c>
+      <c r="C105" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="260" t="inlineStr">
+        <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E105" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="260" t="inlineStr">
+        <is>
+          <t>6,360 UF — 3 camionetas (35), fletes (50), andamios (30), equipos menores (80) UF/mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="260" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B106" s="260" t="inlineStr">
+        <is>
+          <t>Disposición residuos + excedentes</t>
+        </is>
+      </c>
+      <c r="C106" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="260" t="inlineStr">
+        <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E106" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="260" t="inlineStr">
+        <is>
+          <t>4,080 UF — residuos sólidos (50), excedentes excavación (120) UF/mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="260" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B107" s="260" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="C107" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D107" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="260" t="inlineStr">
+        <is>
+          <t>31,680 UF (≈42% del Directo) — norma 25-35% en obras civiles, 40-50% en obras especializadas tunneling</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="260" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B108" s="260" t="inlineStr">
+        <is>
+          <t>GG Aporte Oficina Central</t>
+        </is>
+      </c>
+      <c r="C108" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D108" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" s="260" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="F108" s="260" t="inlineStr">
+        <is>
+          <t>≈4.4% del Directo (norma 3-6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="260" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B109" s="260" t="inlineStr">
+        <is>
+          <t>GG Gastos Financieros</t>
+        </is>
+      </c>
+      <c r="C109" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D109" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" s="260" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="F109" s="260" t="inlineStr">
+        <is>
+          <t>≈2.5% del Directo (intereses+factoring)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="260" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B110" s="260" t="inlineStr">
+        <is>
+          <t>GG Boletas Garantía + Seguros</t>
+        </is>
+      </c>
+      <c r="C110" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D110" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="260" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="F110" s="260" t="inlineStr">
+        <is>
+          <t>≈1.6% del Directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="260" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B111" s="260" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS GENERALES</t>
+        </is>
+      </c>
+      <c r="C111" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D111" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="260" t="inlineStr">
+        <is>
+          <t>6,200 UF (≈8.3% del Directo) — norma 8-12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="260" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="B112" s="260" t="inlineStr">
+        <is>
+          <t>Utilidad Contratista</t>
+        </is>
+      </c>
+      <c r="C112" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D112" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="260" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F112" s="260" t="inlineStr">
+        <is>
+          <t>≈11% del Directo — norma 8-12% en obras especializadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="260" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B113" s="260" t="inlineStr">
+        <is>
+          <t>RESUMEN OFERTA</t>
+        </is>
+      </c>
+      <c r="C113" s="260" t="inlineStr">
+        <is>
+          <t>Directo: 74.843 UF | Indirecto: 31.680 UF | GG: 6.200 UF | Utilidad: 8.000 UF | Neto: 120.723 UF | IVA: 22.937 UF</t>
+        </is>
+      </c>
+      <c r="D113" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="260" t="inlineStr">
+        <is>
+          <t>TOTAL: 143.660 UF ≈ $5,531M CLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="247" t="inlineStr">
+        <is>
+          <t>⚠ Valores marcados salmón en hoja B son REFERENCIALES (plazo 24 meses + tasas Chile 2026). Contratista debe ajustar a su estructura organizacional, plazo real y costo de personal específico.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A114:F114"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/licitacion_vitacura.xlsx
+++ b/output/licitacion_vitacura.xlsx
@@ -3155,12 +3155,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D45" s="49" t="n"/>
+      <c r="D45" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E45" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F45" s="210">
-        <f>+D45*E45</f>
+      <c r="F45" s="205">
+        <f>D45*E45</f>
         <v/>
       </c>
       <c r="G45" s="47" t="inlineStr">
@@ -3186,12 +3188,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D46" s="49" t="n"/>
+      <c r="D46" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E46" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F46" s="210">
-        <f>+D46*E46</f>
+      <c r="F46" s="205">
+        <f>D46*E46</f>
         <v/>
       </c>
       <c r="G46" s="47" t="inlineStr">
@@ -3217,12 +3221,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D47" s="49" t="n"/>
+      <c r="D47" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E47" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F47" s="210">
-        <f>+D47*E47</f>
+      <c r="F47" s="205">
+        <f>D47*E47</f>
         <v/>
       </c>
       <c r="G47" s="47" t="inlineStr">
@@ -3248,12 +3254,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D48" s="49" t="n"/>
+      <c r="D48" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E48" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F48" s="210">
-        <f>+D48*E48</f>
+      <c r="F48" s="205">
+        <f>D48*E48</f>
         <v/>
       </c>
       <c r="G48" s="47" t="inlineStr">
@@ -3312,12 +3320,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D50" s="49" t="n"/>
+      <c r="D50" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E50" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F50" s="210">
-        <f>+D50*E50</f>
+      <c r="F50" s="205">
+        <f>D50*E50</f>
         <v/>
       </c>
       <c r="G50" s="47" t="inlineStr">
@@ -3667,12 +3677,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D62" s="49" t="n"/>
+      <c r="D62" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E62" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F62" s="210">
-        <f>+D62*E62</f>
+      <c r="F62" s="205">
+        <f>D62*E62</f>
         <v/>
       </c>
       <c r="G62" s="47" t="inlineStr">
@@ -3698,12 +3710,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D63" s="49" t="n"/>
+      <c r="D63" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E63" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F63" s="210">
-        <f>+D63*E63</f>
+      <c r="F63" s="205">
+        <f>D63*E63</f>
         <v/>
       </c>
       <c r="G63" s="47" t="inlineStr">
@@ -3729,12 +3743,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D64" s="49" t="n"/>
+      <c r="D64" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E64" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F64" s="210">
-        <f>+D64*E64</f>
+      <c r="F64" s="205">
+        <f>D64*E64</f>
         <v/>
       </c>
       <c r="G64" s="47" t="inlineStr">
@@ -3760,12 +3776,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D65" s="49" t="n"/>
+      <c r="D65" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E65" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F65" s="210">
-        <f>+D65*E65</f>
+      <c r="F65" s="205">
+        <f>D65*E65</f>
         <v/>
       </c>
       <c r="G65" s="47" t="inlineStr">
@@ -3824,12 +3842,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D67" s="49" t="n"/>
+      <c r="D67" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E67" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F67" s="210">
-        <f>+D67*E67</f>
+      <c r="F67" s="205">
+        <f>D67*E67</f>
         <v/>
       </c>
       <c r="G67" s="47" t="inlineStr">
@@ -4146,12 +4166,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D78" s="49" t="n"/>
+      <c r="D78" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E78" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F78" s="210">
-        <f>+D78*E78</f>
+      <c r="F78" s="205">
+        <f>D78*E78</f>
         <v/>
       </c>
       <c r="G78" s="47" t="inlineStr">
@@ -4177,12 +4199,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D79" s="49" t="n"/>
+      <c r="D79" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E79" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F79" s="210">
-        <f>+D79*E79</f>
+      <c r="F79" s="205">
+        <f>D79*E79</f>
         <v/>
       </c>
       <c r="G79" s="47" t="inlineStr">
@@ -4208,12 +4232,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D80" s="49" t="n"/>
+      <c r="D80" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E80" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F80" s="210">
-        <f>+D80*E80</f>
+      <c r="F80" s="205">
+        <f>D80*E80</f>
         <v/>
       </c>
       <c r="G80" s="47" t="inlineStr">
@@ -4239,12 +4265,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D81" s="49" t="n"/>
+      <c r="D81" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E81" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F81" s="210">
-        <f>+D81*E81</f>
+      <c r="F81" s="205">
+        <f>D81*E81</f>
         <v/>
       </c>
       <c r="G81" s="47" t="inlineStr">
@@ -4303,12 +4331,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D83" s="49" t="n"/>
+      <c r="D83" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E83" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F83" s="210">
-        <f>+D83*E83</f>
+      <c r="F83" s="205">
+        <f>D83*E83</f>
         <v/>
       </c>
       <c r="G83" s="47" t="inlineStr">
@@ -4625,12 +4655,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D94" s="49" t="n"/>
+      <c r="D94" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E94" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F94" s="210">
-        <f>+D94*E94</f>
+      <c r="F94" s="205">
+        <f>D94*E94</f>
         <v/>
       </c>
       <c r="G94" s="47" t="inlineStr">
@@ -4656,12 +4688,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D95" s="49" t="n"/>
+      <c r="D95" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E95" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F95" s="210">
-        <f>+D95*E95</f>
+      <c r="F95" s="205">
+        <f>D95*E95</f>
         <v/>
       </c>
       <c r="G95" s="47" t="inlineStr">
@@ -4687,12 +4721,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D96" s="49" t="n"/>
+      <c r="D96" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E96" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F96" s="210">
-        <f>+D96*E96</f>
+      <c r="F96" s="205">
+        <f>D96*E96</f>
         <v/>
       </c>
       <c r="G96" s="47" t="inlineStr">
@@ -4718,12 +4754,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D97" s="49" t="n"/>
+      <c r="D97" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E97" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F97" s="210">
-        <f>+D97*E97</f>
+      <c r="F97" s="205">
+        <f>D97*E97</f>
         <v/>
       </c>
       <c r="G97" s="47" t="inlineStr">
@@ -4782,12 +4820,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D99" s="49" t="n"/>
+      <c r="D99" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E99" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F99" s="210">
-        <f>+D99*E99</f>
+      <c r="F99" s="205">
+        <f>D99*E99</f>
         <v/>
       </c>
       <c r="G99" s="47" t="inlineStr">
@@ -5104,12 +5144,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D110" s="49" t="n"/>
+      <c r="D110" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E110" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F110" s="210">
-        <f>+D110*E110</f>
+      <c r="F110" s="205">
+        <f>D110*E110</f>
         <v/>
       </c>
       <c r="G110" s="47" t="inlineStr">
@@ -5135,12 +5177,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D111" s="49" t="n"/>
+      <c r="D111" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E111" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F111" s="210">
-        <f>+D111*E111</f>
+      <c r="F111" s="205">
+        <f>D111*E111</f>
         <v/>
       </c>
       <c r="G111" s="47" t="inlineStr">
@@ -5166,12 +5210,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D112" s="49" t="n"/>
+      <c r="D112" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E112" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F112" s="210">
-        <f>+D112*E112</f>
+      <c r="F112" s="205">
+        <f>D112*E112</f>
         <v/>
       </c>
       <c r="G112" s="47" t="inlineStr">
@@ -5197,12 +5243,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D113" s="49" t="n"/>
+      <c r="D113" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E113" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F113" s="210">
-        <f>+D113*E113</f>
+      <c r="F113" s="205">
+        <f>D113*E113</f>
         <v/>
       </c>
       <c r="G113" s="47" t="inlineStr">
@@ -5261,12 +5309,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D115" s="49" t="n"/>
+      <c r="D115" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E115" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F115" s="210">
-        <f>+D115*E115</f>
+      <c r="F115" s="205">
+        <f>D115*E115</f>
         <v/>
       </c>
       <c r="G115" s="47" t="inlineStr">
@@ -5583,12 +5633,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D126" s="49" t="n"/>
+      <c r="D126" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E126" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F126" s="210">
-        <f>+D126*E126</f>
+      <c r="F126" s="205">
+        <f>D126*E126</f>
         <v/>
       </c>
       <c r="G126" s="47" t="inlineStr">
@@ -5614,12 +5666,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D127" s="49" t="n"/>
+      <c r="D127" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E127" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F127" s="210">
-        <f>+D127*E127</f>
+      <c r="F127" s="205">
+        <f>D127*E127</f>
         <v/>
       </c>
       <c r="G127" s="47" t="inlineStr">
@@ -5645,12 +5699,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D128" s="49" t="n"/>
+      <c r="D128" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E128" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F128" s="210">
-        <f>+D128*E128</f>
+      <c r="F128" s="205">
+        <f>D128*E128</f>
         <v/>
       </c>
       <c r="G128" s="47" t="inlineStr">
@@ -5676,12 +5732,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D129" s="49" t="n"/>
+      <c r="D129" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E129" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F129" s="210">
-        <f>+D129*E129</f>
+      <c r="F129" s="205">
+        <f>D129*E129</f>
         <v/>
       </c>
       <c r="G129" s="47" t="inlineStr">
@@ -5740,12 +5798,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D131" s="49" t="n"/>
+      <c r="D131" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E131" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F131" s="210">
-        <f>+D131*E131</f>
+      <c r="F131" s="205">
+        <f>D131*E131</f>
         <v/>
       </c>
       <c r="G131" s="47" t="inlineStr">
@@ -6062,12 +6122,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D142" s="49" t="n"/>
+      <c r="D142" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E142" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F142" s="210">
-        <f>+D142*E142</f>
+      <c r="F142" s="205">
+        <f>D142*E142</f>
         <v/>
       </c>
       <c r="G142" s="47" t="inlineStr">
@@ -6093,12 +6155,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D143" s="49" t="n"/>
+      <c r="D143" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E143" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F143" s="210">
-        <f>+D143*E143</f>
+      <c r="F143" s="205">
+        <f>D143*E143</f>
         <v/>
       </c>
       <c r="G143" s="47" t="inlineStr">
@@ -6124,12 +6188,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D144" s="49" t="n"/>
+      <c r="D144" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E144" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F144" s="210">
-        <f>+D144*E144</f>
+      <c r="F144" s="205">
+        <f>D144*E144</f>
         <v/>
       </c>
       <c r="G144" s="47" t="inlineStr">
@@ -6155,12 +6221,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D145" s="49" t="n"/>
+      <c r="D145" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E145" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F145" s="210">
-        <f>+D145*E145</f>
+      <c r="F145" s="205">
+        <f>D145*E145</f>
         <v/>
       </c>
       <c r="G145" s="47" t="inlineStr">
@@ -6219,12 +6287,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D147" s="49" t="n"/>
+      <c r="D147" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E147" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F147" s="210">
-        <f>+D147*E147</f>
+      <c r="F147" s="205">
+        <f>D147*E147</f>
         <v/>
       </c>
       <c r="G147" s="47" t="inlineStr">
@@ -6541,12 +6611,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D158" s="49" t="n"/>
+      <c r="D158" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E158" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F158" s="210">
-        <f>+D158*E158</f>
+      <c r="F158" s="205">
+        <f>D158*E158</f>
         <v/>
       </c>
       <c r="G158" s="47" t="inlineStr">
@@ -6572,12 +6644,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D159" s="49" t="n"/>
+      <c r="D159" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E159" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F159" s="210">
-        <f>+D159*E159</f>
+      <c r="F159" s="205">
+        <f>D159*E159</f>
         <v/>
       </c>
       <c r="G159" s="47" t="inlineStr">
@@ -6603,12 +6677,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D160" s="49" t="n"/>
+      <c r="D160" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E160" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F160" s="210">
-        <f>+D160*E160</f>
+      <c r="F160" s="205">
+        <f>D160*E160</f>
         <v/>
       </c>
       <c r="G160" s="47" t="inlineStr">
@@ -6634,12 +6710,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D161" s="49" t="n"/>
+      <c r="D161" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E161" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F161" s="210">
-        <f>+D161*E161</f>
+      <c r="F161" s="205">
+        <f>D161*E161</f>
         <v/>
       </c>
       <c r="G161" s="47" t="inlineStr">
@@ -6698,12 +6776,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D163" s="49" t="n"/>
+      <c r="D163" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E163" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F163" s="210">
-        <f>+D163*E163</f>
+      <c r="F163" s="205">
+        <f>D163*E163</f>
         <v/>
       </c>
       <c r="G163" s="47" t="inlineStr">
@@ -7020,12 +7100,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D174" s="49" t="n"/>
+      <c r="D174" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E174" s="222" t="n">
         <v>72.7273</v>
       </c>
-      <c r="F174" s="210">
-        <f>+D174*E174</f>
+      <c r="F174" s="205">
+        <f>D174*E174</f>
         <v/>
       </c>
       <c r="G174" s="47" t="inlineStr">
@@ -7051,12 +7133,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D175" s="49" t="n"/>
+      <c r="D175" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E175" s="222" t="n">
         <v>46.7532</v>
       </c>
-      <c r="F175" s="210">
-        <f>+D175*E175</f>
+      <c r="F175" s="205">
+        <f>D175*E175</f>
         <v/>
       </c>
       <c r="G175" s="47" t="inlineStr">
@@ -7082,12 +7166,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D176" s="49" t="n"/>
+      <c r="D176" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E176" s="222" t="n">
         <v>38.961</v>
       </c>
-      <c r="F176" s="210">
-        <f>+D176*E176</f>
+      <c r="F176" s="205">
+        <f>D176*E176</f>
         <v/>
       </c>
       <c r="G176" s="47" t="inlineStr">
@@ -7113,12 +7199,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D177" s="49" t="n"/>
+      <c r="D177" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E177" s="222" t="n">
         <v>90.9091</v>
       </c>
-      <c r="F177" s="210">
-        <f>+D177*E177</f>
+      <c r="F177" s="205">
+        <f>D177*E177</f>
         <v/>
       </c>
       <c r="G177" s="47" t="inlineStr">
@@ -7177,12 +7265,14 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="D179" s="49" t="n"/>
+      <c r="D179" s="221" t="n">
+        <v>1</v>
+      </c>
       <c r="E179" s="222" t="n">
         <v>57.1429</v>
       </c>
-      <c r="F179" s="210">
-        <f>+D179*E179</f>
+      <c r="F179" s="205">
+        <f>D179*E179</f>
         <v/>
       </c>
       <c r="G179" s="47" t="inlineStr">

--- a/output/licitacion_vitacura.xlsx
+++ b/output/licitacion_vitacura.xlsx
@@ -15972,7 +15972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="B10" s="255" t="inlineStr">
         <is>
-          <t>Espesor liner túnel (PL)</t>
+          <t>Espesor liner acero A-36</t>
         </is>
       </c>
       <c r="C10" s="255" t="inlineStr">
@@ -16192,886 +16192,892 @@
       </c>
       <c r="F10" s="255" t="inlineStr">
         <is>
-          <t>STM38020 nota técnica</t>
+          <t>STM38019 §5.1 modelo TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="255" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B11" s="255" t="inlineStr">
+        <is>
+          <t>Espesor revestimiento estándar</t>
+        </is>
+      </c>
+      <c r="C11" s="255" t="inlineStr">
+        <is>
+          <t>Liner 5mm + Shotcrete G-30 95mm</t>
+        </is>
+      </c>
+      <c r="D11" s="255" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="E11" s="255" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F11" s="255" t="inlineStr">
+        <is>
+          <t>STM38019 §5.1 (pp.17)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="248" t="inlineStr">
+      <c r="A12" s="255" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B12" s="255" t="inlineStr">
+        <is>
+          <t>Espesor zona reforzada (apertura ojo demolición)</t>
+        </is>
+      </c>
+      <c r="C12" s="255" t="inlineStr">
+        <is>
+          <t>Liner + Shotcrete + 2do revestimiento</t>
+        </is>
+      </c>
+      <c r="D12" s="255" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="E12" s="255" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F12" s="255" t="inlineStr">
+        <is>
+          <t>STM38019 §5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="255" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="B13" s="255" t="inlineStr">
+        <is>
+          <t>Avance por anillo (pique y túnel)</t>
+        </is>
+      </c>
+      <c r="C13" s="255" t="inlineStr">
+        <is>
+          <t>Excavación + instalación liner secuencial</t>
+        </is>
+      </c>
+      <c r="D13" s="255" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="E13" s="255" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F13" s="255" t="inlineStr">
+        <is>
+          <t>STM38019 §5.1 Tabla 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>2. PROFUNDIDADES DE PIQUES — NV terreno - NV invert liner</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="249" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>Pique</t>
         </is>
       </c>
-      <c r="B13" s="249" t="inlineStr">
+      <c r="B16" s="249" t="inlineStr">
         <is>
           <t>NV terreno (m.s.n.m)</t>
         </is>
       </c>
-      <c r="C13" s="249" t="inlineStr">
+      <c r="C16" s="249" t="inlineStr">
         <is>
           <t>NV liner invert (m.s.n.m)</t>
         </is>
       </c>
-      <c r="D13" s="249" t="inlineStr">
+      <c r="D16" s="249" t="inlineStr">
         <is>
           <t>Profundidad (m)</t>
         </is>
       </c>
-      <c r="E13" s="249" t="inlineStr">
+      <c r="E16" s="249" t="inlineStr">
         <is>
           <t>Excavación (m³)</t>
         </is>
       </c>
-      <c r="F13" s="249" t="inlineStr">
+      <c r="F16" s="249" t="inlineStr">
         <is>
           <t>Fuente plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="250" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B14" s="250" t="inlineStr">
-        <is>
-          <t>625.06</t>
-        </is>
-      </c>
-      <c r="C14" s="250" t="inlineStr">
-        <is>
-          <t>604.97</t>
-        </is>
-      </c>
-      <c r="D14" s="250" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="E14" s="250" t="n">
-        <v>252.46</v>
-      </c>
-      <c r="F14" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="250" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B15" s="250" t="inlineStr">
-        <is>
-          <t>621.50</t>
-        </is>
-      </c>
-      <c r="C15" s="250" t="inlineStr">
-        <is>
-          <t>602.83</t>
-        </is>
-      </c>
-      <c r="D15" s="250" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="E15" s="250" t="n">
-        <v>234.61</v>
-      </c>
-      <c r="F15" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="250" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B16" s="250" t="inlineStr">
-        <is>
-          <t>619.18</t>
-        </is>
-      </c>
-      <c r="C16" s="250" t="inlineStr">
-        <is>
-          <t>601.88</t>
-        </is>
-      </c>
-      <c r="D16" s="250" t="inlineStr">
-        <is>
-          <t>17.30</t>
-        </is>
-      </c>
-      <c r="E16" s="250" t="n">
-        <v>217.4</v>
-      </c>
-      <c r="F16" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="250" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B17" s="250" t="inlineStr">
         <is>
-          <t>612.91</t>
+          <t>625.06</t>
         </is>
       </c>
       <c r="C17" s="250" t="inlineStr">
         <is>
-          <t>597.93</t>
+          <t>604.97</t>
         </is>
       </c>
       <c r="D17" s="250" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="E17" s="250" t="n">
-        <v>188.24</v>
+        <v>252.46</v>
       </c>
       <c r="F17" s="250" t="inlineStr">
         <is>
-          <t>STM38021</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="250" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B18" s="250" t="inlineStr">
         <is>
-          <t>610.70</t>
+          <t>621.50</t>
         </is>
       </c>
       <c r="C18" s="250" t="inlineStr">
         <is>
-          <t>595.46</t>
+          <t>602.83</t>
         </is>
       </c>
       <c r="D18" s="250" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="E18" s="250" t="n">
-        <v>191.51</v>
+        <v>234.61</v>
       </c>
       <c r="F18" s="250" t="inlineStr">
         <is>
-          <t>STM38021</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="250" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B19" s="250" t="inlineStr">
         <is>
-          <t>607.39</t>
+          <t>619.18</t>
         </is>
       </c>
       <c r="C19" s="250" t="inlineStr">
         <is>
-          <t>591.88</t>
+          <t>601.88</t>
         </is>
       </c>
       <c r="D19" s="250" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>17.30</t>
         </is>
       </c>
       <c r="E19" s="250" t="n">
-        <v>194.9</v>
+        <v>217.4</v>
       </c>
       <c r="F19" s="250" t="inlineStr">
         <is>
-          <t>STM38022</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="250" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B20" s="250" t="inlineStr">
         <is>
-          <t>603.15</t>
+          <t>612.91</t>
         </is>
       </c>
       <c r="C20" s="250" t="inlineStr">
         <is>
-          <t>587.53</t>
+          <t>597.93</t>
         </is>
       </c>
       <c r="D20" s="250" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="E20" s="250" t="n">
-        <v>196.29</v>
+        <v>188.24</v>
       </c>
       <c r="F20" s="250" t="inlineStr">
         <is>
-          <t>STM38022</t>
+          <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="250" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B21" s="250" t="inlineStr">
         <is>
-          <t>599.00</t>
+          <t>610.70</t>
         </is>
       </c>
       <c r="C21" s="250" t="inlineStr">
         <is>
-          <t>584.59</t>
+          <t>595.46</t>
         </is>
       </c>
       <c r="D21" s="250" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="E21" s="250" t="n">
-        <v>181.08</v>
+        <v>191.51</v>
       </c>
       <c r="F21" s="250" t="inlineStr">
         <is>
-          <t>STM38023</t>
+          <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="250" t="inlineStr">
         <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B22" s="250" t="inlineStr">
+        <is>
+          <t>607.39</t>
+        </is>
+      </c>
+      <c r="C22" s="250" t="inlineStr">
+        <is>
+          <t>591.88</t>
+        </is>
+      </c>
+      <c r="D22" s="250" t="inlineStr">
+        <is>
+          <t>15.51</t>
+        </is>
+      </c>
+      <c r="E22" s="250" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="F22" s="250" t="inlineStr">
+        <is>
+          <t>STM38022</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="250" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B23" s="250" t="inlineStr">
+        <is>
+          <t>603.15</t>
+        </is>
+      </c>
+      <c r="C23" s="250" t="inlineStr">
+        <is>
+          <t>587.53</t>
+        </is>
+      </c>
+      <c r="D23" s="250" t="inlineStr">
+        <is>
+          <t>15.62</t>
+        </is>
+      </c>
+      <c r="E23" s="250" t="n">
+        <v>196.29</v>
+      </c>
+      <c r="F23" s="250" t="inlineStr">
+        <is>
+          <t>STM38022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="250" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="B24" s="250" t="inlineStr">
+        <is>
+          <t>599.00</t>
+        </is>
+      </c>
+      <c r="C24" s="250" t="inlineStr">
+        <is>
+          <t>584.59</t>
+        </is>
+      </c>
+      <c r="D24" s="250" t="inlineStr">
+        <is>
+          <t>14.41</t>
+        </is>
+      </c>
+      <c r="E24" s="250" t="n">
+        <v>181.08</v>
+      </c>
+      <c r="F24" s="250" t="inlineStr">
+        <is>
+          <t>STM38023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="250" t="inlineStr">
+        <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B22" s="250" t="inlineStr">
+      <c r="B25" s="250" t="inlineStr">
         <is>
           <t>591.18</t>
         </is>
       </c>
-      <c r="C22" s="250" t="inlineStr">
+      <c r="C25" s="250" t="inlineStr">
         <is>
           <t>582.12</t>
         </is>
       </c>
-      <c r="D22" s="250" t="inlineStr">
+      <c r="D25" s="250" t="inlineStr">
         <is>
           <t>9.06</t>
         </is>
       </c>
-      <c r="E22" s="250" t="n">
+      <c r="E25" s="250" t="n">
         <v>113.85</v>
       </c>
-      <c r="F22" s="250" t="inlineStr">
+      <c r="F25" s="250" t="inlineStr">
         <is>
           <t>STM38023</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="247" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="247" t="inlineStr">
         <is>
           <t>⚠ Discrepancia P9: STM38109 §2.4 reporta 9.67m (referencia portal vs NV terreno). Diferencia 0.61m × 12.57m² = ~7.7 m³ excavación adicional si se usa cota portal.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="248" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="248" t="inlineStr">
         <is>
           <t>3. LONGITUDES DE TRAMOS — DM piques sucesivos</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="249" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="249" t="inlineStr">
         <is>
           <t>Tramo</t>
         </is>
       </c>
-      <c r="B26" s="249" t="inlineStr">
+      <c r="B29" s="249" t="inlineStr">
         <is>
           <t>Entre piques</t>
         </is>
       </c>
-      <c r="C26" s="249" t="inlineStr">
+      <c r="C29" s="249" t="inlineStr">
         <is>
           <t>DM inicio (m)</t>
         </is>
       </c>
-      <c r="D26" s="249" t="inlineStr">
+      <c r="D29" s="249" t="inlineStr">
         <is>
           <t>DM fin (m)</t>
         </is>
       </c>
-      <c r="E26" s="249" t="inlineStr">
+      <c r="E29" s="249" t="inlineStr">
         <is>
           <t>Longitud (m)</t>
         </is>
       </c>
-      <c r="F26" s="249" t="inlineStr">
+      <c r="F29" s="249" t="inlineStr">
         <is>
           <t>Fuente plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="250" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B27" s="250" t="inlineStr">
-        <is>
-          <t>P1-P2</t>
-        </is>
-      </c>
-      <c r="C27" s="250" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D27" s="250" t="inlineStr">
-        <is>
-          <t>389.0</t>
-        </is>
-      </c>
-      <c r="E27" s="250" t="inlineStr">
-        <is>
-          <t>389.0</t>
-        </is>
-      </c>
-      <c r="F27" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="250" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B28" s="250" t="inlineStr">
-        <is>
-          <t>P2-P3</t>
-        </is>
-      </c>
-      <c r="C28" s="250" t="inlineStr">
-        <is>
-          <t>389.0</t>
-        </is>
-      </c>
-      <c r="D28" s="250" t="inlineStr">
-        <is>
-          <t>560.6</t>
-        </is>
-      </c>
-      <c r="E28" s="250" t="inlineStr">
-        <is>
-          <t>171.6</t>
-        </is>
-      </c>
-      <c r="F28" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="250" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="B29" s="250" t="inlineStr">
-        <is>
-          <t>P3-P4</t>
-        </is>
-      </c>
-      <c r="C29" s="250" t="inlineStr">
-        <is>
-          <t>560.6</t>
-        </is>
-      </c>
-      <c r="D29" s="250" t="inlineStr">
-        <is>
-          <t>955.7</t>
-        </is>
-      </c>
-      <c r="E29" s="250" t="inlineStr">
-        <is>
-          <t>395.1</t>
-        </is>
-      </c>
-      <c r="F29" s="250" t="inlineStr">
-        <is>
-          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="250" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B30" s="250" t="inlineStr">
         <is>
-          <t>P4-P5</t>
+          <t>P1-P2</t>
         </is>
       </c>
       <c r="C30" s="250" t="inlineStr">
         <is>
-          <t>955.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" s="250" t="inlineStr">
         <is>
-          <t>1161.6</t>
+          <t>389.0</t>
         </is>
       </c>
       <c r="E30" s="250" t="inlineStr">
         <is>
-          <t>205.9</t>
+          <t>389.0</t>
         </is>
       </c>
       <c r="F30" s="250" t="inlineStr">
         <is>
-          <t>STM38021</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="250" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B31" s="250" t="inlineStr">
         <is>
-          <t>P5-P6</t>
+          <t>P2-P3</t>
         </is>
       </c>
       <c r="C31" s="250" t="inlineStr">
         <is>
-          <t>1161.6</t>
+          <t>389.0</t>
         </is>
       </c>
       <c r="D31" s="250" t="inlineStr">
         <is>
-          <t>1459.4</t>
+          <t>560.6</t>
         </is>
       </c>
       <c r="E31" s="250" t="inlineStr">
         <is>
-          <t>297.8</t>
+          <t>171.6</t>
         </is>
       </c>
       <c r="F31" s="250" t="inlineStr">
         <is>
-          <t>STM38021</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="250" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B32" s="250" t="inlineStr">
         <is>
-          <t>P6-P7</t>
+          <t>P3-P4</t>
         </is>
       </c>
       <c r="C32" s="250" t="inlineStr">
         <is>
-          <t>1459.4</t>
+          <t>560.6</t>
         </is>
       </c>
       <c r="D32" s="250" t="inlineStr">
         <is>
-          <t>1777.4</t>
+          <t>955.7</t>
         </is>
       </c>
       <c r="E32" s="250" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="F32" s="250" t="inlineStr">
         <is>
-          <t>STM38022</t>
+          <t>STM38020</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="250" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B33" s="250" t="inlineStr">
         <is>
-          <t>P7-P8</t>
+          <t>P4-P5</t>
         </is>
       </c>
       <c r="C33" s="250" t="inlineStr">
         <is>
-          <t>1777.4</t>
+          <t>955.7</t>
         </is>
       </c>
       <c r="D33" s="250" t="inlineStr">
         <is>
-          <t>2145.1</t>
+          <t>1161.6</t>
         </is>
       </c>
       <c r="E33" s="250" t="inlineStr">
         <is>
-          <t>367.7</t>
+          <t>205.9</t>
         </is>
       </c>
       <c r="F33" s="250" t="inlineStr">
         <is>
-          <t>STM38022</t>
+          <t>STM38021</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="250" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B34" s="250" t="inlineStr">
+        <is>
+          <t>P5-P6</t>
+        </is>
+      </c>
+      <c r="C34" s="250" t="inlineStr">
+        <is>
+          <t>1161.6</t>
+        </is>
+      </c>
+      <c r="D34" s="250" t="inlineStr">
+        <is>
+          <t>1459.4</t>
+        </is>
+      </c>
+      <c r="E34" s="250" t="inlineStr">
+        <is>
+          <t>297.8</t>
+        </is>
+      </c>
+      <c r="F34" s="250" t="inlineStr">
+        <is>
+          <t>STM38021</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="250" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B35" s="250" t="inlineStr">
+        <is>
+          <t>P6-P7</t>
+        </is>
+      </c>
+      <c r="C35" s="250" t="inlineStr">
+        <is>
+          <t>1459.4</t>
+        </is>
+      </c>
+      <c r="D35" s="250" t="inlineStr">
+        <is>
+          <t>1777.4</t>
+        </is>
+      </c>
+      <c r="E35" s="250" t="inlineStr">
+        <is>
+          <t>318.0</t>
+        </is>
+      </c>
+      <c r="F35" s="250" t="inlineStr">
+        <is>
+          <t>STM38022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="250" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B36" s="250" t="inlineStr">
+        <is>
+          <t>P7-P8</t>
+        </is>
+      </c>
+      <c r="C36" s="250" t="inlineStr">
+        <is>
+          <t>1777.4</t>
+        </is>
+      </c>
+      <c r="D36" s="250" t="inlineStr">
+        <is>
+          <t>2145.1</t>
+        </is>
+      </c>
+      <c r="E36" s="250" t="inlineStr">
+        <is>
+          <t>367.7</t>
+        </is>
+      </c>
+      <c r="F36" s="250" t="inlineStr">
+        <is>
+          <t>STM38022</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="250" t="inlineStr">
+        <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B34" s="250" t="inlineStr">
+      <c r="B37" s="250" t="inlineStr">
         <is>
           <t>P8-P9</t>
         </is>
       </c>
-      <c r="C34" s="250" t="inlineStr">
+      <c r="C37" s="250" t="inlineStr">
         <is>
           <t>2145.1</t>
         </is>
       </c>
-      <c r="D34" s="250" t="inlineStr">
+      <c r="D37" s="250" t="inlineStr">
         <is>
           <t>2454.2</t>
         </is>
       </c>
-      <c r="E34" s="250" t="inlineStr">
+      <c r="E37" s="250" t="inlineStr">
         <is>
           <t>309.1</t>
         </is>
       </c>
-      <c r="F34" s="250" t="inlineStr">
+      <c r="F37" s="250" t="inlineStr">
         <is>
           <t>STM38023</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="248" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="248" t="inlineStr">
         <is>
           <t>4. FÓRMULAS POR PARTIDA</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="249" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B37" s="249" t="inlineStr">
+      <c r="B40" s="249" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="C37" s="249" t="inlineStr">
+      <c r="C40" s="249" t="inlineStr">
         <is>
           <t>Fórmula aplicada</t>
         </is>
       </c>
-      <c r="D37" s="249" t="inlineStr">
+      <c r="D40" s="249" t="inlineStr">
         <is>
           <t>Cantidad total</t>
         </is>
       </c>
-      <c r="E37" s="249" t="inlineStr">
+      <c r="E40" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F37" s="249" t="inlineStr">
+      <c r="F40" s="249" t="inlineStr">
         <is>
           <t>Validación</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="255" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B38" s="255" t="inlineStr">
-        <is>
-          <t>Excavación piques</t>
-        </is>
-      </c>
-      <c r="C38" s="255" t="inlineStr">
-        <is>
-          <t>Σ (12.5664 m² × prof_i) para i=1..9</t>
-        </is>
-      </c>
-      <c r="D38" s="255" t="n">
-        <v>1770.34</v>
-      </c>
-      <c r="E38" s="255" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F38" s="255" t="inlineStr">
-        <is>
-          <t>✓ Coincide con suma manual</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="255" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B39" s="255" t="inlineStr">
-        <is>
-          <t>Retiro excavación piques</t>
-        </is>
-      </c>
-      <c r="C39" s="255">
-        <f> Excavación pique (igual volumen al botadero)</f>
-        <v/>
-      </c>
-      <c r="D39" s="255" t="n">
-        <v>1770.34</v>
-      </c>
-      <c r="E39" s="255" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F39" s="255" t="inlineStr">
-        <is>
-          <t>✓ = Excavación</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="255" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B40" s="255" t="inlineStr">
-        <is>
-          <t>Montaje liner pique</t>
-        </is>
-      </c>
-      <c r="C40" s="255" t="inlineStr">
-        <is>
-          <t>Σ profundidad_i para i=1..9</t>
-        </is>
-      </c>
-      <c r="D40" s="255" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="E40" s="255" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F40" s="255">
-        <f> longitud anillo × cantidad anillos</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="255" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B41" s="255" t="inlineStr">
         <is>
-          <t>Refuerzo losa anillo fondo (.4)</t>
+          <t>Excavación piques</t>
         </is>
       </c>
       <c r="C41" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques (suma alzada por pique)</t>
+          <t>Σ (12.5664 m² × prof_i) para i=1..9</t>
         </is>
       </c>
       <c r="D41" s="255" t="n">
-        <v>9</v>
+        <v>1770.34</v>
       </c>
       <c r="E41" s="255" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F41" s="255" t="inlineStr">
         <is>
-          <t>Cant 1 gl/pique — precio cotizar</t>
+          <t>✓ Coincide con suma manual</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="255" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B42" s="255" t="inlineStr">
         <is>
-          <t>Dren / Terminaciones / Cobertura / Refuerzo apertura</t>
-        </is>
-      </c>
-      <c r="C42" s="255" t="inlineStr">
-        <is>
-          <t>1 gl × 9 piques cada uno (items .5, .6, .7, .9)</t>
-        </is>
+          <t>Retiro excavación piques</t>
+        </is>
+      </c>
+      <c r="C42" s="255">
+        <f> Excavación pique (igual volumen al botadero)</f>
+        <v/>
       </c>
       <c r="D42" s="255" t="n">
-        <v>36</v>
+        <v>1770.34</v>
       </c>
       <c r="E42" s="255" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F42" s="255" t="inlineStr">
         <is>
-          <t>4 items × 9 piques = 36 gl en total</t>
+          <t>✓ = Excavación</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="255" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B43" s="255" t="inlineStr">
         <is>
-          <t>Montaje escalas+plataformas (.8)</t>
+          <t>Montaje liner pique</t>
         </is>
       </c>
       <c r="C43" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques (Aporte STM)</t>
+          <t>Σ profundidad_i para i=1..9</t>
         </is>
       </c>
       <c r="D43" s="255" t="n">
-        <v>9</v>
+        <v>140.9</v>
       </c>
       <c r="E43" s="255" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="F43" s="255" t="inlineStr">
-        <is>
-          <t>✓ Una unidad global por pique</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F43" s="255">
+        <f> longitud anillo × cantidad anillos</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="255" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B44" s="255" t="inlineStr">
         <is>
-          <t>Estructura soporte cables SS (.13)</t>
+          <t>Refuerzo losa anillo fondo (.4)</t>
         </is>
       </c>
       <c r="C44" s="255" t="inlineStr">
         <is>
-          <t>500 kg × 2 piques (P1, P9) — estimado acero galvanizado</t>
+          <t>1 gl × 9 piques (suma alzada por pique)</t>
         </is>
       </c>
       <c r="D44" s="255" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="E44" s="255" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="F44" s="255" t="inlineStr">
         <is>
-          <t>Solo SS Vitacura + SS Providencia</t>
+          <t>Cant 1 gl/pique — precio cotizar</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="255" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B45" s="255" t="inlineStr">
         <is>
-          <t>Brocal definitivo (.14 / .15)</t>
+          <t>Dren / Terminaciones / Cobertura / Refuerzo apertura</t>
         </is>
       </c>
       <c r="C45" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques</t>
+          <t>1 gl × 9 piques cada uno (items .5, .6, .7, .9)</t>
         </is>
       </c>
       <c r="D45" s="255" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E45" s="255" t="inlineStr">
         <is>
@@ -17080,975 +17086,997 @@
       </c>
       <c r="F45" s="255" t="inlineStr">
         <is>
-          <t>P1/P9 → ítem .15; P2-8 → ítem .14</t>
+          <t>4 items × 9 piques = 36 gl en total</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="255" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B46" s="255" t="inlineStr">
         <is>
-          <t>Shotcrete / Malla / Pernos (.10, .11, .12)</t>
+          <t>Montaje escalas+plataformas (.8)</t>
         </is>
       </c>
       <c r="C46" s="255" t="inlineStr">
         <is>
-          <t>Sin cant — depende RMR geotecnico (STM38019 pendiente)</t>
+          <t>1 gl × 9 piques (Aporte STM)</t>
         </is>
       </c>
       <c r="D46" s="255" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E46" s="255" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="F46" s="255" t="inlineStr">
         <is>
-          <t>⚠ Precios listados, cantidades en blanco</t>
+          <t>✓ Una unidad global por pique</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="255" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B47" s="255" t="inlineStr">
         <is>
-          <t>Excavación túnel</t>
+          <t>Estructura soporte cables SS (.13)</t>
         </is>
       </c>
       <c r="C47" s="255" t="inlineStr">
         <is>
-          <t>Σ (3.8359 m² × longitud_i) para i=1..8</t>
+          <t>500 kg × 2 piques (P1, P9) — estimado acero galvanizado</t>
         </is>
       </c>
       <c r="D47" s="255" t="n">
-        <v>9414.219999999999</v>
+        <v>1000</v>
       </c>
       <c r="E47" s="255" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F47" s="255" t="inlineStr">
         <is>
-          <t>Verifica: 3.8359 × 2454.2 = 9414.2 ✓</t>
+          <t>Solo SS Vitacura + SS Providencia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="255" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B48" s="255" t="inlineStr">
         <is>
-          <t>Radier túnel H30</t>
+          <t>Brocal definitivo (.14 / .15)</t>
         </is>
       </c>
       <c r="C48" s="255" t="inlineStr">
         <is>
-          <t>Σ (0.3315 m³/m × longitud_i) para i=1..8</t>
+          <t>1 gl × 9 piques</t>
         </is>
       </c>
       <c r="D48" s="255" t="n">
-        <v>813.58</v>
+        <v>9</v>
       </c>
       <c r="E48" s="255" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="F48" s="255" t="inlineStr">
         <is>
-          <t>Verifica: 0.3315 × 2454.2 = 813.6 ✓</t>
+          <t>P1/P9 → ítem .15; P2-8 → ítem .14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="255" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B49" s="255" t="inlineStr">
         <is>
-          <t>Monitoreo de Pernos (.8)</t>
+          <t>Shotcrete / Malla / Pernos Conv. (.10, .11, .12)</t>
         </is>
       </c>
       <c r="C49" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 8 tramos</t>
+          <t>EVENTUAL — Tabla 15 STM38019 medidas auxiliares condicionales</t>
         </is>
       </c>
       <c r="D49" s="255" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E49" s="255" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="255" t="inlineStr">
         <is>
-          <t>Item .8 del template (NO instalación cables)</t>
+          <t>✓ Eventual: sin cantidad sistemática (Bosc.Cord. Nivel 0)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="255" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B50" s="255" t="inlineStr">
         <is>
-          <t>Estructura soporte cables AT túnel (.12)</t>
+          <t>Excavación túnel</t>
         </is>
       </c>
       <c r="C50" s="255" t="inlineStr">
         <is>
-          <t>20 kg/ml × longitud_i para i=1..8 (acero galvanizado)</t>
+          <t>Σ (3.8359 m² × longitud_i) para i=1..8</t>
         </is>
       </c>
       <c r="D50" s="255" t="n">
-        <v>49084</v>
+        <v>9414.219999999999</v>
       </c>
       <c r="E50" s="255" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F50" s="255" t="inlineStr">
         <is>
-          <t>⚠ Estimado 20 kg/ml — confirmar diseño bandejas</t>
+          <t>Verifica: 3.8359 × 2454.2 = 9414.2 ✓</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="255" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B51" s="255" t="inlineStr">
+        <is>
+          <t>Radier túnel H30</t>
+        </is>
+      </c>
+      <c r="C51" s="255" t="inlineStr">
+        <is>
+          <t>Σ (0.3315 m³/m × longitud_i) para i=1..8</t>
+        </is>
+      </c>
+      <c r="D51" s="255" t="n">
+        <v>813.58</v>
+      </c>
+      <c r="E51" s="255" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F51" s="255" t="inlineStr">
+        <is>
+          <t>Verifica: 0.3315 × 2454.2 = 813.6 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="255" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B52" s="255" t="inlineStr">
+        <is>
+          <t>Monitoreo de Pernos (.8)</t>
+        </is>
+      </c>
+      <c r="C52" s="255" t="inlineStr">
+        <is>
+          <t>1 gl × 8 tramos</t>
+        </is>
+      </c>
+      <c r="D52" s="255" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="255" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="F52" s="255" t="inlineStr">
+        <is>
+          <t>Item .8 del template (NO instalación cables)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="255" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B53" s="255" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables AT túnel (.12)</t>
+        </is>
+      </c>
+      <c r="C53" s="255" t="inlineStr">
+        <is>
+          <t>20 kg/ml × longitud_i para i=1..8 (acero galvanizado)</t>
+        </is>
+      </c>
+      <c r="D53" s="255" t="n">
+        <v>49084</v>
+      </c>
+      <c r="E53" s="255" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F53" s="255" t="inlineStr">
+        <is>
+          <t>⚠ Estimado 20 kg/ml — confirmar diseño bandejas</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="255" t="inlineStr">
+        <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B51" s="255" t="inlineStr">
+      <c r="B54" s="255" t="inlineStr">
         <is>
           <t>Pernos frente / Shotcrete / Paraguas (.4, .5, .6)</t>
         </is>
       </c>
-      <c r="C51" s="255" t="inlineStr">
+      <c r="C54" s="255" t="inlineStr">
         <is>
           <t>Cantidades del template original (eventuales)</t>
         </is>
       </c>
-      <c r="D51" s="255" t="n">
+      <c r="D54" s="255" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="255" t="inlineStr">
+      <c r="E54" s="255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="255" t="inlineStr">
+      <c r="F54" s="255" t="inlineStr">
         <is>
           <t>Cant 'eventual' del cuadro precios STM</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="248" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="248" t="inlineStr">
         <is>
           <t>5. EQUIPAMIENTO ELÉCTRICO (Aporte STM — Sección 2 licitación)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="249" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B54" s="249" t="inlineStr">
+      <c r="B57" s="249" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="C54" s="249" t="inlineStr">
+      <c r="C57" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D54" s="249" t="inlineStr">
+      <c r="D57" s="249" t="inlineStr">
         <is>
           <t>Modelo / specs</t>
         </is>
       </c>
-      <c r="E54" s="249" t="inlineStr">
+      <c r="E57" s="249" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="F54" s="249" t="inlineStr">
+      <c r="F57" s="249" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="250" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="250" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B55" s="250" t="inlineStr">
+      <c r="B58" s="250" t="inlineStr">
         <is>
           <t>Jet Fan túnel</t>
         </is>
       </c>
-      <c r="C55" s="250" t="inlineStr">
+      <c r="C58" s="250" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D55" s="250" t="inlineStr">
+      <c r="D58" s="250" t="inlineStr">
         <is>
           <t>S&amp;P TJHT2/4-315-CN (0.8 kW, 24 N, 4500 m³/h)</t>
         </is>
       </c>
-      <c r="E55" s="250" t="inlineStr">
+      <c r="E58" s="250" t="inlineStr">
         <is>
           <t>Fan1 DM+70 → Fan23 DM+2380, cada 105 m</t>
         </is>
       </c>
-      <c r="F55" s="250" t="inlineStr">
+      <c r="F58" s="250" t="inlineStr">
         <is>
           <t>STM38109 §4.5 + Tabla 4.2 (REV.E 28-01-2026)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="250" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="250" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B56" s="250" t="inlineStr">
+      <c r="B59" s="250" t="inlineStr">
         <is>
           <t>Extractor pique</t>
         </is>
       </c>
-      <c r="C56" s="250" t="inlineStr">
+      <c r="C59" s="250" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="250" t="inlineStr">
+      <c r="D59" s="250" t="inlineStr">
         <is>
           <t>Soler-Palau TGT/6-1409 (37 kW, 132000 m³/h, Ø1409 mm)</t>
         </is>
       </c>
-      <c r="E56" s="250" t="inlineStr">
+      <c r="E59" s="250" t="inlineStr">
         <is>
           <t>bocas P1 (SS Vitacura) y P9 (SS Providencia)</t>
         </is>
       </c>
-      <c r="F56" s="250" t="inlineStr">
+      <c r="F59" s="250" t="inlineStr">
         <is>
           <t>STM38110 §3.1 + §3.14</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="248" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="248" t="inlineStr">
         <is>
           <t>6. SUPUESTOS CRÍTICOS Y VALIDACIONES PENDIENTES</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="249" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B59" s="249" t="inlineStr">
+      <c r="B62" s="249" t="inlineStr">
         <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C59" s="249" t="inlineStr">
+      <c r="C62" s="249" t="inlineStr">
         <is>
           <t>Valor usado</t>
         </is>
       </c>
-      <c r="D59" s="249" t="inlineStr">
+      <c r="D62" s="249" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="E59" s="249" t="inlineStr">
+      <c r="E62" s="249" t="inlineStr">
         <is>
           <t>Impacto si cambia</t>
         </is>
       </c>
-      <c r="F59" s="249" t="inlineStr">
+      <c r="F62" s="249" t="inlineStr">
         <is>
           <t>Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="255" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B60" s="255" t="inlineStr">
-        <is>
-          <t>N° túneles paralelos</t>
-        </is>
-      </c>
-      <c r="C60" s="255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D60" s="255" t="inlineStr">
-        <is>
-          <t>Diseño STM</t>
-        </is>
-      </c>
-      <c r="E60" s="255" t="inlineStr">
-        <is>
-          <t>Multiplicar Sec 5 por N</t>
-        </is>
-      </c>
-      <c r="F60" s="255" t="inlineStr">
-        <is>
-          <t>✓ Confirmado 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="255" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B61" s="255" t="inlineStr">
-        <is>
-          <t>Estructura soporte cables AT túnel (5.x.12)</t>
-        </is>
-      </c>
-      <c r="C61" s="255" t="inlineStr">
-        <is>
-          <t>20 kg/ml × 2454m = 49.084 kg</t>
-        </is>
-      </c>
-      <c r="D61" s="255" t="inlineStr">
-        <is>
-          <t>Estimado: 6 cables LAT 2×110kV, bandejas+soportes acero galv.</t>
-        </is>
-      </c>
-      <c r="E61" s="255" t="inlineStr">
-        <is>
-          <t>Si diseño real difiere → ajustar kg/ml</t>
-        </is>
-      </c>
-      <c r="F61" s="255" t="inlineStr">
-        <is>
-          <t>⚠ Confirmar plano bandejas</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="255" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B62" s="255" t="inlineStr">
-        <is>
-          <t>Estructura soporte cables SS (4.x.13)</t>
-        </is>
-      </c>
-      <c r="C62" s="255" t="inlineStr">
-        <is>
-          <t>500 kg × 2 (P1, P9) = 1.000 kg</t>
-        </is>
-      </c>
-      <c r="D62" s="255" t="inlineStr">
-        <is>
-          <t>Estimado por SS — racks, bandejas, terminales</t>
-        </is>
-      </c>
-      <c r="E62" s="255" t="inlineStr">
-        <is>
-          <t>Verificar plano SS Vitacura/Providencia</t>
-        </is>
-      </c>
-      <c r="F62" s="255" t="inlineStr">
-        <is>
-          <t>⚠ Estimado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="255" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B63" s="255" t="inlineStr">
         <is>
-          <t>Profundidad P9</t>
+          <t>N° túneles paralelos</t>
         </is>
       </c>
       <c r="C63" s="255" t="inlineStr">
         <is>
-          <t>9.06 m (NV)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" s="255" t="inlineStr">
         <is>
-          <t>STM38023 vs STM38109 (9.67m)</t>
+          <t>Diseño STM</t>
         </is>
       </c>
       <c r="E63" s="255" t="inlineStr">
         <is>
-          <t>Δ excav P9 = 7.7 m³</t>
+          <t>Multiplicar Sec 5 por N</t>
         </is>
       </c>
       <c r="F63" s="255" t="inlineStr">
         <is>
-          <t>⚠ Discrepancia 0.61m</t>
+          <t>✓ Confirmado 1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="255" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B64" s="255" t="inlineStr">
         <is>
-          <t>Diámetro liner interior</t>
+          <t>Estructura soporte cables AT túnel (5.x.12)</t>
         </is>
       </c>
       <c r="C64" s="255" t="inlineStr">
         <is>
-          <t>2.21 m</t>
+          <t>20 kg/ml × 2454m = 49.084 kg</t>
         </is>
       </c>
       <c r="D64" s="255" t="inlineStr">
         <is>
-          <t>STM38136 vs STM38109 (2.10m)</t>
+          <t>Estimado: 6 cables LAT 2×110kV, bandejas+soportes acero galv.</t>
         </is>
       </c>
       <c r="E64" s="255" t="inlineStr">
         <is>
-          <t>Δ sección = 0.38 m² (10%)</t>
+          <t>Si diseño real difiere → ajustar kg/ml</t>
         </is>
       </c>
       <c r="F64" s="255" t="inlineStr">
         <is>
-          <t>✓ 2.21m incluye espesor anillos</t>
+          <t>⚠ Confirmar plano bandejas</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="255" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B65" s="255" t="inlineStr">
         <is>
-          <t>Longitud túnel total</t>
+          <t>Estructura soporte cables SS (4.x.13)</t>
         </is>
       </c>
       <c r="C65" s="255" t="inlineStr">
         <is>
-          <t>2454.2 m</t>
+          <t>500 kg × 2 (P1, P9) = 1.000 kg</t>
         </is>
       </c>
       <c r="D65" s="255" t="inlineStr">
         <is>
-          <t>STM38020-23 suma DM</t>
+          <t>Estimado por SS — racks, bandejas, terminales</t>
         </is>
       </c>
       <c r="E65" s="255" t="inlineStr">
         <is>
-          <t>STM38109 redondea a 2450m</t>
+          <t>Verificar plano SS Vitacura/Providencia</t>
         </is>
       </c>
       <c r="F65" s="255" t="inlineStr">
         <is>
-          <t>✓ Diferencia 4.2m (0.17%)</t>
+          <t>⚠ Estimado</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="255" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B66" s="255" t="inlineStr">
         <is>
-          <t>Cantidades 4.x.10-12 (shotcrete/malla/pernos)</t>
+          <t>Profundidad P9</t>
         </is>
       </c>
       <c r="C66" s="255" t="inlineStr">
         <is>
-          <t>No cubicado — solo precio UF/u</t>
+          <t>9.06 m (NV)</t>
         </is>
       </c>
       <c r="D66" s="255" t="inlineStr">
         <is>
-          <t>Requiere RMR/Q rock mass STM38019</t>
+          <t>STM38023 vs STM38109 (9.67m)</t>
         </is>
       </c>
       <c r="E66" s="255" t="inlineStr">
         <is>
-          <t>Eventual según geotecnia</t>
+          <t>Δ excav P9 = 7.7 m³</t>
         </is>
       </c>
       <c r="F66" s="255" t="inlineStr">
         <is>
-          <t>⚠ Pendiente RMR</t>
+          <t>⚠ Discrepancia 0.61m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="255" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B67" s="255" t="inlineStr">
         <is>
-          <t>Items 4.x.4-7, 4.x.9 (suma alzada)</t>
+          <t>Diámetro liner interior</t>
         </is>
       </c>
       <c r="C67" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 9 piques cada uno</t>
+          <t>2.21 m</t>
         </is>
       </c>
       <c r="D67" s="255" t="inlineStr">
         <is>
-          <t>Refuerzo losa, dren, terminaciones, cobertura, refuerzo apertura</t>
+          <t>STM38136 vs STM38109 (2.10m)</t>
         </is>
       </c>
       <c r="E67" s="255" t="inlineStr">
         <is>
-          <t>Precios referenciales — cotizar</t>
+          <t>Δ sección = 0.38 m² (10%)</t>
         </is>
       </c>
       <c r="F67" s="255" t="inlineStr">
         <is>
-          <t>⚠ Suma alzada</t>
+          <t>✓ 2.21m incluye espesor anillos</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="255" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B68" s="255" t="inlineStr">
         <is>
-          <t>Monitoreo Pernos (5.x.8)</t>
+          <t>Longitud túnel total</t>
         </is>
       </c>
       <c r="C68" s="255" t="inlineStr">
         <is>
-          <t>1 gl × 8 tramos</t>
+          <t>2454.2 m</t>
         </is>
       </c>
       <c r="D68" s="255" t="inlineStr">
         <is>
-          <t>Item correcto del template (NO instalación cables — bug v3)</t>
+          <t>STM38020-23 suma DM</t>
         </is>
       </c>
       <c r="E68" s="255" t="inlineStr">
         <is>
-          <t>Cant 1 gl/tramo es estándar</t>
+          <t>STM38109 redondea a 2450m</t>
         </is>
       </c>
       <c r="F68" s="255" t="inlineStr">
         <is>
-          <t>✓ Corregido v4</t>
+          <t>✓ Diferencia 4.2m (0.17%)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="255" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B69" s="255" t="inlineStr">
         <is>
-          <t>UF referencial</t>
+          <t>Cantidades 4.x.10-12 (shotcrete/malla/pernos)</t>
         </is>
       </c>
       <c r="C69" s="255" t="inlineStr">
         <is>
-          <t>38.500 CLP</t>
+          <t>EVENTUAL — sin cantidad sistemática</t>
         </is>
       </c>
       <c r="D69" s="255" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>STM38019 §7+§8: Tabla 15 medidas auxiliares condicionales; Boscarding Cording Nivel 0 (deformaciones &lt;1mm)</t>
         </is>
       </c>
       <c r="E69" s="255" t="inlineStr">
         <is>
-          <t>Actualizar al mes oferta</t>
+          <t>Solo se aplica si terreno lo requiere</t>
         </is>
       </c>
       <c r="F69" s="255" t="inlineStr">
         <is>
-          <t>✓ Configurable</t>
+          <t>✓ Eventual confirmado</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="255" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B70" s="255" t="inlineStr">
         <is>
-          <t>Altura excavación = profundidad NV</t>
+          <t>Items 4.x.4-7, 4.x.9 (suma alzada)</t>
         </is>
       </c>
       <c r="C70" s="255" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>1 gl × 9 piques cada uno</t>
         </is>
       </c>
       <c r="D70" s="255" t="inlineStr">
         <is>
-          <t>Convención técnica</t>
+          <t>Refuerzo losa, dren, terminaciones, cobertura, refuerzo apertura</t>
         </is>
       </c>
       <c r="E70" s="255" t="inlineStr">
         <is>
-          <t>Si sump existe → +volumen</t>
+          <t>Precios referenciales — cotizar</t>
         </is>
       </c>
       <c r="F70" s="255" t="inlineStr">
         <is>
-          <t>⚠ STM38023 nota 'Nivel -3.50' en P9</t>
+          <t>⚠ Suma alzada</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="255" t="inlineStr">
         <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B71" s="255" t="inlineStr">
+        <is>
+          <t>Monitoreo Pernos (5.x.8)</t>
+        </is>
+      </c>
+      <c r="C71" s="255" t="inlineStr">
+        <is>
+          <t>1 gl × 8 tramos</t>
+        </is>
+      </c>
+      <c r="D71" s="255" t="inlineStr">
+        <is>
+          <t>Item correcto del template (NO instalación cables — bug v3)</t>
+        </is>
+      </c>
+      <c r="E71" s="255" t="inlineStr">
+        <is>
+          <t>Cant 1 gl/tramo es estándar</t>
+        </is>
+      </c>
+      <c r="F71" s="255" t="inlineStr">
+        <is>
+          <t>✓ Corregido v4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="255" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="B72" s="255" t="inlineStr">
+        <is>
+          <t>UF referencial</t>
+        </is>
+      </c>
+      <c r="C72" s="255" t="inlineStr">
+        <is>
+          <t>38.500 CLP</t>
+        </is>
+      </c>
+      <c r="D72" s="255" t="inlineStr">
+        <is>
+          <t>Mayo 2026</t>
+        </is>
+      </c>
+      <c r="E72" s="255" t="inlineStr">
+        <is>
+          <t>Actualizar al mes oferta</t>
+        </is>
+      </c>
+      <c r="F72" s="255" t="inlineStr">
+        <is>
+          <t>✓ Configurable</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="255" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="B73" s="255" t="inlineStr">
+        <is>
+          <t>Altura excavación = profundidad NV</t>
+        </is>
+      </c>
+      <c r="C73" s="255" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D73" s="255" t="inlineStr">
+        <is>
+          <t>Convención técnica</t>
+        </is>
+      </c>
+      <c r="E73" s="255" t="inlineStr">
+        <is>
+          <t>Si sump existe → +volumen</t>
+        </is>
+      </c>
+      <c r="F73" s="255" t="inlineStr">
+        <is>
+          <t>⚠ STM38023 nota 'Nivel -3.50' en P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="255" t="inlineStr">
+        <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="B71" s="255" t="inlineStr">
+      <c r="B74" s="255" t="inlineStr">
         <is>
           <t>Plazo proyecto (Costos Indirectos)</t>
         </is>
       </c>
-      <c r="C71" s="255" t="inlineStr">
+      <c r="C74" s="255" t="inlineStr">
         <is>
           <t>24 meses</t>
         </is>
       </c>
-      <c r="D71" s="255" t="inlineStr">
+      <c r="D74" s="255" t="inlineStr">
         <is>
           <t>Estimado proyecto OOCC tunneling 2.45km + 9 piques</t>
         </is>
       </c>
-      <c r="E71" s="255" t="inlineStr">
+      <c r="E74" s="255" t="inlineStr">
         <is>
           <t>Cada mes adicional × 1.300 UF/mes indirecto</t>
         </is>
       </c>
-      <c r="F71" s="255" t="inlineStr">
+      <c r="F74" s="255" t="inlineStr">
         <is>
           <t>⚠ Verificar Bases Técnicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="248" t="inlineStr">
-        <is>
-          <t>7. TRAZABILIDAD DE FUENTES (documentos consultados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="249" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B74" s="249" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="C74" s="249" t="inlineStr">
-        <is>
-          <t>Revisión</t>
-        </is>
-      </c>
-      <c r="D74" s="249" t="inlineStr">
-        <is>
-          <t>Datos extraídos</t>
-        </is>
-      </c>
-      <c r="E74" s="249" t="inlineStr">
-        <is>
-          <t>Hoja relevante</t>
-        </is>
-      </c>
-      <c r="F74" s="249" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="255" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="B75" s="255" t="inlineStr">
         <is>
-          <t>STM38020 Planta y Perfil</t>
+          <t>Estratigrafía (3 estratos)</t>
         </is>
       </c>
       <c r="C75" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>H1 Relleno 0-3.45m / H2 Grava 2° 3.45-7.50m / H3 Grava 1° 7.50-20m</t>
         </is>
       </c>
       <c r="D75" s="255" t="inlineStr">
         <is>
-          <t>P1, P2, P3 NV + DM tramos T1-T3</t>
+          <t>STM38019 §4.1.1 Tabla 1 — 'Gravas de Santiago'</t>
         </is>
       </c>
       <c r="E75" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F75" s="255" t="inlineStr"/>
+          <t>Túnel principalmente en Grava 1° (φ'=45°, c'=35 kPa)</t>
+        </is>
+      </c>
+      <c r="F75" s="255" t="inlineStr">
+        <is>
+          <t>✓ Confirmado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="255" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="B76" s="255" t="inlineStr">
         <is>
-          <t>STM38021 Planta y Perfil</t>
+          <t>Napa freática</t>
         </is>
       </c>
       <c r="C76" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>25-35 m bajo superficie</t>
         </is>
       </c>
       <c r="D76" s="255" t="inlineStr">
         <is>
-          <t>P4, P5 NV + DM tramos T3-T5</t>
+          <t>STM38019 §4.2 — bajo nivel cota túnel</t>
         </is>
       </c>
       <c r="E76" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F76" s="255" t="inlineStr"/>
+          <t>Túnel NO estanco — sistema captación aguas Fig 66</t>
+        </is>
+      </c>
+      <c r="F76" s="255" t="inlineStr">
+        <is>
+          <t>✓ Sin presión hidrostática diseño</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="255" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="B77" s="255" t="inlineStr">
         <is>
-          <t>STM38022 Planta y Perfil</t>
+          <t>Pernos Marchiavanti (sostenimiento bóveda)</t>
         </is>
       </c>
       <c r="C77" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>L=4m traslape 1.5m / L=2m traslape 1.0m</t>
         </is>
       </c>
       <c r="D77" s="255" t="inlineStr">
         <is>
-          <t>P6, P7 NV + DM tramos T5-T7</t>
+          <t>STM38019 §7 Fig 64 — eventual según riesgo</t>
         </is>
       </c>
       <c r="E77" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F77" s="255" t="inlineStr"/>
+          <t>Cant. ya en template 5.x.4 + 5.9.1/5.9.2</t>
+        </is>
+      </c>
+      <c r="F77" s="255" t="inlineStr">
+        <is>
+          <t>✓ Cant del mandante</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="255" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="B78" s="255" t="inlineStr">
         <is>
-          <t>STM38023 Planta y Perfil</t>
+          <t>Boscarding Cording (afectaciones)</t>
         </is>
       </c>
       <c r="C78" s="255" t="inlineStr">
         <is>
-          <t>REV.0</t>
+          <t>Nivel 0 (despreciable) en TODOS los cruces</t>
         </is>
       </c>
       <c r="D78" s="255" t="inlineStr">
         <is>
-          <t>P8, P9 NV + DM tramos T7-T8</t>
+          <t>STM38019 §8 — Costanera Norte, Mapocho Limpio, San Carlos, L7 Metro</t>
         </is>
       </c>
       <c r="E78" s="255" t="inlineStr">
         <is>
-          <t>Detalle Costo Directo</t>
-        </is>
-      </c>
-      <c r="F78" s="255" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="255" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="B79" s="255" t="inlineStr">
-        <is>
-          <t>STM38109 Memoria Ventilación</t>
-        </is>
-      </c>
-      <c r="C79" s="255" t="inlineStr">
-        <is>
-          <t>REV.E 28-01-2026</t>
-        </is>
-      </c>
-      <c r="D79" s="255" t="inlineStr">
-        <is>
-          <t>23 jet fans S&amp;P TJHT2/4-315-CN, ubicación Tabla 4.2</t>
-        </is>
-      </c>
-      <c r="E79" s="255" t="inlineStr">
-        <is>
-          <t>Sec 5 supuestos</t>
-        </is>
-      </c>
-      <c r="F79" s="255" t="inlineStr"/>
+          <t>Sin requerimiento extra de monitoreo intensivo</t>
+        </is>
+      </c>
+      <c r="F78" s="255" t="inlineStr">
+        <is>
+          <t>✓ Bajo riesgo confirmado</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="255" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="B80" s="255" t="inlineStr">
-        <is>
-          <t>STM38110 ETP Equipos Ventilación</t>
-        </is>
-      </c>
-      <c r="C80" s="255" t="inlineStr">
-        <is>
-          <t>REV.0 14-11-2025</t>
-        </is>
-      </c>
-      <c r="D80" s="255" t="inlineStr">
-        <is>
-          <t>2 extractores Soler-Palau TGT/6-1409, modelo jet fan</t>
-        </is>
-      </c>
-      <c r="E80" s="255" t="inlineStr">
-        <is>
-          <t>Sec 5 supuestos</t>
-        </is>
-      </c>
-      <c r="F80" s="255" t="inlineStr"/>
+      <c r="A80" s="248" t="inlineStr">
+        <is>
+          <t>7. TRAZABILIDAD DE FUENTES (documentos consultados)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="255" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="B81" s="255" t="inlineStr">
-        <is>
-          <t>STM38019 Geotécnica</t>
-        </is>
-      </c>
-      <c r="C81" s="255" t="inlineStr">
+      <c r="A81" s="249" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B81" s="249" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="C81" s="249" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="D81" s="249" t="inlineStr">
+        <is>
+          <t>Datos extraídos</t>
+        </is>
+      </c>
+      <c r="E81" s="249" t="inlineStr">
+        <is>
+          <t>Hoja relevante</t>
+        </is>
+      </c>
+      <c r="F81" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D81" s="255" t="inlineStr">
-        <is>
-          <t>Estratigrafía H1-H3 (Relleno/Grava 2°/Grava 1°)</t>
-        </is>
-      </c>
-      <c r="E81" s="255" t="inlineStr">
-        <is>
-          <t>Pendiente RMR para 4.x.10-12</t>
-        </is>
-      </c>
-      <c r="F81" s="255" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="255" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B82" s="255" t="inlineStr">
         <is>
-          <t>STM38136 Planos eléctricos</t>
+          <t>STM38020 Planta y Perfil</t>
         </is>
       </c>
       <c r="C82" s="255" t="inlineStr">
         <is>
-          <t>REV.1 06/04/2026</t>
+          <t>REV.0</t>
         </is>
       </c>
       <c r="D82" s="255" t="inlineStr">
         <is>
-          <t>Ø interior pique 4.0m, Ø interior liner 2.21m</t>
+          <t>P1, P2, P3 NV + DM tramos T1-T3</t>
         </is>
       </c>
       <c r="E82" s="255" t="inlineStr">
         <is>
-          <t>Sec 1 constantes</t>
+          <t>Detalle Costo Directo</t>
         </is>
       </c>
       <c r="F82" s="255" t="inlineStr"/>
@@ -18056,27 +18084,27 @@
     <row r="83">
       <c r="A83" s="255" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B83" s="255" t="inlineStr">
         <is>
-          <t>BAE Licitación 2025-25-TX-SS-RM</t>
+          <t>STM38021 Planta y Perfil</t>
         </is>
       </c>
       <c r="C83" s="255" t="inlineStr">
         <is>
-          <t>REV.0 13/04/2026</t>
+          <t>REV.0</t>
         </is>
       </c>
       <c r="D83" s="255" t="inlineStr">
         <is>
-          <t>Estructura items 4.x y 5.x</t>
+          <t>P4, P5 NV + DM tramos T3-T5</t>
         </is>
       </c>
       <c r="E83" s="255" t="inlineStr">
         <is>
-          <t>A) Detalle</t>
+          <t>Detalle Costo Directo</t>
         </is>
       </c>
       <c r="F83" s="255" t="inlineStr"/>
@@ -18084,249 +18112,283 @@
     <row r="84">
       <c r="A84" s="255" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B84" s="255" t="inlineStr">
+        <is>
+          <t>STM38022 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C84" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D84" s="255" t="inlineStr">
+        <is>
+          <t>P6, P7 NV + DM tramos T5-T7</t>
+        </is>
+      </c>
+      <c r="E84" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F84" s="255" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="255" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B85" s="255" t="inlineStr">
+        <is>
+          <t>STM38023 Planta y Perfil</t>
+        </is>
+      </c>
+      <c r="C85" s="255" t="inlineStr">
+        <is>
+          <t>REV.0</t>
+        </is>
+      </c>
+      <c r="D85" s="255" t="inlineStr">
+        <is>
+          <t>P8, P9 NV + DM tramos T7-T8</t>
+        </is>
+      </c>
+      <c r="E85" s="255" t="inlineStr">
+        <is>
+          <t>Detalle Costo Directo</t>
+        </is>
+      </c>
+      <c r="F85" s="255" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="255" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="B86" s="255" t="inlineStr">
+        <is>
+          <t>STM38109 Memoria Ventilación</t>
+        </is>
+      </c>
+      <c r="C86" s="255" t="inlineStr">
+        <is>
+          <t>REV.E 28-01-2026</t>
+        </is>
+      </c>
+      <c r="D86" s="255" t="inlineStr">
+        <is>
+          <t>23 jet fans S&amp;P TJHT2/4-315-CN, ubicación Tabla 4.2</t>
+        </is>
+      </c>
+      <c r="E86" s="255" t="inlineStr">
+        <is>
+          <t>Sec 5 supuestos</t>
+        </is>
+      </c>
+      <c r="F86" s="255" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="255" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B87" s="255" t="inlineStr">
+        <is>
+          <t>STM38110 ETP Equipos Ventilación</t>
+        </is>
+      </c>
+      <c r="C87" s="255" t="inlineStr">
+        <is>
+          <t>REV.0 14-11-2025</t>
+        </is>
+      </c>
+      <c r="D87" s="255" t="inlineStr">
+        <is>
+          <t>2 extractores Soler-Palau TGT/6-1409, modelo jet fan</t>
+        </is>
+      </c>
+      <c r="E87" s="255" t="inlineStr">
+        <is>
+          <t>Sec 5 supuestos</t>
+        </is>
+      </c>
+      <c r="F87" s="255" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="255" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="B88" s="255" t="inlineStr">
+        <is>
+          <t>STM38019 Informe No-Afecciones (NATM, FLAC3D)</t>
+        </is>
+      </c>
+      <c r="C88" s="255" t="inlineStr">
+        <is>
+          <t>REV.0 15-01-2026</t>
+        </is>
+      </c>
+      <c r="D88" s="255" t="inlineStr">
+        <is>
+          <t>Estratigrafía H1-H3 + Parámetros geotécnicos + Espesor revestimiento (10cm estándar, 20cm reforzado) + Avance 0.46m + Tabla 15 medidas eventuales + Boscarding Cording Nivel 0</t>
+        </is>
+      </c>
+      <c r="E88" s="255" t="inlineStr">
+        <is>
+          <t>Sec 1 constantes + Sec 6 supuestos</t>
+        </is>
+      </c>
+      <c r="F88" s="255" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="255" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="B89" s="255" t="inlineStr">
+        <is>
+          <t>STM38136 Planos eléctricos</t>
+        </is>
+      </c>
+      <c r="C89" s="255" t="inlineStr">
+        <is>
+          <t>REV.1 06/04/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="255" t="inlineStr">
+        <is>
+          <t>Ø interior pique 4.0m, Ø interior liner 2.21m</t>
+        </is>
+      </c>
+      <c r="E89" s="255" t="inlineStr">
+        <is>
+          <t>Sec 1 constantes</t>
+        </is>
+      </c>
+      <c r="F89" s="255" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="255" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="B90" s="255" t="inlineStr">
+        <is>
+          <t>BAE Licitación 2025-25-TX-SS-RM</t>
+        </is>
+      </c>
+      <c r="C90" s="255" t="inlineStr">
+        <is>
+          <t>REV.0 13/04/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="255" t="inlineStr">
+        <is>
+          <t>Estructura items 4.x y 5.x</t>
+        </is>
+      </c>
+      <c r="E90" s="255" t="inlineStr">
+        <is>
+          <t>A) Detalle</t>
+        </is>
+      </c>
+      <c r="F90" s="255" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="255" t="inlineStr">
+        <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="B84" s="255" t="inlineStr">
+      <c r="B91" s="255" t="inlineStr">
         <is>
           <t>IF SS Vitacura</t>
         </is>
       </c>
-      <c r="C84" s="255" t="inlineStr">
+      <c r="C91" s="255" t="inlineStr">
         <is>
           <t>20251009 (3 etapas)</t>
         </is>
       </c>
-      <c r="D84" s="255" t="inlineStr">
+      <c r="D91" s="255" t="inlineStr">
         <is>
           <t>Composición Instalación de Faenas</t>
         </is>
       </c>
-      <c r="E84" s="255" t="inlineStr">
+      <c r="E91" s="255" t="inlineStr">
         <is>
           <t>Sec 3 supuestos suma alzada</t>
         </is>
       </c>
-      <c r="F84" s="255" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="248" t="inlineStr">
+      <c r="F91" s="255" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="248" t="inlineStr">
         <is>
           <t>8. RESUMEN TOTALES CUBICADOS</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="249" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B87" s="249" t="inlineStr">
+      <c r="B94" s="249" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C87" s="249" t="inlineStr">
+      <c r="C94" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D87" s="249" t="inlineStr">
+      <c r="D94" s="249" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="E87" s="249" t="inlineStr">
+      <c r="E94" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F87" s="249" t="inlineStr">
+      <c r="F94" s="249" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="250" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B88" s="250" t="inlineStr">
-        <is>
-          <t>Excavación piques (suma)</t>
-        </is>
-      </c>
-      <c r="C88" s="250" t="n">
-        <v>1770.34</v>
-      </c>
-      <c r="D88" s="250" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E88" s="250" t="inlineStr"/>
-      <c r="F88" s="250" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="250" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B89" s="250" t="inlineStr">
-        <is>
-          <t>Excavación túnel (suma)</t>
-        </is>
-      </c>
-      <c r="C89" s="250" t="n">
-        <v>9414.219999999999</v>
-      </c>
-      <c r="D89" s="250" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E89" s="250" t="inlineStr"/>
-      <c r="F89" s="250" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="250" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="B90" s="250" t="inlineStr">
-        <is>
-          <t>Liner pique (suma profundidades)</t>
-        </is>
-      </c>
-      <c r="C90" s="250" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="D90" s="250" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E90" s="250" t="inlineStr"/>
-      <c r="F90" s="250" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="250" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="B91" s="250" t="inlineStr">
-        <is>
-          <t>Liner túnel (longitud total)</t>
-        </is>
-      </c>
-      <c r="C91" s="250" t="n">
-        <v>2454.2</v>
-      </c>
-      <c r="D91" s="250" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E91" s="250" t="inlineStr"/>
-      <c r="F91" s="250" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="250" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="B92" s="250" t="inlineStr">
-        <is>
-          <t>Radier H30</t>
-        </is>
-      </c>
-      <c r="C92" s="250" t="n">
-        <v>813.58</v>
-      </c>
-      <c r="D92" s="250" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E92" s="250" t="inlineStr"/>
-      <c r="F92" s="250" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="250" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="B93" s="250" t="inlineStr">
-        <is>
-          <t>Estructura soporte cables AT túnel (5.x.12)</t>
-        </is>
-      </c>
-      <c r="C93" s="250" t="n">
-        <v>49084</v>
-      </c>
-      <c r="D93" s="250" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E93" s="250" t="inlineStr">
-        <is>
-          <t>(20 kg/ml × 2454m)</t>
-        </is>
-      </c>
-      <c r="F93" s="250" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="250" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="B94" s="250" t="inlineStr">
-        <is>
-          <t>Estructura soporte cables SS (4.x.13)</t>
-        </is>
-      </c>
-      <c r="C94" s="250" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D94" s="250" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E94" s="250" t="inlineStr">
-        <is>
-          <t>(500 kg × P1+P9 = 1000 kg)</t>
-        </is>
-      </c>
-      <c r="F94" s="250" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="250" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B95" s="250" t="inlineStr">
         <is>
-          <t>Escalas+plataformas</t>
+          <t>Excavación piques (suma)</t>
         </is>
       </c>
       <c r="C95" s="250" t="n">
-        <v>9</v>
+        <v>1770.34</v>
       </c>
       <c r="D95" s="250" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E95" s="250" t="inlineStr"/>
@@ -18335,20 +18397,20 @@
     <row r="96">
       <c r="A96" s="250" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B96" s="250" t="inlineStr">
         <is>
-          <t>Brocales definitivos</t>
+          <t>Excavación túnel (suma)</t>
         </is>
       </c>
       <c r="C96" s="250" t="n">
-        <v>9</v>
+        <v>9414.219999999999</v>
       </c>
       <c r="D96" s="250" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E96" s="250" t="inlineStr"/>
@@ -18357,391 +18419,329 @@
     <row r="97">
       <c r="A97" s="250" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B97" s="250" t="inlineStr">
         <is>
-          <t>Monitoreo de Pernos (5.x.8)</t>
+          <t>Liner pique (suma profundidades)</t>
         </is>
       </c>
       <c r="C97" s="250" t="n">
-        <v>8</v>
+        <v>140.9</v>
       </c>
       <c r="D97" s="250" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="E97" s="250" t="inlineStr">
-        <is>
-          <t>(1 gl × 8 tramos)</t>
-        </is>
-      </c>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E97" s="250" t="inlineStr"/>
       <c r="F97" s="250" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="250" t="inlineStr">
         <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B98" s="250" t="inlineStr">
+        <is>
+          <t>Liner túnel (longitud total)</t>
+        </is>
+      </c>
+      <c r="C98" s="250" t="n">
+        <v>2454.2</v>
+      </c>
+      <c r="D98" s="250" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E98" s="250" t="inlineStr"/>
+      <c r="F98" s="250" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="250" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B99" s="250" t="inlineStr">
+        <is>
+          <t>Radier H30</t>
+        </is>
+      </c>
+      <c r="C99" s="250" t="n">
+        <v>813.58</v>
+      </c>
+      <c r="D99" s="250" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E99" s="250" t="inlineStr"/>
+      <c r="F99" s="250" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="250" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="B100" s="250" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables AT túnel (5.x.12)</t>
+        </is>
+      </c>
+      <c r="C100" s="250" t="n">
+        <v>49084</v>
+      </c>
+      <c r="D100" s="250" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E100" s="250" t="inlineStr">
+        <is>
+          <t>(20 kg/ml × 2454m)</t>
+        </is>
+      </c>
+      <c r="F100" s="250" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="250" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="B101" s="250" t="inlineStr">
+        <is>
+          <t>Estructura soporte cables SS (4.x.13)</t>
+        </is>
+      </c>
+      <c r="C101" s="250" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D101" s="250" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E101" s="250" t="inlineStr">
+        <is>
+          <t>(500 kg × P1+P9 = 1000 kg)</t>
+        </is>
+      </c>
+      <c r="F101" s="250" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="250" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="B102" s="250" t="inlineStr">
+        <is>
+          <t>Escalas+plataformas</t>
+        </is>
+      </c>
+      <c r="C102" s="250" t="n">
+        <v>9</v>
+      </c>
+      <c r="D102" s="250" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="E102" s="250" t="inlineStr"/>
+      <c r="F102" s="250" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="250" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="B103" s="250" t="inlineStr">
+        <is>
+          <t>Brocales definitivos</t>
+        </is>
+      </c>
+      <c r="C103" s="250" t="n">
+        <v>9</v>
+      </c>
+      <c r="D103" s="250" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="E103" s="250" t="inlineStr"/>
+      <c r="F103" s="250" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="250" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="B104" s="250" t="inlineStr">
+        <is>
+          <t>Monitoreo de Pernos (5.x.8)</t>
+        </is>
+      </c>
+      <c r="C104" s="250" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="250" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="E104" s="250" t="inlineStr">
+        <is>
+          <t>(1 gl × 8 tramos)</t>
+        </is>
+      </c>
+      <c r="F104" s="250" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="250" t="inlineStr">
+        <is>
           <t>8.11</t>
         </is>
       </c>
-      <c r="B98" s="250" t="inlineStr">
+      <c r="B105" s="250" t="inlineStr">
         <is>
           <t>Items suma alzada piques (4.x.4-7, 4.x.9)</t>
         </is>
       </c>
-      <c r="C98" s="250" t="n">
+      <c r="C105" s="250" t="n">
         <v>45</v>
       </c>
-      <c r="D98" s="250" t="inlineStr">
+      <c r="D105" s="250" t="inlineStr">
         <is>
           <t>gl</t>
         </is>
       </c>
-      <c r="E98" s="250" t="inlineStr">
+      <c r="E105" s="250" t="inlineStr">
         <is>
           <t>(5 items × 9 piques = 45 gl)</t>
         </is>
       </c>
-      <c r="F98" s="250" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="248" t="inlineStr">
+      <c r="F105" s="250" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="248" t="inlineStr">
         <is>
           <t>9. RACIONALES COSTOS INDIRECTOS, GG Y UTILIDAD (hoja B)</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="249" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="249" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B101" s="249" t="inlineStr">
+      <c r="B108" s="249" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C101" s="249" t="inlineStr">
+      <c r="C108" s="249" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D101" s="249" t="inlineStr">
+      <c r="D108" s="249" t="inlineStr">
         <is>
           <t>Tiempo</t>
         </is>
       </c>
-      <c r="E101" s="249" t="inlineStr">
+      <c r="E108" s="249" t="inlineStr">
         <is>
           <t>Precio UF/u</t>
         </is>
       </c>
-      <c r="F101" s="249" t="inlineStr">
+      <c r="F108" s="249" t="inlineStr">
         <is>
           <t>Subtotal UF / Justificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="260" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="B102" s="260" t="inlineStr">
-        <is>
-          <t>Plazo referencial proyecto</t>
-        </is>
-      </c>
-      <c r="C102" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D102" s="260" t="inlineStr">
-        <is>
-          <t>24 meses</t>
-        </is>
-      </c>
-      <c r="E102" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F102" s="260" t="inlineStr">
-        <is>
-          <t>Estimado tunneling 2.45km — verificar Bases Técnicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="260" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B103" s="260" t="inlineStr">
-        <is>
-          <t>Vigilancia 24h externalizada</t>
-        </is>
-      </c>
-      <c r="C103" s="260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D103" s="260" t="inlineStr">
-        <is>
-          <t>24 m</t>
-        </is>
-      </c>
-      <c r="E103" s="260" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F103" s="260" t="inlineStr">
-        <is>
-          <t>2,400 UF — servicio integral 4 guardias rotación</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="260" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B104" s="260" t="inlineStr">
-        <is>
-          <t>Personal indirecto (8 personas, sueldo UF/mes)</t>
-        </is>
-      </c>
-      <c r="C104" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D104" s="260" t="inlineStr">
-        <is>
-          <t>24 m</t>
-        </is>
-      </c>
-      <c r="E104" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F104" s="260" t="inlineStr">
-        <is>
-          <t>18,840 UF total. Admin 150, JT 120, 2×Sup 90, Prev 80, MA 70, Topo 80, Tra 55, Bod 50 UF/mes (mid-range Chile 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="260" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B105" s="260" t="inlineStr">
-        <is>
-          <t>Maquinarias y vehículos</t>
-        </is>
-      </c>
-      <c r="C105" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D105" s="260" t="inlineStr">
-        <is>
-          <t>24 m</t>
-        </is>
-      </c>
-      <c r="E105" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="260" t="inlineStr">
-        <is>
-          <t>6,360 UF — 3 camionetas (35), fletes (50), andamios (30), equipos menores (80) UF/mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="260" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B106" s="260" t="inlineStr">
-        <is>
-          <t>Disposición residuos + excedentes</t>
-        </is>
-      </c>
-      <c r="C106" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D106" s="260" t="inlineStr">
-        <is>
-          <t>24 m</t>
-        </is>
-      </c>
-      <c r="E106" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F106" s="260" t="inlineStr">
-        <is>
-          <t>4,080 UF — residuos sólidos (50), excedentes excavación (120) UF/mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="260" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="B107" s="260" t="inlineStr">
-        <is>
-          <t>TOTAL COSTOS INDIRECTOS</t>
-        </is>
-      </c>
-      <c r="C107" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D107" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F107" s="260" t="inlineStr">
-        <is>
-          <t>31,680 UF (≈42% del Directo) — norma 25-35% en obras civiles, 40-50% en obras especializadas tunneling</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="260" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="B108" s="260" t="inlineStr">
-        <is>
-          <t>GG Aporte Oficina Central</t>
-        </is>
-      </c>
-      <c r="C108" s="260" t="inlineStr">
-        <is>
-          <t>1 gl</t>
-        </is>
-      </c>
-      <c r="D108" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E108" s="260" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="F108" s="260" t="inlineStr">
-        <is>
-          <t>≈4.4% del Directo (norma 3-6%)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="260" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="B109" s="260" t="inlineStr">
         <is>
-          <t>GG Gastos Financieros</t>
+          <t>Plazo referencial proyecto</t>
         </is>
       </c>
       <c r="C109" s="260" t="inlineStr">
         <is>
-          <t>1 gl</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D109" s="260" t="inlineStr">
         <is>
+          <t>24 meses</t>
+        </is>
+      </c>
+      <c r="E109" s="260" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E109" s="260" t="inlineStr">
-        <is>
-          <t>1,800</t>
-        </is>
-      </c>
       <c r="F109" s="260" t="inlineStr">
         <is>
-          <t>≈2.5% del Directo (intereses+factoring)</t>
+          <t>Estimado tunneling 2.45km — verificar Bases Técnicas</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="260" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B110" s="260" t="inlineStr">
         <is>
-          <t>GG Boletas Garantía + Seguros</t>
+          <t>Vigilancia 24h externalizada</t>
         </is>
       </c>
       <c r="C110" s="260" t="inlineStr">
         <is>
-          <t>1 gl</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D110" s="260" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24 m</t>
         </is>
       </c>
       <c r="E110" s="260" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F110" s="260" t="inlineStr">
         <is>
-          <t>≈1.6% del Directo</t>
+          <t>2,400 UF — servicio integral 4 guardias rotación</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="260" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B111" s="260" t="inlineStr">
         <is>
-          <t>TOTAL GASTOS GENERALES</t>
+          <t>Personal indirecto (8 personas, sueldo UF/mes)</t>
         </is>
       </c>
       <c r="C111" s="260" t="inlineStr">
@@ -18751,86 +18751,310 @@
       </c>
       <c r="D111" s="260" t="inlineStr">
         <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E111" s="260" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E111" s="260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F111" s="260" t="inlineStr">
         <is>
-          <t>6,200 UF (≈8.3% del Directo) — norma 8-12%</t>
+          <t>18,840 UF total. Admin 150, JT 120, 2×Sup 90, Prev 80, MA 70, Topo 80, Tra 55, Bod 50 UF/mes (mid-range Chile 2026)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="260" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B112" s="260" t="inlineStr">
         <is>
-          <t>Utilidad Contratista</t>
+          <t>Maquinarias y vehículos</t>
         </is>
       </c>
       <c r="C112" s="260" t="inlineStr">
         <is>
-          <t>1 gl</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D112" s="260" t="inlineStr">
         <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E112" s="260" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E112" s="260" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
       <c r="F112" s="260" t="inlineStr">
         <is>
-          <t>≈11% del Directo — norma 8-12% en obras especializadas</t>
+          <t>6,360 UF — 3 camionetas (35), fletes (50), andamios (30), equipos menores (80) UF/mes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="260" t="inlineStr">
         <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B113" s="260" t="inlineStr">
+        <is>
+          <t>Disposición residuos + excedentes</t>
+        </is>
+      </c>
+      <c r="C113" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D113" s="260" t="inlineStr">
+        <is>
+          <t>24 m</t>
+        </is>
+      </c>
+      <c r="E113" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="260" t="inlineStr">
+        <is>
+          <t>4,080 UF — residuos sólidos (50), excedentes excavación (120) UF/mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="260" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B114" s="260" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="C114" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="260" t="inlineStr">
+        <is>
+          <t>31,680 UF (≈42% del Directo) — norma 25-35% en obras civiles, 40-50% en obras especializadas tunneling</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="260" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B115" s="260" t="inlineStr">
+        <is>
+          <t>GG Aporte Oficina Central</t>
+        </is>
+      </c>
+      <c r="C115" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D115" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="260" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="F115" s="260" t="inlineStr">
+        <is>
+          <t>≈4.4% del Directo (norma 3-6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="260" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="260" t="inlineStr">
+        <is>
+          <t>GG Gastos Financieros</t>
+        </is>
+      </c>
+      <c r="C116" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D116" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="260" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="F116" s="260" t="inlineStr">
+        <is>
+          <t>≈2.5% del Directo (intereses+factoring)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="260" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B117" s="260" t="inlineStr">
+        <is>
+          <t>GG Boletas Garantía + Seguros</t>
+        </is>
+      </c>
+      <c r="C117" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D117" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="260" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="F117" s="260" t="inlineStr">
+        <is>
+          <t>≈1.6% del Directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="260" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B118" s="260" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS GENERALES</t>
+        </is>
+      </c>
+      <c r="C118" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D118" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="260" t="inlineStr">
+        <is>
+          <t>6,200 UF (≈8.3% del Directo) — norma 8-12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="260" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="B119" s="260" t="inlineStr">
+        <is>
+          <t>Utilidad Contratista</t>
+        </is>
+      </c>
+      <c r="C119" s="260" t="inlineStr">
+        <is>
+          <t>1 gl</t>
+        </is>
+      </c>
+      <c r="D119" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="260" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F119" s="260" t="inlineStr">
+        <is>
+          <t>≈11% del Directo — norma 8-12% en obras especializadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="260" t="inlineStr">
+        <is>
           <t>9.11</t>
         </is>
       </c>
-      <c r="B113" s="260" t="inlineStr">
+      <c r="B120" s="260" t="inlineStr">
         <is>
           <t>RESUMEN OFERTA</t>
         </is>
       </c>
-      <c r="C113" s="260" t="inlineStr">
+      <c r="C120" s="260" t="inlineStr">
         <is>
           <t>Directo: 74.843 UF | Indirecto: 31.680 UF | GG: 6.200 UF | Utilidad: 8.000 UF | Neto: 120.723 UF | IVA: 22.937 UF</t>
         </is>
       </c>
-      <c r="D113" s="260" t="inlineStr">
+      <c r="D120" s="260" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E113" s="260" t="inlineStr">
+      <c r="E120" s="260" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F113" s="260" t="inlineStr">
+      <c r="F120" s="260" t="inlineStr">
         <is>
           <t>TOTAL: 143.660 UF ≈ $5,531M CLP</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="247" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="247" t="inlineStr">
         <is>
           <t>⚠ Valores marcados salmón en hoja B son REFERENCIALES (plazo 24 meses + tasas Chile 2026). Contratista debe ajustar a su estructura organizacional, plazo real y costo de personal específico.</t>
         </is>
@@ -18838,19 +19062,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
